--- a/MA_Model.xlsx
+++ b/MA_Model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\OneDrive\Desktop\Equity Research\Models\Financials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49E07061-94C2-4DBF-A324-F23FAD91F49F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A75B26A-DD46-4B57-B54C-2B65747F9A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -4750,7 +4750,7 @@
     <t>Q3'25</t>
   </si>
   <si>
-    <t>10/31/25</t>
+    <t>1/10/2025</t>
   </si>
 </sst>
 </file>
@@ -5250,17 +5250,17 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="3" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Comma" xfId="3" builtinId="3"/>
@@ -10943,8 +10943,8 @@
       <sheetName val="Model"/>
       <sheetName val="Notes | Quant Analysis"/>
       <sheetName val="M&amp;A Scope"/>
+      <sheetName val="Markets | Product Lines"/>
       <sheetName val="Management"/>
-      <sheetName val="Markets | Product Lines"/>
       <sheetName val="Debt Schedule"/>
       <sheetName val="Clinical Trial Channel"/>
     </sheetNames>
@@ -11820,7 +11820,7 @@
         <v>1</v>
       </c>
       <c r="C3" s="50">
-        <v>551.99</v>
+        <v>576.75</v>
       </c>
       <c r="D3" s="42" t="s">
         <v>1546</v>
@@ -11830,7 +11830,7 @@
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="73">
+      <c r="C4" s="71">
         <v>903</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -11843,7 +11843,7 @@
       </c>
       <c r="C5" s="49">
         <f>C3*C4</f>
-        <v>498446.97000000003</v>
+        <v>520805.25</v>
       </c>
     </row>
     <row r="6" spans="1:17">
@@ -11875,7 +11875,7 @@
       </c>
       <c r="C8" s="49">
         <f>C5-C6+C7</f>
-        <v>505508.97000000003</v>
+        <v>527867.25</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="15">
@@ -11884,12 +11884,12 @@
       </c>
     </row>
     <row r="12" spans="1:17" ht="15" customHeight="1">
-      <c r="B12" s="70" t="s">
+      <c r="B12" s="73" t="s">
         <v>1437</v>
       </c>
-      <c r="C12" s="70"/>
-      <c r="D12" s="70"/>
-      <c r="E12" s="70"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="73"/>
       <c r="F12" s="1" t="s">
         <v>1444</v>
       </c>
@@ -12149,9 +12149,6 @@
     <hyperlink ref="P17" r:id="rId6" xr:uid="{BFFE0515-D705-45D2-BE38-8564DD95016D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <ignoredErrors>
-    <ignoredError sqref="D3" twoDigitTextYear="1"/>
-  </ignoredErrors>
   <drawing r:id="rId7"/>
 </worksheet>
 </file>
@@ -15096,67 +15093,67 @@
       <c r="BU26" s="34"/>
       <c r="BV26" s="34"/>
       <c r="CA26" s="2">
-        <f>SUM(C26:F26)</f>
+        <f t="shared" ref="CA26:CA39" si="41">SUM(C26:F26)</f>
         <v>5099</v>
       </c>
       <c r="CB26" s="2">
-        <f>SUM(G26:J26)</f>
+        <f t="shared" ref="CB26:CB39" si="42">SUM(G26:J26)</f>
         <v>5539</v>
       </c>
       <c r="CC26" s="2">
-        <f>SUM(K26:N26)</f>
+        <f t="shared" ref="CC26:CC39" si="43">SUM(K26:N26)</f>
         <v>6714</v>
       </c>
       <c r="CD26" s="2">
-        <f>SUM(O26:R26)</f>
+        <f t="shared" ref="CD26:CD39" si="44">SUM(O26:R26)</f>
         <v>7391</v>
       </c>
       <c r="CE26" s="2">
-        <f>SUM(S26:V26)</f>
+        <f t="shared" ref="CE26:CE39" si="45">SUM(S26:V26)</f>
         <v>8312</v>
       </c>
       <c r="CF26" s="2">
-        <f>SUM(W26:Z26)</f>
+        <f t="shared" ref="CF26:CF39" si="46">SUM(W26:Z26)</f>
         <v>9441</v>
       </c>
       <c r="CG26" s="2">
-        <f>SUM(AA26:AD26)</f>
+        <f t="shared" ref="CG26:CG39" si="47">SUM(AA26:AD26)</f>
         <v>9667</v>
       </c>
       <c r="CH26" s="2">
-        <f>SUM(AE26:AH26)</f>
+        <f t="shared" ref="CH26:CH39" si="48">SUM(AE26:AH26)</f>
         <v>10776</v>
       </c>
       <c r="CI26" s="2">
-        <f>SUM(AI26:AL26)</f>
+        <f t="shared" ref="CI26:CI39" si="49">SUM(AI26:AL26)</f>
         <v>12497</v>
       </c>
       <c r="CJ26" s="2">
-        <f>SUM(AM26:AP26)</f>
+        <f t="shared" ref="CJ26:CJ39" si="50">SUM(AM26:AP26)</f>
         <v>14950</v>
       </c>
       <c r="CK26" s="2">
-        <f>SUM(AQ26:AT26)</f>
+        <f t="shared" ref="CK26:CK39" si="51">SUM(AQ26:AT26)</f>
         <v>16883</v>
       </c>
       <c r="CL26" s="2">
-        <f>SUM(AU26:AX26)</f>
+        <f t="shared" ref="CL26:CL39" si="52">SUM(AU26:AX26)</f>
         <v>15301</v>
       </c>
       <c r="CM26" s="2">
-        <f>SUM(AY26:BB26)</f>
+        <f t="shared" ref="CM26:CM39" si="53">SUM(AY26:BB26)</f>
         <v>18884</v>
       </c>
       <c r="CN26" s="2">
-        <f>SUM(BC26:BF26)</f>
+        <f t="shared" ref="CN26:CN39" si="54">SUM(BC26:BF26)</f>
         <v>22237</v>
       </c>
       <c r="CO26" s="2">
-        <f>SUM(BG26:BJ26)</f>
+        <f t="shared" ref="CO26:CO39" si="55">SUM(BG26:BJ26)</f>
         <v>25098</v>
       </c>
       <c r="CP26" s="2">
-        <f>SUM(BK26:BN26)</f>
+        <f t="shared" ref="CP26:CP39" si="56">SUM(BK26:BN26)</f>
         <v>28167</v>
       </c>
       <c r="CQ26" s="67">
@@ -15164,39 +15161,39 @@
         <v>32478.629999999997</v>
       </c>
       <c r="CR26" s="67">
-        <f t="shared" ref="CR26:CZ26" si="41">CR6</f>
+        <f t="shared" ref="CR26:CZ26" si="57">CR6</f>
         <v>36855.64215</v>
       </c>
       <c r="CS26" s="67">
-        <f t="shared" si="41"/>
+        <f t="shared" si="57"/>
         <v>41279.782982374993</v>
       </c>
       <c r="CT26" s="67">
-        <f t="shared" si="41"/>
+        <f t="shared" si="57"/>
         <v>46041.17782458687</v>
       </c>
       <c r="CU26" s="67">
-        <f t="shared" si="41"/>
+        <f t="shared" si="57"/>
         <v>51040.633973943157</v>
       </c>
       <c r="CV26" s="67">
-        <f t="shared" si="41"/>
+        <f t="shared" si="57"/>
         <v>55566.663662783933</v>
       </c>
       <c r="CW26" s="67">
-        <f t="shared" si="41"/>
+        <f t="shared" si="57"/>
         <v>59387.720350568808</v>
       </c>
       <c r="CX26" s="67">
-        <f t="shared" si="41"/>
+        <f t="shared" si="57"/>
         <v>62751.622431191703</v>
       </c>
       <c r="CY26" s="67">
-        <f t="shared" si="41"/>
+        <f t="shared" si="57"/>
         <v>65995.605047790916</v>
       </c>
       <c r="CZ26" s="67">
-        <f t="shared" si="41"/>
+        <f t="shared" si="57"/>
         <v>69080.798433329881</v>
       </c>
       <c r="DA26" s="34"/>
@@ -15465,67 +15462,67 @@
         <v>2923</v>
       </c>
       <c r="CA27" s="1">
-        <f>SUM(C27:F27)</f>
+        <f t="shared" si="41"/>
         <v>1942</v>
       </c>
       <c r="CB27" s="1">
-        <f>SUM(G27:J27)</f>
+        <f t="shared" si="42"/>
         <v>1857</v>
       </c>
       <c r="CC27" s="1">
-        <f>SUM(K27:N27)</f>
+        <f t="shared" si="43"/>
         <v>2196</v>
       </c>
       <c r="CD27" s="1">
-        <f>SUM(O27:R27)</f>
+        <f t="shared" si="44"/>
         <v>2429</v>
       </c>
       <c r="CE27" s="1">
-        <f>SUM(S27:V27)</f>
+        <f t="shared" si="45"/>
         <v>2615</v>
       </c>
       <c r="CF27" s="1">
-        <f>SUM(W27:Z27)</f>
+        <f t="shared" si="46"/>
         <v>3152</v>
       </c>
       <c r="CG27" s="1">
-        <f>SUM(AA27:AD27)</f>
+        <f t="shared" si="47"/>
         <v>3341</v>
       </c>
       <c r="CH27" s="1">
-        <f>SUM(AE27:AH27)</f>
+        <f t="shared" si="48"/>
         <v>3827</v>
       </c>
       <c r="CI27" s="1">
-        <f>SUM(AI27:AL27)</f>
+        <f t="shared" si="49"/>
         <v>4653</v>
       </c>
       <c r="CJ27" s="1">
-        <f>SUM(AM27:AP27)</f>
+        <f t="shared" si="50"/>
         <v>5174</v>
       </c>
       <c r="CK27" s="1">
-        <f>SUM(AQ27:AT27)</f>
+        <f t="shared" si="51"/>
         <v>5763</v>
       </c>
       <c r="CL27" s="1">
-        <f>SUM(AU27:AX27)</f>
+        <f t="shared" si="52"/>
         <v>5910</v>
       </c>
       <c r="CM27" s="1">
-        <f>SUM(AY27:BB27)</f>
+        <f t="shared" si="53"/>
         <v>7087</v>
       </c>
       <c r="CN27" s="1">
-        <f>SUM(BC27:BF27)</f>
+        <f t="shared" si="54"/>
         <v>8078</v>
       </c>
       <c r="CO27" s="1">
-        <f>SUM(BG27:BJ27)</f>
+        <f t="shared" si="55"/>
         <v>8927</v>
       </c>
       <c r="CP27" s="1">
-        <f>SUM(BK27:BN27)</f>
+        <f t="shared" si="56"/>
         <v>10193</v>
       </c>
       <c r="CQ27" s="63">
@@ -15533,39 +15530,39 @@
         <v>11286.323924999999</v>
       </c>
       <c r="CR27" s="63">
-        <f t="shared" ref="CR27:CZ27" si="42">CR26*(CR43)</f>
+        <f t="shared" ref="CR27:CZ27" si="58">CR26*(CR43)</f>
         <v>12715.19654175</v>
       </c>
       <c r="CS27" s="63">
-        <f t="shared" si="42"/>
+        <f t="shared" si="58"/>
         <v>14138.325671463435</v>
       </c>
       <c r="CT27" s="63">
-        <f t="shared" si="42"/>
+        <f t="shared" si="58"/>
         <v>15654.000460359537</v>
       </c>
       <c r="CU27" s="63">
-        <f t="shared" si="42"/>
+        <f t="shared" si="58"/>
         <v>17226.213966205818</v>
       </c>
       <c r="CV27" s="63">
-        <f t="shared" si="42"/>
+        <f t="shared" si="58"/>
         <v>18614.832327032618</v>
       </c>
       <c r="CW27" s="63">
-        <f t="shared" si="42"/>
+        <f t="shared" si="58"/>
         <v>19746.41701656413</v>
       </c>
       <c r="CX27" s="63">
-        <f t="shared" si="42"/>
+        <f t="shared" si="58"/>
         <v>20833.538647155645</v>
       </c>
       <c r="CY27" s="63">
-        <f t="shared" si="42"/>
+        <f t="shared" si="58"/>
         <v>21844.545270818795</v>
       </c>
       <c r="CZ27" s="63">
-        <f t="shared" si="42"/>
+        <f t="shared" si="58"/>
         <v>22796.663482998862</v>
       </c>
     </row>
@@ -15824,67 +15821,67 @@
         <v>245</v>
       </c>
       <c r="CA28" s="1">
-        <f>SUM(C28:F28)</f>
+        <f t="shared" si="41"/>
         <v>897</v>
       </c>
       <c r="CB28" s="1">
-        <f>SUM(G28:J28)</f>
+        <f t="shared" si="42"/>
         <v>930</v>
       </c>
       <c r="CC28" s="1">
-        <f>SUM(K28:N28)</f>
+        <f t="shared" si="43"/>
         <v>1805</v>
       </c>
       <c r="CD28" s="1">
-        <f>SUM(O28:R28)</f>
+        <f t="shared" si="44"/>
         <v>1025</v>
       </c>
       <c r="CE28" s="1">
-        <f>SUM(S28:V28)</f>
+        <f t="shared" si="45"/>
         <v>1194</v>
       </c>
       <c r="CF28" s="1">
-        <f>SUM(W28:Z28)</f>
+        <f t="shared" si="46"/>
         <v>1183</v>
       </c>
       <c r="CG28" s="1">
-        <f>SUM(AA28:AD28)</f>
+        <f t="shared" si="47"/>
         <v>1248</v>
       </c>
       <c r="CH28" s="1">
-        <f>SUM(AE28:AH28)</f>
+        <f t="shared" si="48"/>
         <v>1188</v>
       </c>
       <c r="CI28" s="1">
-        <f>SUM(AI28:AL28)</f>
+        <f t="shared" si="49"/>
         <v>1222</v>
       </c>
       <c r="CJ28" s="1">
-        <f>SUM(AM28:AP28)</f>
+        <f t="shared" si="50"/>
         <v>2494</v>
       </c>
       <c r="CK28" s="1">
-        <f>SUM(AQ28:AT28)</f>
+        <f t="shared" si="51"/>
         <v>1456</v>
       </c>
       <c r="CL28" s="1">
-        <f>SUM(AU28:AX28)</f>
+        <f t="shared" si="52"/>
         <v>657</v>
       </c>
       <c r="CM28" s="1">
-        <f>SUM(AY28:BB28)</f>
+        <f t="shared" si="53"/>
         <v>895</v>
       </c>
       <c r="CN28" s="1">
-        <f>SUM(BC28:BF28)</f>
+        <f t="shared" si="54"/>
         <v>789</v>
       </c>
       <c r="CO28" s="1">
-        <f>SUM(BG28:BJ28)</f>
+        <f t="shared" si="55"/>
         <v>825</v>
       </c>
       <c r="CP28" s="1">
-        <f>SUM(BK28:BN28)</f>
+        <f t="shared" si="56"/>
         <v>815</v>
       </c>
       <c r="CQ28" s="63">
@@ -15892,39 +15889,39 @@
         <v>844.44437999999991</v>
       </c>
       <c r="CR28" s="63">
-        <f t="shared" ref="CR28:CZ28" si="43">CR26*(CR44)</f>
+        <f t="shared" ref="CR28:CZ28" si="59">CR26*(CR44)</f>
         <v>1050.3858012749999</v>
       </c>
       <c r="CS28" s="63">
-        <f t="shared" si="43"/>
+        <f t="shared" si="59"/>
         <v>1155.8339235064998</v>
       </c>
       <c r="CT28" s="63">
-        <f t="shared" si="43"/>
+        <f t="shared" si="59"/>
         <v>1266.1323901761389</v>
       </c>
       <c r="CU28" s="63">
-        <f t="shared" si="43"/>
+        <f t="shared" si="59"/>
         <v>1378.0971172964653</v>
       </c>
       <c r="CV28" s="63">
-        <f t="shared" si="43"/>
+        <f t="shared" si="59"/>
         <v>1472.5165870637741</v>
       </c>
       <c r="CW28" s="63">
-        <f t="shared" si="43"/>
+        <f t="shared" si="59"/>
         <v>1544.0807291147889</v>
       </c>
       <c r="CX28" s="63">
-        <f t="shared" si="43"/>
+        <f t="shared" si="59"/>
         <v>1600.1663719953883</v>
       </c>
       <c r="CY28" s="63">
-        <f t="shared" si="43"/>
+        <f t="shared" si="59"/>
         <v>1649.8901261947731</v>
       </c>
       <c r="CZ28" s="63">
-        <f t="shared" si="43"/>
+        <f t="shared" si="59"/>
         <v>1692.4795616165823</v>
       </c>
     </row>
@@ -16051,67 +16048,67 @@
         <v>290</v>
       </c>
       <c r="CA29" s="1">
-        <f>SUM(C29:F29)</f>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="CB29" s="1">
-        <f>SUM(G29:J29)</f>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="CC29" s="1">
-        <f>SUM(K29:N29)</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="CD29" s="1">
-        <f>SUM(O29:R29)</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="CE29" s="1">
-        <f>SUM(S29:V29)</f>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="CF29" s="1">
-        <f>SUM(W29:Z29)</f>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="CG29" s="1">
-        <f>SUM(AA29:AD29)</f>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="CH29" s="1">
-        <f>SUM(AE29:AH29)</f>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="CI29" s="1">
-        <f>SUM(AI29:AL29)</f>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="CJ29" s="1">
-        <f>SUM(AM29:AP29)</f>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="CK29" s="1">
-        <f>SUM(AQ29:AT29)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="CL29" s="1">
-        <f>SUM(AU29:AX29)</f>
+        <f t="shared" si="52"/>
         <v>580</v>
       </c>
       <c r="CM29" s="1">
-        <f>SUM(AY29:BB29)</f>
+        <f t="shared" si="53"/>
         <v>726</v>
       </c>
       <c r="CN29" s="1">
-        <f>SUM(BC29:BF29)</f>
+        <f t="shared" si="54"/>
         <v>750</v>
       </c>
       <c r="CO29" s="1">
-        <f>SUM(BG29:BJ29)</f>
+        <f t="shared" si="55"/>
         <v>799</v>
       </c>
       <c r="CP29" s="1">
-        <f>SUM(BK29:BN29)</f>
+        <f t="shared" si="56"/>
         <v>897</v>
       </c>
       <c r="CQ29" s="63">
@@ -16119,39 +16116,39 @@
         <v>1169.2306799999999</v>
       </c>
       <c r="CR29" s="63">
-        <f t="shared" ref="CR29:CZ29" si="44">CR26*(CR45)</f>
+        <f t="shared" ref="CR29:CZ29" si="60">CR26*(CR45)</f>
         <v>1289.94747525</v>
       </c>
       <c r="CS29" s="63">
-        <f t="shared" si="44"/>
+        <f t="shared" si="60"/>
         <v>825.59565964749982</v>
       </c>
       <c r="CT29" s="63">
-        <f t="shared" si="44"/>
+        <f t="shared" si="60"/>
         <v>920.82355649173746</v>
       </c>
       <c r="CU29" s="63">
-        <f t="shared" si="44"/>
+        <f t="shared" si="60"/>
         <v>1020.8126794788632</v>
       </c>
       <c r="CV29" s="63">
-        <f t="shared" si="44"/>
+        <f t="shared" si="60"/>
         <v>1111.3332732556787</v>
       </c>
       <c r="CW29" s="63">
-        <f t="shared" si="44"/>
+        <f t="shared" si="60"/>
         <v>1187.7544070113761</v>
       </c>
       <c r="CX29" s="63">
-        <f t="shared" si="44"/>
+        <f t="shared" si="60"/>
         <v>1255.0324486238342</v>
       </c>
       <c r="CY29" s="63">
-        <f t="shared" si="44"/>
+        <f t="shared" si="60"/>
         <v>1319.9121009558182</v>
       </c>
       <c r="CZ29" s="63">
-        <f t="shared" si="44"/>
+        <f t="shared" si="60"/>
         <v>1381.6159686665976</v>
       </c>
     </row>
@@ -16278,67 +16275,67 @@
         <v>83</v>
       </c>
       <c r="CA30" s="1">
-        <f>SUM(C30:F30)</f>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="CB30" s="1">
-        <f>SUM(G30:J30)</f>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="CC30" s="1">
-        <f>SUM(K30:N30)</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="CD30" s="1">
-        <f>SUM(O30:R30)</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="CE30" s="1">
-        <f>SUM(S30:V30)</f>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="CF30" s="1">
-        <f>SUM(W30:Z30)</f>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="CG30" s="1">
-        <f>SUM(AA30:AD30)</f>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="CH30" s="1">
-        <f>SUM(AE30:AH30)</f>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="CI30" s="1">
-        <f>SUM(AI30:AL30)</f>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="CJ30" s="1">
-        <f>SUM(AM30:AP30)</f>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="CK30" s="1">
-        <f>SUM(AQ30:AT30)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="CL30" s="1">
-        <f>SUM(AU30:AX30)</f>
+        <f t="shared" si="52"/>
         <v>73</v>
       </c>
       <c r="CM30" s="1">
-        <f>SUM(AY30:BB30)</f>
+        <f t="shared" si="53"/>
         <v>94</v>
       </c>
       <c r="CN30" s="1">
-        <f>SUM(BC30:BF30)</f>
+        <f t="shared" si="54"/>
         <v>356</v>
       </c>
       <c r="CO30" s="1">
-        <f>SUM(BG30:BJ30)</f>
+        <f t="shared" si="55"/>
         <v>539</v>
       </c>
       <c r="CP30" s="1">
-        <f>SUM(BK30:BN30)</f>
+        <f t="shared" si="56"/>
         <v>680</v>
       </c>
       <c r="CQ30" s="63">
@@ -16346,39 +16343,39 @@
         <v>568.37602500000003</v>
       </c>
       <c r="CR30" s="63">
-        <f t="shared" ref="CR30:CZ30" si="45">CR26*(CR46)</f>
+        <f t="shared" ref="CR30:CZ30" si="61">CR26*(CR46)</f>
         <v>552.83463225000003</v>
       </c>
       <c r="CS30" s="63">
-        <f t="shared" si="45"/>
+        <f t="shared" si="61"/>
         <v>515.99728727968738</v>
       </c>
       <c r="CT30" s="63">
-        <f t="shared" si="45"/>
+        <f t="shared" si="61"/>
         <v>460.41177824586873</v>
       </c>
       <c r="CU30" s="63">
-        <f t="shared" si="45"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="CV30" s="63">
-        <f t="shared" si="45"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="CW30" s="63">
-        <f t="shared" si="45"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="CX30" s="63">
-        <f t="shared" si="45"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="CY30" s="63">
-        <f t="shared" si="45"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
       <c r="CZ30" s="63">
-        <f t="shared" si="45"/>
+        <f t="shared" si="61"/>
         <v>0</v>
       </c>
     </row>
@@ -16387,259 +16384,259 @@
         <v>1491</v>
       </c>
       <c r="C31" s="52">
-        <f t="shared" ref="C31:AT31" si="46">SUM(C27:C30)</f>
+        <f t="shared" ref="C31:AT31" si="62">SUM(C27:C30)</f>
         <v>595</v>
       </c>
       <c r="D31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>723</v>
       </c>
       <c r="E31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>691</v>
       </c>
       <c r="F31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>830</v>
       </c>
       <c r="G31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>608</v>
       </c>
       <c r="H31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>648</v>
       </c>
       <c r="I31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>662</v>
       </c>
       <c r="J31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>869</v>
       </c>
       <c r="K31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>665</v>
       </c>
       <c r="L31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>782</v>
       </c>
       <c r="M31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>816</v>
       </c>
       <c r="N31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>1738</v>
       </c>
       <c r="O31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>758</v>
       </c>
       <c r="P31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>846</v>
       </c>
       <c r="Q31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>854</v>
       </c>
       <c r="R31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>996</v>
       </c>
       <c r="S31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>799</v>
       </c>
       <c r="T31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>868</v>
       </c>
       <c r="U31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>970</v>
       </c>
       <c r="V31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>1172</v>
       </c>
       <c r="W31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>887</v>
       </c>
       <c r="X31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>985</v>
       </c>
       <c r="Y31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>1070</v>
       </c>
       <c r="Z31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>1393</v>
       </c>
       <c r="AA31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>879</v>
       </c>
       <c r="AB31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>1139</v>
       </c>
       <c r="AC31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>1161</v>
       </c>
       <c r="AD31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>1410</v>
       </c>
       <c r="AE31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>1098</v>
       </c>
       <c r="AF31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>1314</v>
       </c>
       <c r="AG31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>1210</v>
       </c>
       <c r="AH31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>1393</v>
       </c>
       <c r="AI31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>1228</v>
       </c>
       <c r="AJ31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>1400</v>
       </c>
       <c r="AK31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>1457</v>
       </c>
       <c r="AL31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>1790</v>
       </c>
       <c r="AM31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>1755</v>
       </c>
       <c r="AN31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>1729</v>
       </c>
       <c r="AO31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>1611</v>
       </c>
       <c r="AP31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>2573</v>
       </c>
       <c r="AQ31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>1676</v>
       </c>
       <c r="AR31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>1716</v>
       </c>
       <c r="AS31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>1812</v>
       </c>
       <c r="AT31" s="52">
-        <f t="shared" si="46"/>
+        <f t="shared" si="62"/>
         <v>2015</v>
       </c>
       <c r="AU31" s="1">
-        <f t="shared" ref="AU31" si="47">SUM(AU27:AU30)</f>
+        <f t="shared" ref="AU31" si="63">SUM(AU27:AU30)</f>
         <v>1798</v>
       </c>
       <c r="AV31" s="1">
-        <f t="shared" ref="AV31" si="48">SUM(AV27:AV30)</f>
+        <f t="shared" ref="AV31" si="64">SUM(AV27:AV30)</f>
         <v>1628</v>
       </c>
       <c r="AW31" s="1">
-        <f t="shared" ref="AW31" si="49">SUM(AW27:AW30)</f>
+        <f t="shared" ref="AW31" si="65">SUM(AW27:AW30)</f>
         <v>1732</v>
       </c>
       <c r="AX31" s="1">
-        <f t="shared" ref="AX31" si="50">SUM(AX27:AX30)</f>
+        <f t="shared" ref="AX31" si="66">SUM(AX27:AX30)</f>
         <v>2062</v>
       </c>
       <c r="AY31" s="1">
-        <f t="shared" ref="AY31:BN31" si="51">SUM(AY27:AY30)</f>
+        <f t="shared" ref="AY31:BN31" si="67">SUM(AY27:AY30)</f>
         <v>1958</v>
       </c>
       <c r="AZ31" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="67"/>
         <v>2187</v>
       </c>
       <c r="BA31" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="67"/>
         <v>2268</v>
       </c>
       <c r="BB31" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="67"/>
         <v>2389</v>
       </c>
       <c r="BC31" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="67"/>
         <v>2217</v>
       </c>
       <c r="BD31" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="67"/>
         <v>2479</v>
       </c>
       <c r="BE31" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="67"/>
         <v>2644</v>
       </c>
       <c r="BF31" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="67"/>
         <v>2633</v>
       </c>
       <c r="BG31" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="67"/>
         <v>2612</v>
       </c>
       <c r="BH31" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="67"/>
         <v>2613</v>
       </c>
       <c r="BI31" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="67"/>
         <v>2689</v>
       </c>
       <c r="BJ31" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="67"/>
         <v>3176</v>
       </c>
       <c r="BK31" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="67"/>
         <v>2744</v>
       </c>
       <c r="BL31" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="67"/>
         <v>2925</v>
       </c>
       <c r="BM31" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="67"/>
         <v>3365</v>
       </c>
       <c r="BN31" s="1">
-        <f t="shared" si="51"/>
+        <f t="shared" si="67"/>
         <v>3551</v>
       </c>
       <c r="BO31" s="1">
@@ -16655,67 +16652,67 @@
         <v>3541</v>
       </c>
       <c r="CA31" s="1">
-        <f>SUM(C31:F31)</f>
+        <f t="shared" si="41"/>
         <v>2839</v>
       </c>
       <c r="CB31" s="1">
-        <f>SUM(G31:J31)</f>
+        <f t="shared" si="42"/>
         <v>2787</v>
       </c>
       <c r="CC31" s="1">
-        <f>SUM(K31:N31)</f>
+        <f t="shared" si="43"/>
         <v>4001</v>
       </c>
       <c r="CD31" s="1">
-        <f>SUM(O31:R31)</f>
+        <f t="shared" si="44"/>
         <v>3454</v>
       </c>
       <c r="CE31" s="1">
-        <f>SUM(S31:V31)</f>
+        <f t="shared" si="45"/>
         <v>3809</v>
       </c>
       <c r="CF31" s="1">
-        <f>SUM(W31:Z31)</f>
+        <f t="shared" si="46"/>
         <v>4335</v>
       </c>
       <c r="CG31" s="1">
-        <f>SUM(AA31:AD31)</f>
+        <f t="shared" si="47"/>
         <v>4589</v>
       </c>
       <c r="CH31" s="1">
-        <f>SUM(AE31:AH31)</f>
+        <f t="shared" si="48"/>
         <v>5015</v>
       </c>
       <c r="CI31" s="1">
-        <f>SUM(AI31:AL31)</f>
+        <f t="shared" si="49"/>
         <v>5875</v>
       </c>
       <c r="CJ31" s="1">
-        <f>SUM(AM31:AP31)</f>
+        <f t="shared" si="50"/>
         <v>7668</v>
       </c>
       <c r="CK31" s="1">
-        <f>SUM(AQ31:AT31)</f>
+        <f t="shared" si="51"/>
         <v>7219</v>
       </c>
       <c r="CL31" s="1">
-        <f>SUM(AU31:AX31)</f>
+        <f t="shared" si="52"/>
         <v>7220</v>
       </c>
       <c r="CM31" s="1">
-        <f>SUM(AY31:BB31)</f>
+        <f t="shared" si="53"/>
         <v>8802</v>
       </c>
       <c r="CN31" s="1">
-        <f>SUM(BC31:BF31)</f>
+        <f t="shared" si="54"/>
         <v>9973</v>
       </c>
       <c r="CO31" s="1">
-        <f>SUM(BG31:BJ31)</f>
+        <f t="shared" si="55"/>
         <v>11090</v>
       </c>
       <c r="CP31" s="1">
-        <f>SUM(BK31:BN31)</f>
+        <f t="shared" si="56"/>
         <v>12585</v>
       </c>
       <c r="CQ31" s="63">
@@ -16723,39 +16720,39 @@
         <v>13868.375009999998</v>
       </c>
       <c r="CR31" s="63">
-        <f t="shared" ref="CR31:CZ31" si="52">SUM(CR27:CR30)</f>
+        <f t="shared" ref="CR31:CZ31" si="68">SUM(CR27:CR30)</f>
         <v>15608.364450525001</v>
       </c>
       <c r="CS31" s="63">
-        <f t="shared" si="52"/>
+        <f t="shared" si="68"/>
         <v>16635.75254189712</v>
       </c>
       <c r="CT31" s="63">
-        <f t="shared" si="52"/>
+        <f t="shared" si="68"/>
         <v>18301.368185273281</v>
       </c>
       <c r="CU31" s="63">
-        <f t="shared" si="52"/>
+        <f t="shared" si="68"/>
         <v>19625.123762981144</v>
       </c>
       <c r="CV31" s="63">
-        <f t="shared" si="52"/>
+        <f t="shared" si="68"/>
         <v>21198.682187352071</v>
       </c>
       <c r="CW31" s="63">
-        <f t="shared" si="52"/>
+        <f t="shared" si="68"/>
         <v>22478.252152690296</v>
       </c>
       <c r="CX31" s="63">
-        <f t="shared" si="52"/>
+        <f t="shared" si="68"/>
         <v>23688.737467774867</v>
       </c>
       <c r="CY31" s="63">
-        <f t="shared" si="52"/>
+        <f t="shared" si="68"/>
         <v>24814.347497969386</v>
       </c>
       <c r="CZ31" s="63">
-        <f t="shared" si="52"/>
+        <f t="shared" si="68"/>
         <v>25870.759013282041</v>
       </c>
     </row>
@@ -16764,259 +16761,259 @@
         <v>1492</v>
       </c>
       <c r="C32" s="52">
-        <f t="shared" ref="C32:AT32" si="53">C26-C31</f>
+        <f t="shared" ref="C32:AT32" si="69">C26-C31</f>
         <v>561</v>
       </c>
       <c r="D32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>557</v>
       </c>
       <c r="E32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>673</v>
       </c>
       <c r="F32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>469</v>
       </c>
       <c r="G32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>700</v>
       </c>
       <c r="H32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>717</v>
       </c>
       <c r="I32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>766</v>
       </c>
       <c r="J32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>569</v>
       </c>
       <c r="K32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>836</v>
       </c>
       <c r="L32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>885</v>
       </c>
       <c r="M32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>1002</v>
       </c>
       <c r="N32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>-10</v>
       </c>
       <c r="O32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>1000</v>
       </c>
       <c r="P32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>974</v>
       </c>
       <c r="Q32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>1064</v>
       </c>
       <c r="R32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>899</v>
       </c>
       <c r="S32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>1107</v>
       </c>
       <c r="T32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>1228</v>
       </c>
       <c r="U32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>1248</v>
       </c>
       <c r="V32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>920</v>
       </c>
       <c r="W32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>1285</v>
       </c>
       <c r="X32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>1383</v>
       </c>
       <c r="Y32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>1420</v>
       </c>
       <c r="Z32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>1018</v>
       </c>
       <c r="AA32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>1351</v>
       </c>
       <c r="AB32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>1251</v>
       </c>
       <c r="AC32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>1369</v>
       </c>
       <c r="AD32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>1107</v>
       </c>
       <c r="AE32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>1348</v>
       </c>
       <c r="AF32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>1380</v>
       </c>
       <c r="AG32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>1670</v>
       </c>
       <c r="AH32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>1363</v>
       </c>
       <c r="AI32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>1506</v>
       </c>
       <c r="AJ32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>1653</v>
       </c>
       <c r="AK32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>1941</v>
       </c>
       <c r="AL32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>1522</v>
       </c>
       <c r="AM32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>1825</v>
       </c>
       <c r="AN32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>1936</v>
       </c>
       <c r="AO32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>2287</v>
       </c>
       <c r="AP32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>1234</v>
       </c>
       <c r="AQ32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>2213</v>
       </c>
       <c r="AR32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>2397</v>
       </c>
       <c r="AS32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>2655</v>
       </c>
       <c r="AT32" s="52">
-        <f t="shared" si="53"/>
+        <f t="shared" si="69"/>
         <v>2399</v>
       </c>
       <c r="AU32" s="1">
-        <f t="shared" ref="AU32:BJ32" si="54">AU26-AU31</f>
+        <f t="shared" ref="AU32:BJ32" si="70">AU26-AU31</f>
         <v>2211</v>
       </c>
       <c r="AV32" s="1">
-        <f t="shared" si="54"/>
+        <f t="shared" si="70"/>
         <v>1707</v>
       </c>
       <c r="AW32" s="1">
-        <f t="shared" si="54"/>
+        <f t="shared" si="70"/>
         <v>2105</v>
       </c>
       <c r="AX32" s="1">
-        <f t="shared" si="54"/>
+        <f t="shared" si="70"/>
         <v>2058</v>
       </c>
       <c r="AY32" s="1">
-        <f t="shared" si="54"/>
+        <f t="shared" si="70"/>
         <v>2197</v>
       </c>
       <c r="AZ32" s="1">
-        <f t="shared" si="54"/>
+        <f t="shared" si="70"/>
         <v>2341</v>
       </c>
       <c r="BA32" s="1">
-        <f t="shared" si="54"/>
+        <f t="shared" si="70"/>
         <v>2717</v>
       </c>
       <c r="BB32" s="1">
-        <f t="shared" si="54"/>
+        <f t="shared" si="70"/>
         <v>2827</v>
       </c>
       <c r="BC32" s="1">
-        <f t="shared" si="54"/>
+        <f t="shared" si="70"/>
         <v>2950</v>
       </c>
       <c r="BD32" s="1">
-        <f t="shared" si="54"/>
+        <f t="shared" si="70"/>
         <v>3018</v>
       </c>
       <c r="BE32" s="1">
-        <f t="shared" si="54"/>
+        <f t="shared" si="70"/>
         <v>3112</v>
       </c>
       <c r="BF32" s="1">
-        <f t="shared" si="54"/>
+        <f t="shared" si="70"/>
         <v>3184</v>
       </c>
       <c r="BG32" s="1">
-        <f t="shared" si="54"/>
+        <f t="shared" si="70"/>
         <v>3136</v>
       </c>
       <c r="BH32" s="1">
-        <f t="shared" si="54"/>
+        <f t="shared" si="70"/>
         <v>3656</v>
       </c>
       <c r="BI32" s="1">
-        <f t="shared" si="54"/>
+        <f t="shared" si="70"/>
         <v>3844</v>
       </c>
       <c r="BJ32" s="1">
-        <f t="shared" si="54"/>
+        <f t="shared" si="70"/>
         <v>3372</v>
       </c>
       <c r="BK32" s="1">
-        <f t="shared" ref="BK32:BN32" si="55">BK26-BK31</f>
+        <f t="shared" ref="BK32:BN32" si="71">BK26-BK31</f>
         <v>3604</v>
       </c>
       <c r="BL32" s="1">
-        <f t="shared" si="55"/>
+        <f t="shared" si="71"/>
         <v>4036</v>
       </c>
       <c r="BM32" s="1">
-        <f t="shared" si="55"/>
+        <f t="shared" si="71"/>
         <v>4004</v>
       </c>
       <c r="BN32" s="1">
-        <f t="shared" si="55"/>
+        <f t="shared" si="71"/>
         <v>3938</v>
       </c>
       <c r="BO32" s="1">
@@ -17032,67 +17029,67 @@
         <v>5061</v>
       </c>
       <c r="CA32" s="1">
-        <f>SUM(C32:F32)</f>
+        <f t="shared" si="41"/>
         <v>2260</v>
       </c>
       <c r="CB32" s="1">
-        <f>SUM(G32:J32)</f>
+        <f t="shared" si="42"/>
         <v>2752</v>
       </c>
       <c r="CC32" s="1">
-        <f>SUM(K32:N32)</f>
+        <f t="shared" si="43"/>
         <v>2713</v>
       </c>
       <c r="CD32" s="1">
-        <f>SUM(O32:R32)</f>
+        <f t="shared" si="44"/>
         <v>3937</v>
       </c>
       <c r="CE32" s="1">
-        <f>SUM(S32:V32)</f>
+        <f t="shared" si="45"/>
         <v>4503</v>
       </c>
       <c r="CF32" s="1">
-        <f>SUM(W32:Z32)</f>
+        <f t="shared" si="46"/>
         <v>5106</v>
       </c>
       <c r="CG32" s="1">
-        <f>SUM(AA32:AD32)</f>
+        <f t="shared" si="47"/>
         <v>5078</v>
       </c>
       <c r="CH32" s="1">
-        <f>SUM(AE32:AH32)</f>
+        <f t="shared" si="48"/>
         <v>5761</v>
       </c>
       <c r="CI32" s="1">
-        <f>SUM(AI32:AL32)</f>
+        <f t="shared" si="49"/>
         <v>6622</v>
       </c>
       <c r="CJ32" s="1">
-        <f>SUM(AM32:AP32)</f>
+        <f t="shared" si="50"/>
         <v>7282</v>
       </c>
       <c r="CK32" s="1">
-        <f>SUM(AQ32:AT32)</f>
+        <f t="shared" si="51"/>
         <v>9664</v>
       </c>
       <c r="CL32" s="1">
-        <f>SUM(AU32:AX32)</f>
+        <f t="shared" si="52"/>
         <v>8081</v>
       </c>
       <c r="CM32" s="1">
-        <f>SUM(AY32:BB32)</f>
+        <f t="shared" si="53"/>
         <v>10082</v>
       </c>
       <c r="CN32" s="1">
-        <f>SUM(BC32:BF32)</f>
+        <f t="shared" si="54"/>
         <v>12264</v>
       </c>
       <c r="CO32" s="1">
-        <f>SUM(BG32:BJ32)</f>
+        <f t="shared" si="55"/>
         <v>14008</v>
       </c>
       <c r="CP32" s="1">
-        <f>SUM(BK32:BN32)</f>
+        <f t="shared" si="56"/>
         <v>15582</v>
       </c>
       <c r="CQ32" s="63">
@@ -17100,39 +17097,39 @@
         <v>18610.254990000001</v>
       </c>
       <c r="CR32" s="63">
-        <f t="shared" ref="CR32:CZ32" si="56">CR26-CR31</f>
+        <f t="shared" ref="CR32:CZ32" si="72">CR26-CR31</f>
         <v>21247.277699474998</v>
       </c>
       <c r="CS32" s="63">
-        <f t="shared" si="56"/>
+        <f t="shared" si="72"/>
         <v>24644.030440477873</v>
       </c>
       <c r="CT32" s="63">
-        <f t="shared" si="56"/>
+        <f t="shared" si="72"/>
         <v>27739.809639313589</v>
       </c>
       <c r="CU32" s="63">
-        <f t="shared" si="56"/>
+        <f t="shared" si="72"/>
         <v>31415.510210962013</v>
       </c>
       <c r="CV32" s="63">
-        <f t="shared" si="56"/>
+        <f t="shared" si="72"/>
         <v>34367.981475431865</v>
       </c>
       <c r="CW32" s="63">
-        <f t="shared" si="56"/>
+        <f t="shared" si="72"/>
         <v>36909.468197878508</v>
       </c>
       <c r="CX32" s="63">
-        <f t="shared" si="56"/>
+        <f t="shared" si="72"/>
         <v>39062.884963416836</v>
       </c>
       <c r="CY32" s="63">
-        <f t="shared" si="56"/>
+        <f t="shared" si="72"/>
         <v>41181.25754982153</v>
       </c>
       <c r="CZ32" s="63">
-        <f t="shared" si="56"/>
+        <f t="shared" si="72"/>
         <v>43210.03942004784</v>
       </c>
     </row>
@@ -17347,108 +17344,108 @@
         <v>81</v>
       </c>
       <c r="CA33" s="1">
-        <f>SUM(C33:F33)</f>
+        <f t="shared" si="41"/>
         <v>-42</v>
       </c>
       <c r="CB33" s="1">
-        <f>SUM(G33:J33)</f>
+        <f t="shared" si="42"/>
         <v>5</v>
       </c>
       <c r="CC33" s="1">
-        <f>SUM(K33:N33)</f>
+        <f t="shared" si="43"/>
         <v>35</v>
       </c>
       <c r="CD33" s="1">
-        <f>SUM(O33:R33)</f>
+        <f t="shared" si="44"/>
         <v>-4</v>
       </c>
       <c r="CE33" s="1">
-        <f>SUM(S33:V33)</f>
+        <f t="shared" si="45"/>
         <v>-3</v>
       </c>
       <c r="CF33" s="1">
-        <f>SUM(W33:Z33)</f>
+        <f t="shared" si="46"/>
         <v>-27</v>
       </c>
       <c r="CG33" s="1">
-        <f>SUM(AA33:AD33)</f>
+        <f t="shared" si="47"/>
         <v>-120</v>
       </c>
       <c r="CH33" s="1">
-        <f>SUM(AE33:AH33)</f>
+        <f t="shared" si="48"/>
         <v>-115</v>
       </c>
       <c r="CI33" s="1">
-        <f>SUM(AI33:AL33)</f>
+        <f t="shared" si="49"/>
         <v>-100</v>
       </c>
       <c r="CJ33" s="1">
-        <f>SUM(AM33:AP33)</f>
+        <f t="shared" si="50"/>
         <v>-78</v>
       </c>
       <c r="CK33" s="1">
-        <f>SUM(AQ33:AT33)</f>
+        <f t="shared" si="51"/>
         <v>67</v>
       </c>
       <c r="CL33" s="1">
-        <f>SUM(AU33:AX33)</f>
+        <f t="shared" si="52"/>
         <v>24</v>
       </c>
       <c r="CM33" s="1">
-        <f>SUM(AY33:BB33)</f>
+        <f t="shared" si="53"/>
         <v>11</v>
       </c>
       <c r="CN33" s="1">
-        <f>SUM(BC33:BF33)</f>
+        <f t="shared" si="54"/>
         <v>61</v>
       </c>
       <c r="CO33" s="1">
-        <f>SUM(BG33:BJ33)</f>
+        <f t="shared" si="55"/>
         <v>274</v>
       </c>
       <c r="CP33" s="1">
-        <f>SUM(BK33:BN33)</f>
+        <f t="shared" si="56"/>
         <v>327</v>
       </c>
       <c r="CQ33" s="63">
-        <f>CP51*(1+$CZ$53)</f>
-        <v>12072.06</v>
+        <f>CP51*($CZ$53)</f>
+        <v>3207.96</v>
       </c>
       <c r="CR33" s="63">
-        <f t="shared" ref="CR33:CZ33" si="57">CQ33*(1+$CZ$53)</f>
-        <v>17263.0458</v>
+        <f t="shared" ref="CR33:CZ33" si="73">CQ33*(1+$CZ$53)</f>
+        <v>4426.9847999999993</v>
       </c>
       <c r="CS33" s="63">
-        <f t="shared" si="57"/>
-        <v>24686.155493999999</v>
+        <f t="shared" si="73"/>
+        <v>6109.2390239999986</v>
       </c>
       <c r="CT33" s="63">
-        <f t="shared" si="57"/>
-        <v>35301.202356419999</v>
+        <f t="shared" si="73"/>
+        <v>8430.7498531199981</v>
       </c>
       <c r="CU33" s="63">
-        <f t="shared" si="57"/>
-        <v>50480.719369680599</v>
+        <f t="shared" si="73"/>
+        <v>11634.434797305596</v>
       </c>
       <c r="CV33" s="63">
-        <f t="shared" si="57"/>
-        <v>72187.428698643256</v>
+        <f t="shared" si="73"/>
+        <v>16055.520020281721</v>
       </c>
       <c r="CW33" s="63">
-        <f t="shared" si="57"/>
-        <v>103228.02303905986</v>
+        <f t="shared" si="73"/>
+        <v>22156.617627988773</v>
       </c>
       <c r="CX33" s="63">
-        <f t="shared" si="57"/>
-        <v>147616.07294585559</v>
+        <f t="shared" si="73"/>
+        <v>30576.132326624505</v>
       </c>
       <c r="CY33" s="63">
-        <f t="shared" si="57"/>
-        <v>211090.98431257348</v>
+        <f t="shared" si="73"/>
+        <v>42195.062610741814</v>
       </c>
       <c r="CZ33" s="63">
-        <f t="shared" si="57"/>
-        <v>301860.10756698006</v>
+        <f t="shared" si="73"/>
+        <v>58229.186402823696</v>
       </c>
     </row>
     <row r="34" spans="2:158">
@@ -17530,67 +17527,67 @@
         <v>41</v>
       </c>
       <c r="CA34" s="1">
-        <f>SUM(C34:F34)</f>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="CB34" s="1">
-        <f>SUM(G34:J34)</f>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="CC34" s="1">
-        <f>SUM(K34:N34)</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="CD34" s="1">
-        <f>SUM(O34:R34)</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="CE34" s="1">
-        <f>SUM(S34:V34)</f>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="CF34" s="1">
-        <f>SUM(W34:Z34)</f>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="CG34" s="1">
-        <f>SUM(AA34:AD34)</f>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="CH34" s="1">
-        <f>SUM(AE34:AH34)</f>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="CI34" s="1">
-        <f>SUM(AI34:AL34)</f>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="CJ34" s="1">
-        <f>SUM(AM34:AP34)</f>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="CK34" s="1">
-        <f>SUM(AQ34:AT34)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="CL34" s="1">
-        <f>SUM(AU34:AX34)</f>
+        <f t="shared" si="52"/>
         <v>30</v>
       </c>
       <c r="CM34" s="1">
-        <f>SUM(AY34:BB34)</f>
+        <f t="shared" si="53"/>
         <v>645</v>
       </c>
       <c r="CN34" s="1">
-        <f>SUM(BC34:BF34)</f>
+        <f t="shared" si="54"/>
         <v>-145</v>
       </c>
       <c r="CO34" s="1">
-        <f>SUM(BG34:BJ34)</f>
+        <f t="shared" si="55"/>
         <v>-61</v>
       </c>
       <c r="CP34" s="1">
-        <f>SUM(BK34:BN34)</f>
+        <f t="shared" si="56"/>
         <v>-29</v>
       </c>
       <c r="CQ34" s="35">
@@ -17703,67 +17700,67 @@
         <v>-186</v>
       </c>
       <c r="CA35" s="1">
-        <f>SUM(C35:F35)</f>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="CB35" s="1">
-        <f>SUM(G35:J35)</f>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="CC35" s="1">
-        <f>SUM(K35:N35)</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="CD35" s="1">
-        <f>SUM(O35:R35)</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="CE35" s="1">
-        <f>SUM(S35:V35)</f>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="CF35" s="1">
-        <f>SUM(W35:Z35)</f>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="CG35" s="1">
-        <f>SUM(AA35:AD35)</f>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="CH35" s="1">
-        <f>SUM(AE35:AH35)</f>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="CI35" s="1">
-        <f>SUM(AI35:AL35)</f>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="CJ35" s="1">
-        <f>SUM(AM35:AP35)</f>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="CK35" s="1">
-        <f>SUM(AQ35:AT35)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="CL35" s="1">
-        <f>SUM(AU35:AX35)</f>
+        <f t="shared" si="52"/>
         <v>-380</v>
       </c>
       <c r="CM35" s="1">
-        <f>SUM(AY35:BB35)</f>
+        <f t="shared" si="53"/>
         <v>-431</v>
       </c>
       <c r="CN35" s="1">
-        <f>SUM(BC35:BF35)</f>
+        <f t="shared" si="54"/>
         <v>-471</v>
       </c>
       <c r="CO35" s="1">
-        <f>SUM(BG35:BJ35)</f>
+        <f t="shared" si="55"/>
         <v>-575</v>
       </c>
       <c r="CP35" s="1">
-        <f>SUM(BK35:BN35)</f>
+        <f t="shared" si="56"/>
         <v>-646</v>
       </c>
       <c r="CQ35" s="63">
@@ -17771,39 +17768,39 @@
         <v>-820.17</v>
       </c>
       <c r="CR35" s="63">
-        <f t="shared" ref="CR35:CZ35" si="58">-($CP$70+$CP$72)*4.5%</f>
+        <f t="shared" ref="CR35:CZ35" si="74">-($CP$70+$CP$72)*4.5%</f>
         <v>-820.17</v>
       </c>
       <c r="CS35" s="63">
-        <f t="shared" si="58"/>
+        <f t="shared" si="74"/>
         <v>-820.17</v>
       </c>
       <c r="CT35" s="63">
-        <f t="shared" si="58"/>
+        <f t="shared" si="74"/>
         <v>-820.17</v>
       </c>
       <c r="CU35" s="63">
-        <f t="shared" si="58"/>
+        <f t="shared" si="74"/>
         <v>-820.17</v>
       </c>
       <c r="CV35" s="63">
-        <f t="shared" si="58"/>
+        <f t="shared" si="74"/>
         <v>-820.17</v>
       </c>
       <c r="CW35" s="63">
-        <f t="shared" si="58"/>
+        <f t="shared" si="74"/>
         <v>-820.17</v>
       </c>
       <c r="CX35" s="63">
-        <f t="shared" si="58"/>
+        <f t="shared" si="74"/>
         <v>-820.17</v>
       </c>
       <c r="CY35" s="63">
-        <f t="shared" si="58"/>
+        <f t="shared" si="74"/>
         <v>-820.17</v>
       </c>
       <c r="CZ35" s="63">
-        <f t="shared" si="58"/>
+        <f t="shared" si="74"/>
         <v>-820.17</v>
       </c>
     </row>
@@ -17886,67 +17883,67 @@
         <v>2</v>
       </c>
       <c r="CA36" s="1">
-        <f>SUM(C36:F36)</f>
+        <f t="shared" si="41"/>
         <v>0</v>
       </c>
       <c r="CB36" s="1">
-        <f>SUM(G36:J36)</f>
+        <f t="shared" si="42"/>
         <v>0</v>
       </c>
       <c r="CC36" s="1">
-        <f>SUM(K36:N36)</f>
+        <f t="shared" si="43"/>
         <v>0</v>
       </c>
       <c r="CD36" s="1">
-        <f>SUM(O36:R36)</f>
+        <f t="shared" si="44"/>
         <v>0</v>
       </c>
       <c r="CE36" s="1">
-        <f>SUM(S36:V36)</f>
+        <f t="shared" si="45"/>
         <v>0</v>
       </c>
       <c r="CF36" s="1">
-        <f>SUM(W36:Z36)</f>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="CG36" s="1">
-        <f>SUM(AA36:AD36)</f>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="CH36" s="1">
-        <f>SUM(AE36:AH36)</f>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="CI36" s="1">
-        <f>SUM(AI36:AL36)</f>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="CJ36" s="1">
-        <f>SUM(AM36:AP36)</f>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="CK36" s="1">
-        <f>SUM(AQ36:AT36)</f>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="CL36" s="1">
-        <f>SUM(AU36:AX36)</f>
+        <f t="shared" si="52"/>
         <v>5</v>
       </c>
       <c r="CM36" s="1">
-        <f>SUM(AY36:BB36)</f>
+        <f t="shared" si="53"/>
         <v>0</v>
       </c>
       <c r="CN36" s="1">
-        <f>SUM(BC36:BF36)</f>
+        <f t="shared" si="54"/>
         <v>23</v>
       </c>
       <c r="CO36" s="1">
-        <f>SUM(BG36:BJ36)</f>
+        <f t="shared" si="55"/>
         <v>-7</v>
       </c>
       <c r="CP36" s="1">
-        <f>SUM(BK36:BN36)</f>
+        <f t="shared" si="56"/>
         <v>20</v>
       </c>
       <c r="CQ36" s="35">
@@ -17985,259 +17982,259 @@
         <v>1496</v>
       </c>
       <c r="C37" s="1">
-        <f t="shared" ref="C37:AT37" si="59">C32+SUM(C33:C36)</f>
+        <f t="shared" ref="C37:AT37" si="75">C32+SUM(C33:C36)</f>
         <v>550</v>
       </c>
       <c r="D37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>536</v>
       </c>
       <c r="E37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>660</v>
       </c>
       <c r="F37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>472</v>
       </c>
       <c r="G37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>695</v>
       </c>
       <c r="H37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>713</v>
       </c>
       <c r="I37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>767</v>
       </c>
       <c r="J37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>582</v>
       </c>
       <c r="K37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>836</v>
       </c>
       <c r="L37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>892</v>
       </c>
       <c r="M37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>1030</v>
       </c>
       <c r="N37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>-10</v>
       </c>
       <c r="O37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>1000</v>
       </c>
       <c r="P37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>973</v>
       </c>
       <c r="Q37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>1066</v>
       </c>
       <c r="R37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>894</v>
       </c>
       <c r="S37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>1102</v>
       </c>
       <c r="T37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>1233</v>
       </c>
       <c r="U37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>1254</v>
       </c>
       <c r="V37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>911</v>
       </c>
       <c r="W37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>1281</v>
       </c>
       <c r="X37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>1373</v>
       </c>
       <c r="Y37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>1418</v>
       </c>
       <c r="Z37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>1007</v>
       </c>
       <c r="AA37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>1340</v>
       </c>
       <c r="AB37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>1241</v>
       </c>
       <c r="AC37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>1352</v>
       </c>
       <c r="AD37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>1025</v>
       </c>
       <c r="AE37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>1337</v>
       </c>
       <c r="AF37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>1365</v>
       </c>
       <c r="AG37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>1633</v>
       </c>
       <c r="AH37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>1311</v>
       </c>
       <c r="AI37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>1478</v>
       </c>
       <c r="AJ37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>1628</v>
       </c>
       <c r="AK37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>1932</v>
       </c>
       <c r="AL37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>1484</v>
       </c>
       <c r="AM37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>1803</v>
       </c>
       <c r="AN37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>1922</v>
       </c>
       <c r="AO37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>2264</v>
       </c>
       <c r="AP37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>1215</v>
       </c>
       <c r="AQ37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>2203</v>
       </c>
       <c r="AR37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>2519</v>
       </c>
       <c r="AS37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>2534</v>
       </c>
       <c r="AT37" s="1">
-        <f t="shared" si="59"/>
+        <f t="shared" si="75"/>
         <v>2475</v>
       </c>
       <c r="AU37" s="1">
-        <f t="shared" ref="AU37:BJ37" si="60">AU32+SUM(AU33:AU36)</f>
+        <f t="shared" ref="AU37:BJ37" si="76">AU32+SUM(AU33:AU36)</f>
         <v>1987</v>
       </c>
       <c r="AV37" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="76"/>
         <v>1690</v>
       </c>
       <c r="AW37" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="76"/>
         <v>1915</v>
       </c>
       <c r="AX37" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="76"/>
         <v>2168</v>
       </c>
       <c r="AY37" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="76"/>
         <v>2190</v>
       </c>
       <c r="AZ37" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="76"/>
         <v>2478</v>
       </c>
       <c r="BA37" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="76"/>
         <v>2816</v>
       </c>
       <c r="BB37" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="76"/>
         <v>2823</v>
       </c>
       <c r="BC37" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="76"/>
         <v>2773</v>
       </c>
       <c r="BD37" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="76"/>
         <v>2798</v>
       </c>
       <c r="BE37" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="76"/>
         <v>3072</v>
       </c>
       <c r="BF37" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="76"/>
         <v>3089</v>
       </c>
       <c r="BG37" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="76"/>
         <v>2853</v>
       </c>
       <c r="BH37" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="76"/>
         <v>3704</v>
       </c>
       <c r="BI37" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="76"/>
         <v>3761</v>
       </c>
       <c r="BJ37" s="1">
-        <f t="shared" si="60"/>
+        <f t="shared" si="76"/>
         <v>3321</v>
       </c>
       <c r="BK37" s="1">
-        <f t="shared" ref="BK37:BN37" si="61">BK32+SUM(BK33:BK36)</f>
+        <f t="shared" ref="BK37:BN37" si="77">BK32+SUM(BK33:BK36)</f>
         <v>3558</v>
       </c>
       <c r="BL37" s="1">
-        <f t="shared" si="61"/>
+        <f t="shared" si="77"/>
         <v>3939</v>
       </c>
       <c r="BM37" s="1">
-        <f t="shared" si="61"/>
+        <f t="shared" si="77"/>
         <v>3866</v>
       </c>
       <c r="BN37" s="1">
-        <f t="shared" si="61"/>
+        <f t="shared" si="77"/>
         <v>3891</v>
       </c>
       <c r="BO37" s="1">
@@ -18253,108 +18250,108 @@
         <v>4999</v>
       </c>
       <c r="CA37" s="1">
-        <f>SUM(C37:F37)</f>
+        <f t="shared" si="41"/>
         <v>2218</v>
       </c>
       <c r="CB37" s="1">
-        <f>SUM(G37:J37)</f>
+        <f t="shared" si="42"/>
         <v>2757</v>
       </c>
       <c r="CC37" s="1">
-        <f>SUM(K37:N37)</f>
+        <f t="shared" si="43"/>
         <v>2748</v>
       </c>
       <c r="CD37" s="1">
-        <f>SUM(O37:R37)</f>
+        <f t="shared" si="44"/>
         <v>3933</v>
       </c>
       <c r="CE37" s="1">
-        <f>SUM(S37:V37)</f>
+        <f t="shared" si="45"/>
         <v>4500</v>
       </c>
       <c r="CF37" s="1">
-        <f>SUM(W37:Z37)</f>
+        <f t="shared" si="46"/>
         <v>5079</v>
       </c>
       <c r="CG37" s="1">
-        <f>SUM(AA37:AD37)</f>
+        <f t="shared" si="47"/>
         <v>4958</v>
       </c>
       <c r="CH37" s="1">
-        <f>SUM(AE37:AH37)</f>
+        <f t="shared" si="48"/>
         <v>5646</v>
       </c>
       <c r="CI37" s="1">
-        <f>SUM(AI37:AL37)</f>
+        <f t="shared" si="49"/>
         <v>6522</v>
       </c>
       <c r="CJ37" s="1">
-        <f>SUM(AM37:AP37)</f>
+        <f t="shared" si="50"/>
         <v>7204</v>
       </c>
       <c r="CK37" s="1">
-        <f>SUM(AQ37:AT37)</f>
+        <f t="shared" si="51"/>
         <v>9731</v>
       </c>
       <c r="CL37" s="1">
-        <f>SUM(AU37:AX37)</f>
+        <f t="shared" si="52"/>
         <v>7760</v>
       </c>
       <c r="CM37" s="1">
-        <f>SUM(AY37:BB37)</f>
+        <f t="shared" si="53"/>
         <v>10307</v>
       </c>
       <c r="CN37" s="1">
-        <f>SUM(BC37:BF37)</f>
+        <f t="shared" si="54"/>
         <v>11732</v>
       </c>
       <c r="CO37" s="1">
-        <f>SUM(BG37:BJ37)</f>
+        <f t="shared" si="55"/>
         <v>13639</v>
       </c>
       <c r="CP37" s="1">
-        <f>SUM(BK37:BN37)</f>
+        <f t="shared" si="56"/>
         <v>15254</v>
       </c>
       <c r="CQ37" s="63">
         <f>CQ32+SUM(CQ33:CQ36)</f>
-        <v>29862.144990000001</v>
+        <v>20998.044990000002</v>
       </c>
       <c r="CR37" s="63">
-        <f t="shared" ref="CR37:CZ37" si="62">CR32+SUM(CR33:CR36)</f>
-        <v>37690.153499474996</v>
+        <f t="shared" ref="CR37:CZ37" si="78">CR32+SUM(CR33:CR36)</f>
+        <v>24854.092499474998</v>
       </c>
       <c r="CS37" s="63">
-        <f t="shared" si="62"/>
-        <v>48510.015934477873</v>
+        <f t="shared" si="78"/>
+        <v>29933.099464477869</v>
       </c>
       <c r="CT37" s="63">
-        <f t="shared" si="62"/>
-        <v>62220.841995733586</v>
+        <f t="shared" si="78"/>
+        <v>35350.389492433591</v>
       </c>
       <c r="CU37" s="63">
-        <f t="shared" si="62"/>
-        <v>81076.059580642614</v>
+        <f t="shared" si="78"/>
+        <v>42229.775008267607</v>
       </c>
       <c r="CV37" s="63">
-        <f t="shared" si="62"/>
-        <v>105735.24017407512</v>
+        <f t="shared" si="78"/>
+        <v>49603.331495713588</v>
       </c>
       <c r="CW37" s="63">
-        <f t="shared" si="62"/>
-        <v>139317.32123693835</v>
+        <f t="shared" si="78"/>
+        <v>58245.915825867283</v>
       </c>
       <c r="CX37" s="63">
-        <f t="shared" si="62"/>
-        <v>185858.78790927242</v>
+        <f t="shared" si="78"/>
+        <v>68818.847290041347</v>
       </c>
       <c r="CY37" s="63">
-        <f t="shared" si="62"/>
-        <v>251452.07186239498</v>
+        <f t="shared" si="78"/>
+        <v>82556.150160563353</v>
       </c>
       <c r="CZ37" s="63">
-        <f t="shared" si="62"/>
-        <v>344249.97698702791</v>
+        <f t="shared" si="78"/>
+        <v>100619.05582287154</v>
       </c>
     </row>
     <row r="38" spans="2:158">
@@ -18568,108 +18565,108 @@
         <v>1072</v>
       </c>
       <c r="CA38" s="1">
-        <f>SUM(C38:F38)</f>
+        <f t="shared" si="41"/>
         <v>755</v>
       </c>
       <c r="CB38" s="1">
-        <f>SUM(G38:J38)</f>
+        <f t="shared" si="42"/>
         <v>910</v>
       </c>
       <c r="CC38" s="1">
-        <f>SUM(K38:N38)</f>
+        <f t="shared" si="43"/>
         <v>842</v>
       </c>
       <c r="CD38" s="1">
-        <f>SUM(O38:R38)</f>
+        <f t="shared" si="44"/>
         <v>1174</v>
       </c>
       <c r="CE38" s="1">
-        <f>SUM(S38:V38)</f>
+        <f t="shared" si="45"/>
         <v>1384</v>
       </c>
       <c r="CF38" s="1">
-        <f>SUM(W38:Z38)</f>
+        <f t="shared" si="46"/>
         <v>1462</v>
       </c>
       <c r="CG38" s="1">
-        <f>SUM(AA38:AD38)</f>
+        <f t="shared" si="47"/>
         <v>1150</v>
       </c>
       <c r="CH38" s="1">
-        <f>SUM(AE38:AH38)</f>
+        <f t="shared" si="48"/>
         <v>1587</v>
       </c>
       <c r="CI38" s="1">
-        <f>SUM(AI38:AL38)</f>
+        <f t="shared" si="49"/>
         <v>2607</v>
       </c>
       <c r="CJ38" s="1">
-        <f>SUM(AM38:AP38)</f>
+        <f t="shared" si="50"/>
         <v>1345</v>
       </c>
       <c r="CK38" s="1">
-        <f>SUM(AQ38:AT38)</f>
+        <f t="shared" si="51"/>
         <v>1613</v>
       </c>
       <c r="CL38" s="1">
-        <f>SUM(AU38:AX38)</f>
+        <f t="shared" si="52"/>
         <v>1349</v>
       </c>
       <c r="CM38" s="1">
-        <f>SUM(AY38:BB38)</f>
+        <f t="shared" si="53"/>
         <v>1620</v>
       </c>
       <c r="CN38" s="1">
-        <f>SUM(BC38:BF38)</f>
+        <f t="shared" si="54"/>
         <v>1802</v>
       </c>
       <c r="CO38" s="1">
-        <f>SUM(BG38:BJ38)</f>
+        <f t="shared" si="55"/>
         <v>2444</v>
       </c>
       <c r="CP38" s="1">
-        <f>SUM(BK38:BN38)</f>
+        <f t="shared" si="56"/>
         <v>2380</v>
       </c>
       <c r="CQ38" s="63">
         <f>CQ37*CQ48</f>
-        <v>5972.4289980000003</v>
+        <v>4199.6089980000006</v>
       </c>
       <c r="CR38" s="63">
-        <f t="shared" ref="CR38:CZ38" si="63">CR37*CR48</f>
-        <v>7538.030699895</v>
+        <f t="shared" ref="CR38:CZ38" si="79">CR37*CR48</f>
+        <v>4970.8184998950001</v>
       </c>
       <c r="CS38" s="63">
-        <f t="shared" si="63"/>
-        <v>9702.0031868955757</v>
+        <f t="shared" si="79"/>
+        <v>5986.6198928955746</v>
       </c>
       <c r="CT38" s="63">
-        <f t="shared" si="63"/>
-        <v>12444.168399146718</v>
+        <f t="shared" si="79"/>
+        <v>7070.0778984867184</v>
       </c>
       <c r="CU38" s="63">
-        <f t="shared" si="63"/>
-        <v>16215.211916128523</v>
+        <f t="shared" si="79"/>
+        <v>8445.9550016535213</v>
       </c>
       <c r="CV38" s="63">
-        <f t="shared" si="63"/>
-        <v>21147.048034815027</v>
+        <f t="shared" si="79"/>
+        <v>9920.6662991427183</v>
       </c>
       <c r="CW38" s="63">
-        <f t="shared" si="63"/>
-        <v>27863.464247387674</v>
+        <f t="shared" si="79"/>
+        <v>11649.183165173457</v>
       </c>
       <c r="CX38" s="63">
-        <f t="shared" si="63"/>
-        <v>37171.757581854486</v>
+        <f t="shared" si="79"/>
+        <v>13763.76945800827</v>
       </c>
       <c r="CY38" s="63">
-        <f t="shared" si="63"/>
-        <v>50290.414372478997</v>
+        <f t="shared" si="79"/>
+        <v>16511.230032112671</v>
       </c>
       <c r="CZ38" s="63">
-        <f t="shared" si="63"/>
-        <v>68849.995397405582</v>
+        <f t="shared" si="79"/>
+        <v>20123.811164574308</v>
       </c>
     </row>
     <row r="39" spans="2:158" s="2" customFormat="1" ht="15">
@@ -18677,259 +18674,259 @@
         <v>132</v>
       </c>
       <c r="C39" s="2">
-        <f t="shared" ref="C39:AT39" si="64">C37-C38</f>
+        <f t="shared" ref="C39:AT39" si="80">C37-C38</f>
         <v>367</v>
       </c>
       <c r="D39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>349</v>
       </c>
       <c r="E39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>439</v>
       </c>
       <c r="F39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>308</v>
       </c>
       <c r="G39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>455</v>
       </c>
       <c r="H39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>458</v>
       </c>
       <c r="I39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>519</v>
       </c>
       <c r="J39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>415</v>
       </c>
       <c r="K39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>562</v>
       </c>
       <c r="L39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>608</v>
       </c>
       <c r="M39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>716</v>
       </c>
       <c r="N39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>20</v>
       </c>
       <c r="O39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>682</v>
       </c>
       <c r="P39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>700</v>
       </c>
       <c r="Q39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>772</v>
       </c>
       <c r="R39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>605</v>
       </c>
       <c r="S39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>766</v>
       </c>
       <c r="T39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>848</v>
       </c>
       <c r="U39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>879</v>
       </c>
       <c r="V39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>623</v>
       </c>
       <c r="W39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>870</v>
       </c>
       <c r="X39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>931</v>
       </c>
       <c r="Y39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>1015</v>
       </c>
       <c r="Z39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>801</v>
       </c>
       <c r="AA39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>1020</v>
       </c>
       <c r="AB39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>921</v>
       </c>
       <c r="AC39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>977</v>
       </c>
       <c r="AD39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>890</v>
       </c>
       <c r="AE39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>959</v>
       </c>
       <c r="AF39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>983</v>
       </c>
       <c r="AG39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>1184</v>
       </c>
       <c r="AH39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>933</v>
       </c>
       <c r="AI39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>1081</v>
       </c>
       <c r="AJ39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>1177</v>
       </c>
       <c r="AK39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>1430</v>
       </c>
       <c r="AL39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>227</v>
       </c>
       <c r="AM39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>1492</v>
       </c>
       <c r="AN39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>1569</v>
       </c>
       <c r="AO39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>1899</v>
       </c>
       <c r="AP39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>899</v>
       </c>
       <c r="AQ39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>1862</v>
       </c>
       <c r="AR39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>2048</v>
       </c>
       <c r="AS39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>2108</v>
       </c>
       <c r="AT39" s="2">
-        <f t="shared" si="64"/>
+        <f t="shared" si="80"/>
         <v>2100</v>
       </c>
       <c r="AU39" s="2">
-        <f t="shared" ref="AU39:BJ39" si="65">AU37-AU38</f>
+        <f t="shared" ref="AU39:BJ39" si="81">AU37-AU38</f>
         <v>1693</v>
       </c>
       <c r="AV39" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="81"/>
         <v>1420</v>
       </c>
       <c r="AW39" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="81"/>
         <v>1513</v>
       </c>
       <c r="AX39" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="81"/>
         <v>1785</v>
       </c>
       <c r="AY39" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="81"/>
         <v>1828</v>
       </c>
       <c r="AZ39" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="81"/>
         <v>2066</v>
       </c>
       <c r="BA39" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="81"/>
         <v>2414</v>
       </c>
       <c r="BB39" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="81"/>
         <v>2379</v>
       </c>
       <c r="BC39" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="81"/>
         <v>2631</v>
       </c>
       <c r="BD39" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="81"/>
         <v>2275</v>
       </c>
       <c r="BE39" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="81"/>
         <v>2499</v>
       </c>
       <c r="BF39" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="81"/>
         <v>2525</v>
       </c>
       <c r="BG39" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="81"/>
         <v>2361</v>
       </c>
       <c r="BH39" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="81"/>
         <v>2845</v>
       </c>
       <c r="BI39" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="81"/>
         <v>3198</v>
       </c>
       <c r="BJ39" s="2">
-        <f t="shared" si="65"/>
+        <f t="shared" si="81"/>
         <v>2791</v>
       </c>
       <c r="BK39" s="2">
-        <f t="shared" ref="BK39:BN39" si="66">BK37-BK38</f>
+        <f t="shared" ref="BK39:BN39" si="82">BK37-BK38</f>
         <v>3011</v>
       </c>
       <c r="BL39" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="82"/>
         <v>3258</v>
       </c>
       <c r="BM39" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="82"/>
         <v>3263</v>
       </c>
       <c r="BN39" s="2">
-        <f t="shared" si="66"/>
+        <f t="shared" si="82"/>
         <v>3342</v>
       </c>
       <c r="BO39" s="2">
@@ -18950,308 +18947,308 @@
       <c r="BU39" s="34"/>
       <c r="BV39" s="34"/>
       <c r="CA39" s="2">
-        <f>SUM(C39:F39)</f>
+        <f t="shared" si="41"/>
         <v>1463</v>
       </c>
       <c r="CB39" s="2">
-        <f>SUM(G39:J39)</f>
+        <f t="shared" si="42"/>
         <v>1847</v>
       </c>
       <c r="CC39" s="2">
-        <f>SUM(K39:N39)</f>
+        <f t="shared" si="43"/>
         <v>1906</v>
       </c>
       <c r="CD39" s="2">
-        <f>SUM(O39:R39)</f>
+        <f t="shared" si="44"/>
         <v>2759</v>
       </c>
       <c r="CE39" s="2">
-        <f>SUM(S39:V39)</f>
+        <f t="shared" si="45"/>
         <v>3116</v>
       </c>
       <c r="CF39" s="2">
-        <f>SUM(W39:Z39)</f>
+        <f t="shared" si="46"/>
         <v>3617</v>
       </c>
       <c r="CG39" s="2">
-        <f>SUM(AA39:AD39)</f>
+        <f t="shared" si="47"/>
         <v>3808</v>
       </c>
       <c r="CH39" s="2">
-        <f>SUM(AE39:AH39)</f>
+        <f t="shared" si="48"/>
         <v>4059</v>
       </c>
       <c r="CI39" s="2">
-        <f>SUM(AI39:AL39)</f>
+        <f t="shared" si="49"/>
         <v>3915</v>
       </c>
       <c r="CJ39" s="2">
-        <f>SUM(AM39:AP39)</f>
+        <f t="shared" si="50"/>
         <v>5859</v>
       </c>
       <c r="CK39" s="2">
-        <f>SUM(AQ39:AT39)</f>
+        <f t="shared" si="51"/>
         <v>8118</v>
       </c>
       <c r="CL39" s="2">
-        <f>SUM(AU39:AX39)</f>
+        <f t="shared" si="52"/>
         <v>6411</v>
       </c>
       <c r="CM39" s="2">
-        <f>SUM(AY39:BB39)</f>
+        <f t="shared" si="53"/>
         <v>8687</v>
       </c>
       <c r="CN39" s="2">
-        <f>SUM(BC39:BF39)</f>
+        <f t="shared" si="54"/>
         <v>9930</v>
       </c>
       <c r="CO39" s="2">
-        <f>SUM(BG39:BJ39)</f>
+        <f t="shared" si="55"/>
         <v>11195</v>
       </c>
       <c r="CP39" s="2">
-        <f>SUM(BK39:BN39)</f>
+        <f t="shared" si="56"/>
         <v>12874</v>
       </c>
       <c r="CQ39" s="67">
         <f>CQ37-CQ38</f>
-        <v>23889.715992000001</v>
+        <v>16798.435992000002</v>
       </c>
       <c r="CR39" s="67">
-        <f t="shared" ref="CR39:CZ39" si="67">CR37-CR38</f>
-        <v>30152.122799579996</v>
+        <f t="shared" ref="CR39:CZ39" si="83">CR37-CR38</f>
+        <v>19883.27399958</v>
       </c>
       <c r="CS39" s="67">
-        <f t="shared" si="67"/>
-        <v>38808.012747582296</v>
+        <f t="shared" si="83"/>
+        <v>23946.479571582295</v>
       </c>
       <c r="CT39" s="67">
-        <f t="shared" si="67"/>
-        <v>49776.673596586872</v>
+        <f t="shared" si="83"/>
+        <v>28280.311593946873</v>
       </c>
       <c r="CU39" s="67">
-        <f t="shared" si="67"/>
-        <v>64860.847664514091</v>
+        <f t="shared" si="83"/>
+        <v>33783.820006614085</v>
       </c>
       <c r="CV39" s="67">
-        <f t="shared" si="67"/>
-        <v>84588.192139260093</v>
+        <f t="shared" si="83"/>
+        <v>39682.665196570873</v>
       </c>
       <c r="CW39" s="67">
-        <f t="shared" si="67"/>
-        <v>111453.85698955068</v>
+        <f t="shared" si="83"/>
+        <v>46596.73266069383</v>
       </c>
       <c r="CX39" s="67">
-        <f t="shared" si="67"/>
-        <v>148687.03032741795</v>
+        <f t="shared" si="83"/>
+        <v>55055.077832033079</v>
       </c>
       <c r="CY39" s="67">
-        <f t="shared" si="67"/>
-        <v>201161.65748991599</v>
+        <f t="shared" si="83"/>
+        <v>66044.920128450685</v>
       </c>
       <c r="CZ39" s="67">
-        <f t="shared" si="67"/>
-        <v>275399.98158962233</v>
+        <f t="shared" si="83"/>
+        <v>80495.244658297233</v>
       </c>
       <c r="DA39" s="67">
         <f>CZ39*(1+$CZ$54)</f>
-        <v>282973.48108333698</v>
+        <v>82708.863886400417</v>
       </c>
       <c r="DB39" s="67">
-        <f t="shared" ref="DB39:EX39" si="68">DA39*(1+$CZ$54)</f>
-        <v>290755.25181312877</v>
+        <f t="shared" ref="DB39:EX39" si="84">DA39*(1+$CZ$54)</f>
+        <v>84983.357643276438</v>
       </c>
       <c r="DC39" s="67">
-        <f t="shared" si="68"/>
-        <v>298751.02123798983</v>
+        <f t="shared" si="84"/>
+        <v>87320.39997846655</v>
       </c>
       <c r="DD39" s="67">
-        <f t="shared" si="68"/>
-        <v>306966.67432203458</v>
+        <f t="shared" si="84"/>
+        <v>89721.710977874391</v>
       </c>
       <c r="DE39" s="67">
-        <f t="shared" si="68"/>
-        <v>315408.25786589057</v>
+        <f t="shared" si="84"/>
+        <v>92189.058029765947</v>
       </c>
       <c r="DF39" s="67">
-        <f t="shared" si="68"/>
-        <v>324081.98495720257</v>
+        <f t="shared" si="84"/>
+        <v>94724.257125584525</v>
       </c>
       <c r="DG39" s="67">
-        <f t="shared" si="68"/>
-        <v>332994.23954352568</v>
+        <f t="shared" si="84"/>
+        <v>97329.174196538108</v>
       </c>
       <c r="DH39" s="67">
-        <f t="shared" si="68"/>
-        <v>342151.58113097266</v>
+        <f t="shared" si="84"/>
+        <v>100005.72648694292</v>
       </c>
       <c r="DI39" s="67">
-        <f t="shared" si="68"/>
-        <v>351560.7496120744</v>
+        <f t="shared" si="84"/>
+        <v>102755.88396533387</v>
       </c>
       <c r="DJ39" s="67">
-        <f t="shared" si="68"/>
-        <v>361228.67022640648</v>
+        <f t="shared" si="84"/>
+        <v>105581.67077438056</v>
       </c>
       <c r="DK39" s="67">
-        <f t="shared" si="68"/>
-        <v>371162.4586576327</v>
+        <f t="shared" si="84"/>
+        <v>108485.16672067603</v>
       </c>
       <c r="DL39" s="67">
-        <f t="shared" si="68"/>
-        <v>381369.42627071764</v>
+        <f t="shared" si="84"/>
+        <v>111468.50880549462</v>
       </c>
       <c r="DM39" s="67">
-        <f t="shared" si="68"/>
-        <v>391857.08549316239</v>
+        <f t="shared" si="84"/>
+        <v>114533.89279764573</v>
       </c>
       <c r="DN39" s="67">
-        <f t="shared" si="68"/>
-        <v>402633.15534422436</v>
+        <f t="shared" si="84"/>
+        <v>117683.574849581</v>
       </c>
       <c r="DO39" s="67">
-        <f t="shared" si="68"/>
-        <v>413705.56711619056</v>
+        <f t="shared" si="84"/>
+        <v>120919.87315794449</v>
       </c>
       <c r="DP39" s="67">
-        <f t="shared" si="68"/>
-        <v>425082.47021188581</v>
+        <f t="shared" si="84"/>
+        <v>124245.16966978797</v>
       </c>
       <c r="DQ39" s="67">
-        <f t="shared" si="68"/>
-        <v>436772.23814271268</v>
+        <f t="shared" si="84"/>
+        <v>127661.91183570714</v>
       </c>
       <c r="DR39" s="67">
-        <f t="shared" si="68"/>
-        <v>448783.47469163733</v>
+        <f t="shared" si="84"/>
+        <v>131172.6144111891</v>
       </c>
       <c r="DS39" s="67">
-        <f t="shared" si="68"/>
-        <v>461125.02024565736</v>
+        <f t="shared" si="84"/>
+        <v>134779.86130749682</v>
       </c>
       <c r="DT39" s="67">
-        <f t="shared" si="68"/>
-        <v>473805.958302413</v>
+        <f t="shared" si="84"/>
+        <v>138486.307493453</v>
       </c>
       <c r="DU39" s="67">
-        <f t="shared" si="68"/>
-        <v>486835.62215572939</v>
+        <f t="shared" si="84"/>
+        <v>142294.68094952297</v>
       </c>
       <c r="DV39" s="67">
-        <f t="shared" si="68"/>
-        <v>500223.60176501196</v>
+        <f t="shared" si="84"/>
+        <v>146207.78467563487</v>
       </c>
       <c r="DW39" s="67">
-        <f t="shared" si="68"/>
-        <v>513979.75081354985</v>
+        <f t="shared" si="84"/>
+        <v>150228.49875421484</v>
       </c>
       <c r="DX39" s="67">
-        <f t="shared" si="68"/>
-        <v>528114.19396092254</v>
+        <f t="shared" si="84"/>
+        <v>154359.78246995577</v>
       </c>
       <c r="DY39" s="67">
-        <f t="shared" si="68"/>
-        <v>542637.33429484791</v>
+        <f t="shared" si="84"/>
+        <v>158604.67648787957</v>
       </c>
       <c r="DZ39" s="67">
-        <f t="shared" si="68"/>
-        <v>557559.86098795629</v>
+        <f t="shared" si="84"/>
+        <v>162966.30509129626</v>
       </c>
       <c r="EA39" s="67">
-        <f t="shared" si="68"/>
-        <v>572892.75716512511</v>
+        <f t="shared" si="84"/>
+        <v>167447.87848130692</v>
       </c>
       <c r="EB39" s="67">
-        <f t="shared" si="68"/>
-        <v>588647.3079871661</v>
+        <f t="shared" si="84"/>
+        <v>172052.69513954286</v>
       </c>
       <c r="EC39" s="67">
-        <f t="shared" si="68"/>
-        <v>604835.10895681323</v>
+        <f t="shared" si="84"/>
+        <v>176784.1442558803</v>
       </c>
       <c r="ED39" s="67">
-        <f t="shared" si="68"/>
-        <v>621468.07445312559</v>
+        <f t="shared" si="84"/>
+        <v>181645.70822291702</v>
       </c>
       <c r="EE39" s="67">
-        <f t="shared" si="68"/>
-        <v>638558.44650058658</v>
+        <f t="shared" si="84"/>
+        <v>186640.96519904726</v>
       </c>
       <c r="EF39" s="67">
-        <f t="shared" si="68"/>
-        <v>656118.80377935281</v>
+        <f t="shared" si="84"/>
+        <v>191773.59174202109</v>
       </c>
       <c r="EG39" s="67">
-        <f t="shared" si="68"/>
-        <v>674162.07088328502</v>
+        <f t="shared" si="84"/>
+        <v>197047.3655149267</v>
       </c>
       <c r="EH39" s="67">
-        <f t="shared" si="68"/>
-        <v>692701.52783257538</v>
+        <f t="shared" si="84"/>
+        <v>202466.16806658721</v>
       </c>
       <c r="EI39" s="67">
-        <f t="shared" si="68"/>
-        <v>711750.8198479712</v>
+        <f t="shared" si="84"/>
+        <v>208033.98768841839</v>
       </c>
       <c r="EJ39" s="67">
-        <f t="shared" si="68"/>
-        <v>731323.96739379049</v>
+        <f t="shared" si="84"/>
+        <v>213754.92234984992</v>
       </c>
       <c r="EK39" s="67">
-        <f t="shared" si="68"/>
-        <v>751435.37649711978</v>
+        <f t="shared" si="84"/>
+        <v>219633.18271447081</v>
       </c>
       <c r="EL39" s="67">
-        <f t="shared" si="68"/>
-        <v>772099.84935079061</v>
+        <f t="shared" si="84"/>
+        <v>225673.09523911876</v>
       </c>
       <c r="EM39" s="67">
-        <f t="shared" si="68"/>
-        <v>793332.59520793741</v>
+        <f t="shared" si="84"/>
+        <v>231879.10535819453</v>
       </c>
       <c r="EN39" s="67">
-        <f t="shared" si="68"/>
-        <v>815149.24157615576</v>
+        <f t="shared" si="84"/>
+        <v>238255.7807555449</v>
       </c>
       <c r="EO39" s="67">
-        <f t="shared" si="68"/>
-        <v>837565.8457195001</v>
+        <f t="shared" si="84"/>
+        <v>244807.81472632239</v>
       </c>
       <c r="EP39" s="67">
-        <f t="shared" si="68"/>
-        <v>860598.90647678636</v>
+        <f t="shared" si="84"/>
+        <v>251540.02963129629</v>
       </c>
       <c r="EQ39" s="67">
-        <f t="shared" si="68"/>
-        <v>884265.37640489801</v>
+        <f t="shared" si="84"/>
+        <v>258457.38044615695</v>
       </c>
       <c r="ER39" s="67">
-        <f t="shared" si="68"/>
-        <v>908582.6742560328</v>
+        <f t="shared" si="84"/>
+        <v>265564.95840842626</v>
       </c>
       <c r="ES39" s="67">
-        <f t="shared" si="68"/>
-        <v>933568.69779807376</v>
+        <f t="shared" si="84"/>
+        <v>272867.99476465798</v>
       </c>
       <c r="ET39" s="67">
-        <f t="shared" si="68"/>
-        <v>959241.83698752092</v>
+        <f t="shared" si="84"/>
+        <v>280371.8646206861</v>
       </c>
       <c r="EU39" s="67">
-        <f t="shared" si="68"/>
-        <v>985620.98750467785</v>
+        <f t="shared" si="84"/>
+        <v>288082.090897755</v>
       </c>
       <c r="EV39" s="67">
-        <f t="shared" si="68"/>
-        <v>1012725.5646610566</v>
+        <f t="shared" si="84"/>
+        <v>296004.3483974433</v>
       </c>
       <c r="EW39" s="67">
-        <f t="shared" si="68"/>
-        <v>1040575.5176892357</v>
+        <f t="shared" si="84"/>
+        <v>304144.467978373</v>
       </c>
       <c r="EX39" s="67">
-        <f t="shared" si="68"/>
-        <v>1069191.3444256899</v>
+        <f t="shared" si="84"/>
+        <v>312508.44084777829</v>
       </c>
       <c r="EY39" s="34"/>
       <c r="EZ39" s="34"/>
@@ -19533,259 +19530,259 @@
         <v>1503</v>
       </c>
       <c r="C41" s="39">
-        <f t="shared" ref="C41:AT41" si="69">C39/C40</f>
+        <f t="shared" ref="C41:AT41" si="85">C39/C40</f>
         <v>0.28230769230769232</v>
       </c>
       <c r="D41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0.26846153846153847</v>
       </c>
       <c r="E41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0.33769230769230768</v>
       </c>
       <c r="F41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0.23692307692307693</v>
       </c>
       <c r="G41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0.35</v>
       </c>
       <c r="H41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0.34961832061068704</v>
       </c>
       <c r="I41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0.39618320610687024</v>
       </c>
       <c r="J41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0.31679389312977096</v>
       </c>
       <c r="K41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0.43230769230769228</v>
       </c>
       <c r="L41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0.47874015748031495</v>
       </c>
       <c r="M41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0.56377952755905514</v>
       </c>
       <c r="N41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>1.5637216575449569E-2</v>
       </c>
       <c r="O41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0.53700787401574801</v>
       </c>
       <c r="P41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0.55555555555555558</v>
       </c>
       <c r="Q41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0.61760000000000004</v>
       </c>
       <c r="R41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0.48284118116520353</v>
       </c>
       <c r="S41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0.6247960848287113</v>
       </c>
       <c r="T41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0.69851729818780894</v>
       </c>
       <c r="U41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0.72946058091286303</v>
       </c>
       <c r="V41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0.51445086705202314</v>
       </c>
       <c r="W41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0.73417721518987344</v>
       </c>
       <c r="X41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0.79914163090128754</v>
       </c>
       <c r="Y41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0.87726879861711327</v>
       </c>
       <c r="Z41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0.68755364806866948</v>
       </c>
       <c r="AA41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0.88850174216027877</v>
       </c>
       <c r="AB41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0.80931458699472758</v>
       </c>
       <c r="AC41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0.86460176991150439</v>
       </c>
       <c r="AD41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0.78483245149911818</v>
       </c>
       <c r="AE41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0.8647430117222723</v>
       </c>
       <c r="AF41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0.89526411657559202</v>
       </c>
       <c r="AG41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>1.0802919708029197</v>
       </c>
       <c r="AH41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0.84972677595628421</v>
       </c>
       <c r="AI41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>1.0027829313543599</v>
       </c>
       <c r="AJ41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="AK41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>1.3452492944496708</v>
       </c>
       <c r="AL41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0.21274601686972822</v>
       </c>
       <c r="AM41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>1.4196003805899144</v>
       </c>
       <c r="AN41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>1.50431447746884</v>
       </c>
       <c r="AO41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>1.8312439729990357</v>
       </c>
       <c r="AP41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>0.86359269932756966</v>
       </c>
       <c r="AQ41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>1.8148148148148149</v>
       </c>
       <c r="AR41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>2.0078431372549019</v>
       </c>
       <c r="AS41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>2.0809476801579465</v>
       </c>
       <c r="AT41" s="39">
-        <f t="shared" si="69"/>
+        <f t="shared" si="85"/>
         <v>2.0648967551622417</v>
       </c>
       <c r="AU41" s="39">
-        <f t="shared" ref="AU41" si="70">AU39/AU40</f>
+        <f t="shared" ref="AU41" si="86">AU39/AU40</f>
         <v>1.6845771144278607</v>
       </c>
       <c r="AV41" s="39">
-        <f t="shared" ref="AV41" si="71">AV39/AV40</f>
+        <f t="shared" ref="AV41" si="87">AV39/AV40</f>
         <v>1.4143426294820718</v>
       </c>
       <c r="AW41" s="39">
-        <f t="shared" ref="AW41" si="72">AW39/AW40</f>
+        <f t="shared" ref="AW41" si="88">AW39/AW40</f>
         <v>1.5114885114885115</v>
       </c>
       <c r="AX41" s="39">
-        <f t="shared" ref="AX41" si="73">AX39/AX40</f>
+        <f t="shared" ref="AX41" si="89">AX39/AX40</f>
         <v>1.7814371257485031</v>
       </c>
       <c r="AY41" s="39">
-        <f t="shared" ref="AY41:BN41" si="74">AY39/AY40</f>
+        <f t="shared" ref="AY41:BN41" si="90">AY39/AY40</f>
         <v>1.8390342052313884</v>
       </c>
       <c r="AZ41" s="39">
-        <f t="shared" si="74"/>
+        <f t="shared" si="90"/>
         <v>2.0868686868686868</v>
       </c>
       <c r="BA41" s="39">
-        <f t="shared" si="74"/>
+        <f t="shared" si="90"/>
         <v>2.4482758620689653</v>
       </c>
       <c r="BB41" s="39">
-        <f t="shared" si="74"/>
+        <f t="shared" si="90"/>
         <v>2.4078947368421053</v>
       </c>
       <c r="BC41" s="39">
-        <f t="shared" si="74"/>
+        <f t="shared" si="90"/>
         <v>2.6929375639713409</v>
       </c>
       <c r="BD41" s="39">
-        <f t="shared" si="74"/>
+        <f t="shared" si="90"/>
         <v>2.3429454170957777</v>
       </c>
       <c r="BE41" s="39">
-        <f t="shared" si="74"/>
+        <f t="shared" si="90"/>
         <v>2.5896373056994819</v>
       </c>
       <c r="BF41" s="39">
-        <f t="shared" si="74"/>
+        <f t="shared" si="90"/>
         <v>2.6084710743801653</v>
       </c>
       <c r="BG41" s="39">
-        <f t="shared" si="74"/>
+        <f t="shared" si="90"/>
         <v>2.4774396642182581</v>
       </c>
       <c r="BH41" s="39">
-        <f t="shared" si="74"/>
+        <f t="shared" si="90"/>
         <v>3.007399577167019</v>
       </c>
       <c r="BI41" s="39">
-        <f t="shared" si="74"/>
+        <f t="shared" si="90"/>
         <v>3.3985122210414453</v>
       </c>
       <c r="BJ41" s="39">
-        <f t="shared" si="74"/>
+        <f t="shared" si="90"/>
         <v>2.9565677966101696</v>
       </c>
       <c r="BK41" s="39">
-        <f t="shared" si="74"/>
+        <f t="shared" si="90"/>
         <v>3.227224008574491</v>
       </c>
       <c r="BL41" s="39">
-        <f t="shared" si="74"/>
+        <f t="shared" si="90"/>
         <v>3.5069967707212055</v>
       </c>
       <c r="BM41" s="39">
-        <f t="shared" si="74"/>
+        <f t="shared" si="90"/>
         <v>3.535211267605634</v>
       </c>
       <c r="BN41" s="39">
-        <f t="shared" si="74"/>
+        <f t="shared" si="90"/>
         <v>3.6129729729729729</v>
       </c>
       <c r="BO41" s="39">
@@ -19870,83 +19867,83 @@
         <v>1498</v>
       </c>
       <c r="AU43" s="53">
-        <f t="shared" ref="AU43:BN43" si="75">AU27/AU26</f>
+        <f t="shared" ref="AU43:BN43" si="91">AU27/AU26</f>
         <v>0.37266151159890248</v>
       </c>
       <c r="AV43" s="53">
-        <f t="shared" si="75"/>
+        <f t="shared" si="91"/>
         <v>0.41019490254872565</v>
       </c>
       <c r="AW43" s="53">
-        <f t="shared" si="75"/>
+        <f t="shared" si="91"/>
         <v>0.3708626531144123</v>
       </c>
       <c r="AX43" s="53">
-        <f t="shared" si="75"/>
+        <f t="shared" si="91"/>
         <v>0.39441747572815533</v>
       </c>
       <c r="AY43" s="53">
-        <f t="shared" si="75"/>
+        <f t="shared" si="91"/>
         <v>0.4033694344163658</v>
       </c>
       <c r="AZ43" s="53">
-        <f t="shared" si="75"/>
+        <f t="shared" si="91"/>
         <v>0.37941696113074203</v>
       </c>
       <c r="BA43" s="53">
-        <f t="shared" si="75"/>
+        <f t="shared" si="91"/>
         <v>0.36730190571715143</v>
       </c>
       <c r="BB43" s="53">
-        <f t="shared" si="75"/>
+        <f t="shared" si="91"/>
         <v>0.35697852760736198</v>
       </c>
       <c r="BC43" s="53">
-        <f t="shared" si="75"/>
+        <f t="shared" si="91"/>
         <v>0.35688020127733694</v>
       </c>
       <c r="BD43" s="53">
-        <f t="shared" si="75"/>
+        <f t="shared" si="91"/>
         <v>0.35419319628888485</v>
       </c>
       <c r="BE43" s="53">
-        <f t="shared" si="75"/>
+        <f t="shared" si="91"/>
         <v>0.35945100764419735</v>
       </c>
       <c r="BF43" s="53">
-        <f t="shared" si="75"/>
+        <f t="shared" si="91"/>
         <v>0.38129620079078563</v>
       </c>
       <c r="BG43" s="53">
-        <f t="shared" si="75"/>
+        <f t="shared" si="91"/>
         <v>0.35542797494780792</v>
       </c>
       <c r="BH43" s="53">
-        <f t="shared" si="75"/>
+        <f t="shared" si="91"/>
         <v>0.35093316318392087</v>
       </c>
       <c r="BI43" s="53">
-        <f t="shared" si="75"/>
+        <f t="shared" si="91"/>
         <v>0.3497627429970917</v>
       </c>
       <c r="BJ43" s="53">
-        <f t="shared" si="75"/>
+        <f t="shared" si="91"/>
         <v>0.36637141111789862</v>
       </c>
       <c r="BK43" s="53">
-        <f t="shared" si="75"/>
+        <f t="shared" si="91"/>
         <v>0.36011342155009451</v>
       </c>
       <c r="BL43" s="53">
-        <f t="shared" si="75"/>
+        <f t="shared" si="91"/>
         <v>0.34736388449935351</v>
       </c>
       <c r="BM43" s="53">
-        <f t="shared" si="75"/>
+        <f t="shared" si="91"/>
         <v>0.37237074229881939</v>
       </c>
       <c r="BN43" s="53">
-        <f t="shared" si="75"/>
+        <f t="shared" si="91"/>
         <v>0.36653758846307916</v>
       </c>
       <c r="BO43" s="53">
@@ -19962,67 +19959,67 @@
         <v>0.3398046965821902</v>
       </c>
       <c r="CA43" s="53">
-        <f t="shared" ref="CA43:CP43" si="76">CA27/CA26</f>
+        <f t="shared" ref="CA43:CP43" si="92">CA27/CA26</f>
         <v>0.38085899195920769</v>
       </c>
       <c r="CB43" s="53">
-        <f t="shared" si="76"/>
+        <f t="shared" si="92"/>
         <v>0.33525907203466332</v>
       </c>
       <c r="CC43" s="53">
-        <f t="shared" si="76"/>
+        <f t="shared" si="92"/>
         <v>0.32707774798927614</v>
       </c>
       <c r="CD43" s="53">
-        <f t="shared" si="76"/>
+        <f t="shared" si="92"/>
         <v>0.32864294412122852</v>
       </c>
       <c r="CE43" s="53">
-        <f t="shared" si="76"/>
+        <f t="shared" si="92"/>
         <v>0.31460538979788261</v>
       </c>
       <c r="CF43" s="53">
-        <f t="shared" si="76"/>
+        <f t="shared" si="92"/>
         <v>0.33386293824806695</v>
       </c>
       <c r="CG43" s="53">
-        <f t="shared" si="76"/>
+        <f t="shared" si="92"/>
         <v>0.34560877211130653</v>
       </c>
       <c r="CH43" s="53">
-        <f t="shared" si="76"/>
+        <f t="shared" si="92"/>
         <v>0.35514105419450631</v>
       </c>
       <c r="CI43" s="53">
-        <f t="shared" si="76"/>
+        <f t="shared" si="92"/>
         <v>0.37232935904617109</v>
       </c>
       <c r="CJ43" s="53">
-        <f t="shared" si="76"/>
+        <f t="shared" si="92"/>
         <v>0.34608695652173915</v>
       </c>
       <c r="CK43" s="53">
-        <f t="shared" si="76"/>
+        <f t="shared" si="92"/>
         <v>0.34134928626428951</v>
       </c>
       <c r="CL43" s="53">
-        <f t="shared" si="76"/>
+        <f t="shared" si="92"/>
         <v>0.38624926475393767</v>
       </c>
       <c r="CM43" s="53">
-        <f t="shared" si="76"/>
+        <f t="shared" si="92"/>
         <v>0.37529125185342088</v>
       </c>
       <c r="CN43" s="53">
-        <f t="shared" si="76"/>
+        <f t="shared" si="92"/>
         <v>0.36326842649637991</v>
       </c>
       <c r="CO43" s="53">
-        <f t="shared" si="76"/>
+        <f t="shared" si="92"/>
         <v>0.35568571200892501</v>
       </c>
       <c r="CP43" s="53">
-        <f t="shared" si="76"/>
+        <f t="shared" si="92"/>
         <v>0.36187737423225763</v>
       </c>
       <c r="CQ43" s="68">
@@ -20061,83 +20058,83 @@
         <v>1499</v>
       </c>
       <c r="AU44" s="53">
-        <f t="shared" ref="AU44:BN44" si="77">AU28/AU26</f>
+        <f t="shared" ref="AU44:BN44" si="93">AU28/AU26</f>
         <v>3.8413569468695438E-2</v>
       </c>
       <c r="AV44" s="53">
-        <f t="shared" si="77"/>
+        <f t="shared" si="93"/>
         <v>2.7886056971514243E-2</v>
       </c>
       <c r="AW44" s="53">
-        <f t="shared" si="77"/>
+        <f t="shared" si="93"/>
         <v>4.3784206411258797E-2</v>
       </c>
       <c r="AX44" s="53">
-        <f t="shared" si="77"/>
+        <f t="shared" si="93"/>
         <v>5.8737864077669906E-2</v>
       </c>
       <c r="AY44" s="53">
-        <f t="shared" si="77"/>
+        <f t="shared" si="93"/>
         <v>2.8640192539109505E-2</v>
       </c>
       <c r="AZ44" s="53">
-        <f t="shared" si="77"/>
+        <f t="shared" si="93"/>
         <v>4.7703180212014133E-2</v>
       </c>
       <c r="BA44" s="53">
-        <f t="shared" si="77"/>
+        <f t="shared" si="93"/>
         <v>4.4533600802407224E-2</v>
       </c>
       <c r="BB44" s="53">
-        <f t="shared" si="77"/>
+        <f t="shared" si="93"/>
         <v>6.4800613496932516E-2</v>
       </c>
       <c r="BC44" s="53">
-        <f t="shared" si="77"/>
+        <f t="shared" si="93"/>
         <v>3.5029998064640994E-2</v>
       </c>
       <c r="BD44" s="53">
-        <f t="shared" si="77"/>
+        <f t="shared" si="93"/>
         <v>3.8202655994178644E-2</v>
       </c>
       <c r="BE44" s="53">
-        <f t="shared" si="77"/>
+        <f t="shared" si="93"/>
         <v>3.1619179986101462E-2</v>
       </c>
       <c r="BF44" s="53">
-        <f t="shared" si="77"/>
+        <f t="shared" si="93"/>
         <v>3.7132542547705004E-2</v>
       </c>
       <c r="BG44" s="53">
-        <f t="shared" si="77"/>
+        <f t="shared" si="93"/>
         <v>2.9053583855254E-2</v>
       </c>
       <c r="BH44" s="53">
-        <f t="shared" si="77"/>
+        <f t="shared" si="93"/>
         <v>3.2062529909076411E-2</v>
       </c>
       <c r="BI44" s="53">
-        <f t="shared" si="77"/>
+        <f t="shared" si="93"/>
         <v>2.9542323587938159E-2</v>
       </c>
       <c r="BJ44" s="53">
-        <f t="shared" si="77"/>
+        <f t="shared" si="93"/>
         <v>4.0317654245571169E-2</v>
       </c>
       <c r="BK44" s="53">
-        <f t="shared" si="77"/>
+        <f t="shared" si="93"/>
         <v>1.8273471959672338E-2</v>
       </c>
       <c r="BL44" s="53">
-        <f t="shared" si="77"/>
+        <f t="shared" si="93"/>
         <v>2.6432983766700186E-2</v>
       </c>
       <c r="BM44" s="53">
-        <f t="shared" si="77"/>
+        <f t="shared" si="93"/>
         <v>2.9854797123083185E-2</v>
       </c>
       <c r="BN44" s="53">
-        <f t="shared" si="77"/>
+        <f t="shared" si="93"/>
         <v>3.9391106956870078E-2</v>
       </c>
       <c r="BO44" s="53">
@@ -20153,67 +20150,67 @@
         <v>2.8481748430597534E-2</v>
       </c>
       <c r="CA44" s="53">
-        <f t="shared" ref="CA44:CP44" si="78">CA28/CA26</f>
+        <f t="shared" ref="CA44:CP44" si="94">CA28/CA26</f>
         <v>0.17591684644047853</v>
       </c>
       <c r="CB44" s="53">
-        <f t="shared" si="78"/>
+        <f t="shared" si="94"/>
         <v>0.16790034302220616</v>
       </c>
       <c r="CC44" s="53">
-        <f t="shared" si="78"/>
+        <f t="shared" si="94"/>
         <v>0.26884122728626753</v>
       </c>
       <c r="CD44" s="53">
-        <f t="shared" si="78"/>
+        <f t="shared" si="94"/>
         <v>0.13868218103098362</v>
       </c>
       <c r="CE44" s="53">
-        <f t="shared" si="78"/>
+        <f t="shared" si="94"/>
         <v>0.14364773820981713</v>
       </c>
       <c r="CF44" s="53">
-        <f t="shared" si="78"/>
+        <f t="shared" si="94"/>
         <v>0.12530452282597182</v>
       </c>
       <c r="CG44" s="53">
-        <f t="shared" si="78"/>
+        <f t="shared" si="94"/>
         <v>0.12909899658632462</v>
       </c>
       <c r="CH44" s="53">
-        <f t="shared" si="78"/>
+        <f t="shared" si="94"/>
         <v>0.11024498886414254</v>
       </c>
       <c r="CI44" s="53">
-        <f t="shared" si="78"/>
+        <f t="shared" si="94"/>
         <v>9.7783468032327764E-2</v>
       </c>
       <c r="CJ44" s="53">
-        <f t="shared" si="78"/>
+        <f t="shared" si="94"/>
         <v>0.16682274247491638</v>
       </c>
       <c r="CK44" s="53">
-        <f t="shared" si="78"/>
+        <f t="shared" si="94"/>
         <v>8.6240597050287277E-2</v>
       </c>
       <c r="CL44" s="53">
-        <f t="shared" si="78"/>
+        <f t="shared" si="94"/>
         <v>4.2938370041173776E-2</v>
       </c>
       <c r="CM44" s="53">
-        <f t="shared" si="78"/>
+        <f t="shared" si="94"/>
         <v>4.7394619783944082E-2</v>
       </c>
       <c r="CN44" s="53">
-        <f t="shared" si="78"/>
+        <f t="shared" si="94"/>
         <v>3.5481404865764267E-2</v>
       </c>
       <c r="CO44" s="53">
-        <f t="shared" si="78"/>
+        <f t="shared" si="94"/>
         <v>3.2871145111164235E-2</v>
       </c>
       <c r="CP44" s="53">
-        <f t="shared" si="78"/>
+        <f t="shared" si="94"/>
         <v>2.893456882167075E-2</v>
       </c>
       <c r="CQ44" s="68">
@@ -20252,83 +20249,83 @@
         <v>1500</v>
       </c>
       <c r="AU45" s="53">
-        <f t="shared" ref="AU45:BN45" si="79">AU29/AU26</f>
+        <f t="shared" ref="AU45:BN45" si="95">AU29/AU26</f>
         <v>3.5919181840858072E-2</v>
       </c>
       <c r="AV45" s="53">
-        <f t="shared" si="79"/>
+        <f t="shared" si="95"/>
         <v>4.3478260869565216E-2</v>
       </c>
       <c r="AW45" s="53">
-        <f t="shared" si="79"/>
+        <f t="shared" si="95"/>
         <v>3.6747458952306487E-2</v>
       </c>
       <c r="AX45" s="53">
-        <f t="shared" si="79"/>
+        <f t="shared" si="95"/>
         <v>3.640776699029126E-2</v>
       </c>
       <c r="AY45" s="53">
-        <f t="shared" si="79"/>
+        <f t="shared" si="95"/>
         <v>3.9229843561973524E-2</v>
       </c>
       <c r="AZ45" s="53">
-        <f t="shared" si="79"/>
+        <f t="shared" si="95"/>
         <v>4.1077738515901061E-2</v>
       </c>
       <c r="BA45" s="53">
-        <f t="shared" si="79"/>
+        <f t="shared" si="95"/>
         <v>3.7713139418254764E-2</v>
       </c>
       <c r="BB45" s="53">
-        <f t="shared" si="79"/>
+        <f t="shared" si="95"/>
         <v>3.6234662576687116E-2</v>
       </c>
       <c r="BC45" s="53">
-        <f t="shared" si="79"/>
+        <f t="shared" si="95"/>
         <v>3.71588929746468E-2</v>
       </c>
       <c r="BD45" s="53">
-        <f t="shared" si="79"/>
+        <f t="shared" si="95"/>
         <v>3.4382390394760778E-2</v>
       </c>
       <c r="BE45" s="53">
-        <f t="shared" si="79"/>
+        <f t="shared" si="95"/>
         <v>3.2140375260597639E-2</v>
       </c>
       <c r="BF45" s="53">
-        <f t="shared" si="79"/>
+        <f t="shared" si="95"/>
         <v>3.1631425133230189E-2</v>
       </c>
       <c r="BG45" s="53">
-        <f t="shared" si="79"/>
+        <f t="shared" si="95"/>
         <v>3.3228949199721643E-2</v>
       </c>
       <c r="BH45" s="53">
-        <f t="shared" si="79"/>
+        <f t="shared" si="95"/>
         <v>3.0626894241505824E-2</v>
       </c>
       <c r="BI45" s="53">
-        <f t="shared" si="79"/>
+        <f t="shared" si="95"/>
         <v>3.2297566202357263E-2</v>
       </c>
       <c r="BJ45" s="53">
-        <f t="shared" si="79"/>
+        <f t="shared" si="95"/>
         <v>3.1307269395235184E-2</v>
       </c>
       <c r="BK45" s="53">
-        <f t="shared" si="79"/>
+        <f t="shared" si="95"/>
         <v>3.4026465028355386E-2</v>
       </c>
       <c r="BL45" s="53">
-        <f t="shared" si="79"/>
+        <f t="shared" si="95"/>
         <v>3.2322942106019249E-2</v>
       </c>
       <c r="BM45" s="53">
-        <f t="shared" si="79"/>
+        <f t="shared" si="95"/>
         <v>3.0533315239516894E-2</v>
       </c>
       <c r="BN45" s="53">
-        <f t="shared" si="79"/>
+        <f t="shared" si="95"/>
         <v>3.0845239684871146E-2</v>
       </c>
       <c r="BO45" s="53">
@@ -20344,67 +20341,67 @@
         <v>3.3713089979074636E-2</v>
       </c>
       <c r="CA45" s="53">
-        <f t="shared" ref="CA45:CP45" si="80">CA29/CA26</f>
+        <f t="shared" ref="CA45:CP45" si="96">CA29/CA26</f>
         <v>0</v>
       </c>
       <c r="CB45" s="53">
-        <f t="shared" si="80"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="CC45" s="53">
-        <f t="shared" si="80"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="CD45" s="53">
-        <f t="shared" si="80"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="CE45" s="53">
-        <f t="shared" si="80"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="CF45" s="53">
-        <f t="shared" si="80"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="CG45" s="53">
-        <f t="shared" si="80"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="CH45" s="53">
-        <f t="shared" si="80"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="CI45" s="53">
-        <f t="shared" si="80"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="CJ45" s="53">
-        <f t="shared" si="80"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="CK45" s="53">
-        <f t="shared" si="80"/>
+        <f t="shared" si="96"/>
         <v>0</v>
       </c>
       <c r="CL45" s="53">
-        <f t="shared" si="80"/>
+        <f t="shared" si="96"/>
         <v>3.7906019214430431E-2</v>
       </c>
       <c r="CM45" s="53">
-        <f t="shared" si="80"/>
+        <f t="shared" si="96"/>
         <v>3.8445244651556874E-2</v>
       </c>
       <c r="CN45" s="53">
-        <f t="shared" si="80"/>
+        <f t="shared" si="96"/>
         <v>3.3727571165175156E-2</v>
       </c>
       <c r="CO45" s="53">
-        <f t="shared" si="80"/>
+        <f t="shared" si="96"/>
         <v>3.1835205992509365E-2</v>
       </c>
       <c r="CP45" s="53">
-        <f t="shared" si="80"/>
+        <f t="shared" si="96"/>
         <v>3.1845776973053574E-2</v>
       </c>
       <c r="CQ45" s="68">
@@ -20443,83 +20440,83 @@
         <v>1501</v>
       </c>
       <c r="AU46" s="53">
-        <f t="shared" ref="AU46:BN46" si="81">AU30/AU26</f>
+        <f t="shared" ref="AU46:BN46" si="97">AU30/AU26</f>
         <v>1.4966325767024195E-3</v>
       </c>
       <c r="AV46" s="53">
-        <f t="shared" si="81"/>
+        <f t="shared" si="97"/>
         <v>6.5967016491754122E-3</v>
       </c>
       <c r="AW46" s="53">
-        <f t="shared" si="81"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="AX46" s="53">
-        <f t="shared" si="81"/>
+        <f t="shared" si="97"/>
         <v>1.0922330097087379E-2</v>
       </c>
       <c r="AY46" s="53">
-        <f t="shared" si="81"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="AZ46" s="53">
-        <f t="shared" si="81"/>
+        <f t="shared" si="97"/>
         <v>1.4796819787985865E-2</v>
       </c>
       <c r="BA46" s="53">
-        <f t="shared" si="81"/>
+        <f t="shared" si="97"/>
         <v>5.416248746238716E-3</v>
       </c>
       <c r="BB46" s="53">
-        <f t="shared" si="81"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="BC46" s="53">
-        <f t="shared" si="81"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="BD46" s="53">
-        <f t="shared" si="81"/>
+        <f t="shared" si="97"/>
         <v>2.4195015462979808E-2</v>
       </c>
       <c r="BE46" s="53">
-        <f t="shared" si="81"/>
+        <f t="shared" si="97"/>
         <v>3.6136205698401667E-2</v>
       </c>
       <c r="BF46" s="53">
-        <f t="shared" si="81"/>
+        <f t="shared" si="97"/>
         <v>2.5786487880350697E-3</v>
       </c>
       <c r="BG46" s="53">
-        <f t="shared" si="81"/>
+        <f t="shared" si="97"/>
         <v>3.6708420320111346E-2</v>
       </c>
       <c r="BH46" s="53">
-        <f t="shared" si="81"/>
+        <f t="shared" si="97"/>
         <v>3.1903014834901897E-3</v>
       </c>
       <c r="BI46" s="53">
-        <f t="shared" si="81"/>
+        <f t="shared" si="97"/>
         <v>0</v>
       </c>
       <c r="BJ46" s="53">
-        <f t="shared" si="81"/>
+        <f t="shared" si="97"/>
         <v>4.7037263286499695E-2</v>
       </c>
       <c r="BK46" s="53">
-        <f t="shared" si="81"/>
+        <f t="shared" si="97"/>
         <v>1.9848771266540641E-2</v>
       </c>
       <c r="BL46" s="53">
-        <f t="shared" si="81"/>
+        <f t="shared" si="97"/>
         <v>1.4078437006177273E-2</v>
       </c>
       <c r="BM46" s="53">
-        <f t="shared" si="81"/>
+        <f t="shared" si="97"/>
         <v>2.388383769846655E-2</v>
       </c>
       <c r="BN46" s="53">
-        <f t="shared" si="81"/>
+        <f t="shared" si="97"/>
         <v>3.7388169314995327E-2</v>
       </c>
       <c r="BO46" s="53">
@@ -20535,67 +20532,67 @@
         <v>9.6489188560799806E-3</v>
       </c>
       <c r="CA46" s="53">
-        <f t="shared" ref="CA46:CP46" si="82">CA30/CA26</f>
+        <f t="shared" ref="CA46:CP46" si="98">CA30/CA26</f>
         <v>0</v>
       </c>
       <c r="CB46" s="53">
-        <f t="shared" si="82"/>
+        <f t="shared" si="98"/>
         <v>0</v>
       </c>
       <c r="CC46" s="53">
-        <f t="shared" si="82"/>
+        <f t="shared" si="98"/>
         <v>0</v>
       </c>
       <c r="CD46" s="53">
-        <f t="shared" si="82"/>
+        <f t="shared" si="98"/>
         <v>0</v>
       </c>
       <c r="CE46" s="53">
-        <f t="shared" si="82"/>
+        <f t="shared" si="98"/>
         <v>0</v>
       </c>
       <c r="CF46" s="53">
-        <f t="shared" si="82"/>
+        <f t="shared" si="98"/>
         <v>0</v>
       </c>
       <c r="CG46" s="53">
-        <f t="shared" si="82"/>
+        <f t="shared" si="98"/>
         <v>0</v>
       </c>
       <c r="CH46" s="53">
-        <f t="shared" si="82"/>
+        <f t="shared" si="98"/>
         <v>0</v>
       </c>
       <c r="CI46" s="53">
-        <f t="shared" si="82"/>
+        <f t="shared" si="98"/>
         <v>0</v>
       </c>
       <c r="CJ46" s="53">
-        <f t="shared" si="82"/>
+        <f t="shared" si="98"/>
         <v>0</v>
       </c>
       <c r="CK46" s="53">
-        <f t="shared" si="82"/>
+        <f t="shared" si="98"/>
         <v>0</v>
       </c>
       <c r="CL46" s="53">
-        <f t="shared" si="82"/>
+        <f t="shared" si="98"/>
         <v>4.7709300045748644E-3</v>
       </c>
       <c r="CM46" s="53">
-        <f t="shared" si="82"/>
+        <f t="shared" si="98"/>
         <v>4.977758949375132E-3</v>
       </c>
       <c r="CN46" s="53">
-        <f t="shared" si="82"/>
+        <f t="shared" si="98"/>
         <v>1.6009353779736474E-2</v>
       </c>
       <c r="CO46" s="53">
-        <f t="shared" si="82"/>
+        <f t="shared" si="98"/>
         <v>2.1475814805960634E-2</v>
       </c>
       <c r="CP46" s="53">
-        <f t="shared" si="82"/>
+        <f t="shared" si="98"/>
         <v>2.4141726133418539E-2</v>
       </c>
       <c r="CQ46" s="68">
@@ -20634,335 +20631,335 @@
         <v>122</v>
       </c>
       <c r="C47" s="53">
-        <f t="shared" ref="C47:BM47" si="83">C32/C26</f>
+        <f t="shared" ref="C47:BM47" si="99">C32/C26</f>
         <v>0.48529411764705882</v>
       </c>
       <c r="D47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.43515625000000002</v>
       </c>
       <c r="E47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.49340175953079179</v>
       </c>
       <c r="F47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.36104695919938412</v>
       </c>
       <c r="G47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.53516819571865448</v>
       </c>
       <c r="H47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.5252747252747253</v>
       </c>
       <c r="I47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.53641456582633051</v>
       </c>
       <c r="J47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.39568845618915161</v>
       </c>
       <c r="K47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.55696202531645567</v>
       </c>
       <c r="L47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.53089382123575279</v>
       </c>
       <c r="M47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.55115511551155116</v>
       </c>
       <c r="N47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>-5.7870370370370367E-3</v>
       </c>
       <c r="O47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.56882821387940841</v>
       </c>
       <c r="P47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.53516483516483515</v>
       </c>
       <c r="Q47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.55474452554744524</v>
       </c>
       <c r="R47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.47440633245382585</v>
       </c>
       <c r="S47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.58079748163693601</v>
       </c>
       <c r="T47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.58587786259541985</v>
       </c>
       <c r="U47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.56266907123534715</v>
       </c>
       <c r="V47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.43977055449330782</v>
       </c>
       <c r="W47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.59162062615101285</v>
       </c>
       <c r="X47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.58403716216216217</v>
       </c>
       <c r="Y47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.57028112449799195</v>
       </c>
       <c r="Z47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.42223143923683121</v>
       </c>
       <c r="AA47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.60582959641255607</v>
       </c>
       <c r="AB47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.52343096234309627</v>
       </c>
       <c r="AC47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.54110671936758892</v>
       </c>
       <c r="AD47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.43980929678188319</v>
       </c>
       <c r="AE47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.55110384300899429</v>
       </c>
       <c r="AF47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.51224944320712695</v>
       </c>
       <c r="AG47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.57986111111111116</v>
       </c>
       <c r="AH47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.49455732946298986</v>
       </c>
       <c r="AI47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.55084125822970009</v>
       </c>
       <c r="AJ47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.54143465443825745</v>
       </c>
       <c r="AK47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.57121836374337842</v>
       </c>
       <c r="AL47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.45954106280193235</v>
       </c>
       <c r="AM47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.50977653631284914</v>
       </c>
       <c r="AN47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.52824010914051844</v>
       </c>
       <c r="AO47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.5867111339148281</v>
       </c>
       <c r="AP47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.32413974257945888</v>
       </c>
       <c r="AQ47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.56904088454615587</v>
       </c>
       <c r="AR47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.58278628738147342</v>
       </c>
       <c r="AS47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.5943586299529886</v>
       </c>
       <c r="AT47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.54349796103307657</v>
       </c>
       <c r="AU47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.55150910451484159</v>
       </c>
       <c r="AV47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.51184407796101949</v>
       </c>
       <c r="AW47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.54860568152202238</v>
       </c>
       <c r="AX47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.49951456310679609</v>
       </c>
       <c r="AY47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.52876052948255114</v>
       </c>
       <c r="AZ47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.5170053003533569</v>
       </c>
       <c r="BA47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.5450351053159479</v>
       </c>
       <c r="BB47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.54198619631901845</v>
       </c>
       <c r="BC47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.57093090768337529</v>
       </c>
       <c r="BD47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.54902674185919598</v>
       </c>
       <c r="BE47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.54065323141070187</v>
       </c>
       <c r="BF47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.54736118274024415</v>
       </c>
       <c r="BG47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.54558107167710512</v>
       </c>
       <c r="BH47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.58318711118200672</v>
       </c>
       <c r="BI47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.58839736721261293</v>
       </c>
       <c r="BJ47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.51496640195479537</v>
       </c>
       <c r="BK47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.56773787019533717</v>
       </c>
       <c r="BL47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.57980175262174971</v>
       </c>
       <c r="BM47" s="53">
-        <f t="shared" si="83"/>
+        <f t="shared" si="99"/>
         <v>0.54335730764011403</v>
       </c>
       <c r="BN47" s="53">
-        <f t="shared" ref="BN47:BO47" si="84">BN32/BN26</f>
+        <f t="shared" ref="BN47:BO47" si="100">BN32/BN26</f>
         <v>0.52583789558018423</v>
       </c>
       <c r="BO47" s="53">
-        <f t="shared" si="84"/>
+        <f t="shared" si="100"/>
         <v>0.57227586206896552</v>
       </c>
       <c r="BP47" s="53">
-        <f t="shared" ref="BP47:BQ47" si="85">BP32/BP26</f>
+        <f t="shared" ref="BP47:BQ47" si="101">BP32/BP26</f>
         <v>0.58736013771056195</v>
       </c>
       <c r="BQ47" s="53">
-        <f t="shared" si="85"/>
+        <f t="shared" si="101"/>
         <v>0.58835154615205765</v>
       </c>
       <c r="CA47" s="53">
-        <f t="shared" ref="CA47:CP47" si="86">CA32/CA26</f>
+        <f t="shared" ref="CA47:CP47" si="102">CA32/CA26</f>
         <v>0.4432241616003138</v>
       </c>
       <c r="CB47" s="53">
-        <f t="shared" si="86"/>
+        <f t="shared" si="102"/>
         <v>0.49684058494313055</v>
       </c>
       <c r="CC47" s="53">
-        <f t="shared" si="86"/>
+        <f t="shared" si="102"/>
         <v>0.40408102472445634</v>
       </c>
       <c r="CD47" s="53">
-        <f t="shared" si="86"/>
+        <f t="shared" si="102"/>
         <v>0.53267487484778786</v>
       </c>
       <c r="CE47" s="53">
-        <f t="shared" si="86"/>
+        <f t="shared" si="102"/>
         <v>0.54174687199230032</v>
       </c>
       <c r="CF47" s="53">
-        <f t="shared" si="86"/>
+        <f t="shared" si="102"/>
         <v>0.54083253892596128</v>
       </c>
       <c r="CG47" s="53">
-        <f t="shared" si="86"/>
+        <f t="shared" si="102"/>
         <v>0.52529223130236891</v>
       </c>
       <c r="CH47" s="53">
-        <f t="shared" si="86"/>
+        <f t="shared" si="102"/>
         <v>0.53461395694135116</v>
       </c>
       <c r="CI47" s="53">
-        <f t="shared" si="86"/>
+        <f t="shared" si="102"/>
         <v>0.52988717292150112</v>
       </c>
       <c r="CJ47" s="53">
-        <f t="shared" si="86"/>
+        <f t="shared" si="102"/>
         <v>0.48709030100334449</v>
       </c>
       <c r="CK47" s="53">
-        <f t="shared" si="86"/>
+        <f t="shared" si="102"/>
         <v>0.57241011668542319</v>
       </c>
       <c r="CL47" s="53">
-        <f t="shared" si="86"/>
+        <f t="shared" si="102"/>
         <v>0.52813541598588332</v>
       </c>
       <c r="CM47" s="53">
-        <f t="shared" si="86"/>
+        <f t="shared" si="102"/>
         <v>0.53389112476170308</v>
       </c>
       <c r="CN47" s="53">
-        <f t="shared" si="86"/>
+        <f t="shared" si="102"/>
         <v>0.55151324369294419</v>
       </c>
       <c r="CO47" s="53">
-        <f t="shared" si="86"/>
+        <f t="shared" si="102"/>
         <v>0.55813212208144081</v>
       </c>
       <c r="CP47" s="53">
-        <f t="shared" si="86"/>
+        <f t="shared" si="102"/>
         <v>0.55320055383959954</v>
       </c>
       <c r="CQ47" s="68">
@@ -20970,39 +20967,39 @@
         <v>0.57300000000000006</v>
       </c>
       <c r="CR47" s="68">
-        <f t="shared" ref="CR47:CZ47" si="87">CR32/CR26</f>
+        <f t="shared" ref="CR47:CZ47" si="103">CR32/CR26</f>
         <v>0.57650000000000001</v>
       </c>
       <c r="CS47" s="68">
-        <f t="shared" si="87"/>
+        <f t="shared" si="103"/>
         <v>0.59700000000000009</v>
       </c>
       <c r="CT47" s="68">
-        <f t="shared" si="87"/>
+        <f t="shared" si="103"/>
         <v>0.60250000000000004</v>
       </c>
       <c r="CU47" s="68">
-        <f t="shared" si="87"/>
+        <f t="shared" si="103"/>
         <v>0.61550000000000005</v>
       </c>
       <c r="CV47" s="68">
-        <f t="shared" si="87"/>
+        <f t="shared" si="103"/>
         <v>0.61850000000000005</v>
       </c>
       <c r="CW47" s="68">
-        <f t="shared" si="87"/>
+        <f t="shared" si="103"/>
         <v>0.62149999999999994</v>
       </c>
       <c r="CX47" s="68">
-        <f t="shared" si="87"/>
+        <f t="shared" si="103"/>
         <v>0.62250000000000005</v>
       </c>
       <c r="CY47" s="68">
-        <f t="shared" si="87"/>
+        <f t="shared" si="103"/>
         <v>0.624</v>
       </c>
       <c r="CZ47" s="68">
-        <f t="shared" si="87"/>
+        <f t="shared" si="103"/>
         <v>0.62549999999999994</v>
       </c>
     </row>
@@ -21011,335 +21008,335 @@
         <v>123</v>
       </c>
       <c r="C48" s="53">
-        <f t="shared" ref="C48:BM48" si="88">C38/C37</f>
+        <f t="shared" ref="C48:BM48" si="104">C38/C37</f>
         <v>0.3327272727272727</v>
       </c>
       <c r="D48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.34888059701492535</v>
       </c>
       <c r="E48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.33484848484848484</v>
       </c>
       <c r="F48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.34745762711864409</v>
       </c>
       <c r="G48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.34532374100719426</v>
       </c>
       <c r="H48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.35764375876577842</v>
       </c>
       <c r="I48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.32333767926988266</v>
       </c>
       <c r="J48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.28694158075601373</v>
       </c>
       <c r="K48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.32775119617224879</v>
       </c>
       <c r="L48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.31838565022421522</v>
       </c>
       <c r="M48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.30485436893203882</v>
       </c>
       <c r="N48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>3</v>
       </c>
       <c r="O48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.318</v>
       </c>
       <c r="P48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.2805755395683453</v>
       </c>
       <c r="Q48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.27579737335834897</v>
       </c>
       <c r="R48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.3232662192393736</v>
       </c>
       <c r="S48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.30490018148820325</v>
       </c>
       <c r="T48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.31224655312246552</v>
       </c>
       <c r="U48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.29904306220095694</v>
       </c>
       <c r="V48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.31613611416026344</v>
       </c>
       <c r="W48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.32084309133489464</v>
       </c>
       <c r="X48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.32192279679533869</v>
       </c>
       <c r="Y48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.2842031029619182</v>
       </c>
       <c r="Z48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.20456802383316783</v>
       </c>
       <c r="AA48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.23880597014925373</v>
       </c>
       <c r="AB48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.257856567284448</v>
       </c>
       <c r="AC48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.27736686390532544</v>
       </c>
       <c r="AD48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.13170731707317074</v>
       </c>
       <c r="AE48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.28272251308900526</v>
       </c>
       <c r="AF48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.27985347985347986</v>
       </c>
       <c r="AG48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.2749540722596448</v>
       </c>
       <c r="AH48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.28832951945080093</v>
       </c>
       <c r="AI48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.26860622462787553</v>
       </c>
       <c r="AJ48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.27702702702702703</v>
       </c>
       <c r="AK48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.25983436853002068</v>
       </c>
       <c r="AL48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.84703504043126687</v>
       </c>
       <c r="AM48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.17249029395452026</v>
       </c>
       <c r="AN48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.18366285119667014</v>
       </c>
       <c r="AO48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.16121908127208481</v>
       </c>
       <c r="AP48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.26008230452674896</v>
       </c>
       <c r="AQ48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.15478892419428053</v>
       </c>
       <c r="AR48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.1869789599047241</v>
       </c>
       <c r="AS48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.1681136543014996</v>
       </c>
       <c r="AT48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.15151515151515152</v>
       </c>
       <c r="AU48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.14796175138399598</v>
       </c>
       <c r="AV48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.15976331360946747</v>
       </c>
       <c r="AW48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.20992167101827677</v>
       </c>
       <c r="AX48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.17666051660516605</v>
       </c>
       <c r="AY48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.16529680365296803</v>
       </c>
       <c r="AZ48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.16626311541565778</v>
       </c>
       <c r="BA48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.14275568181818182</v>
       </c>
       <c r="BB48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.15727948990435706</v>
       </c>
       <c r="BC48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>5.120807789397764E-2</v>
       </c>
       <c r="BD48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.18691922802001429</v>
       </c>
       <c r="BE48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.1865234375</v>
       </c>
       <c r="BF48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.18258336031078018</v>
       </c>
       <c r="BG48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.17245005257623555</v>
       </c>
       <c r="BH48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.23191144708423325</v>
       </c>
       <c r="BI48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.14969423025791012</v>
       </c>
       <c r="BJ48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.15959048479373683</v>
       </c>
       <c r="BK48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.1537380550871276</v>
       </c>
       <c r="BL48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.17288651942117289</v>
       </c>
       <c r="BM48" s="53">
-        <f t="shared" si="88"/>
+        <f t="shared" si="104"/>
         <v>0.15597516813243661</v>
       </c>
       <c r="BN48" s="53">
-        <f t="shared" ref="BN48:BO48" si="89">BN38/BN37</f>
+        <f t="shared" ref="BN48:BO48" si="105">BN38/BN37</f>
         <v>0.14109483423284502</v>
       </c>
       <c r="BO48" s="53">
-        <f t="shared" si="89"/>
+        <f t="shared" si="105"/>
         <v>0.18630612751178369</v>
       </c>
       <c r="BP48" s="53">
-        <f t="shared" ref="BP48:BQ48" si="90">BP38/BP37</f>
+        <f t="shared" ref="BP48:BQ48" si="106">BP38/BP37</f>
         <v>0.20783390410958905</v>
       </c>
       <c r="BQ48" s="53">
-        <f t="shared" si="90"/>
+        <f t="shared" si="106"/>
         <v>0.21444288857771554</v>
       </c>
       <c r="CA48" s="53">
-        <f t="shared" ref="CA48:CP48" si="91">CA38/CA37</f>
+        <f t="shared" ref="CA48:CP48" si="107">CA38/CA37</f>
         <v>0.34039675383228135</v>
       </c>
       <c r="CB48" s="53">
-        <f t="shared" si="91"/>
+        <f t="shared" si="107"/>
         <v>0.33006891548784911</v>
       </c>
       <c r="CC48" s="53">
-        <f t="shared" si="91"/>
+        <f t="shared" si="107"/>
         <v>0.30640465793304222</v>
       </c>
       <c r="CD48" s="53">
-        <f t="shared" si="91"/>
+        <f t="shared" si="107"/>
         <v>0.29849987287058227</v>
       </c>
       <c r="CE48" s="53">
-        <f t="shared" si="91"/>
+        <f t="shared" si="107"/>
         <v>0.30755555555555558</v>
       </c>
       <c r="CF48" s="53">
-        <f t="shared" si="91"/>
+        <f t="shared" si="107"/>
         <v>0.28785193935814135</v>
       </c>
       <c r="CG48" s="53">
-        <f t="shared" si="91"/>
+        <f t="shared" si="107"/>
         <v>0.23194836627672449</v>
       </c>
       <c r="CH48" s="53">
-        <f t="shared" si="91"/>
+        <f t="shared" si="107"/>
         <v>0.28108395324123275</v>
       </c>
       <c r="CI48" s="53">
-        <f t="shared" si="91"/>
+        <f t="shared" si="107"/>
         <v>0.3997240110395584</v>
       </c>
       <c r="CJ48" s="53">
-        <f t="shared" si="91"/>
+        <f t="shared" si="107"/>
         <v>0.18670183231538034</v>
       </c>
       <c r="CK48" s="53">
-        <f t="shared" si="91"/>
+        <f t="shared" si="107"/>
         <v>0.16575891480834445</v>
       </c>
       <c r="CL48" s="53">
-        <f t="shared" si="91"/>
+        <f t="shared" si="107"/>
         <v>0.173840206185567</v>
       </c>
       <c r="CM48" s="53">
-        <f t="shared" si="91"/>
+        <f t="shared" si="107"/>
         <v>0.15717473561657125</v>
       </c>
       <c r="CN48" s="53">
-        <f t="shared" si="91"/>
+        <f t="shared" si="107"/>
         <v>0.15359699965905216</v>
       </c>
       <c r="CO48" s="53">
-        <f t="shared" si="91"/>
+        <f t="shared" si="107"/>
         <v>0.17919202287557739</v>
       </c>
       <c r="CP48" s="53">
-        <f t="shared" si="91"/>
+        <f t="shared" si="107"/>
         <v>0.15602464927232201</v>
       </c>
       <c r="CQ48" s="68">
@@ -21378,376 +21375,376 @@
         <v>124</v>
       </c>
       <c r="C49" s="53">
-        <f t="shared" ref="C49:BM49" si="92">C39/C26</f>
+        <f t="shared" ref="C49:BM49" si="108">C39/C26</f>
         <v>0.31747404844290655</v>
       </c>
       <c r="D49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.27265624999999999</v>
       </c>
       <c r="E49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.32184750733137829</v>
       </c>
       <c r="F49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.23710546574287913</v>
       </c>
       <c r="G49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.34785932721712537</v>
       </c>
       <c r="H49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.3355311355311355</v>
       </c>
       <c r="I49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.36344537815126049</v>
       </c>
       <c r="J49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.28859527121001388</v>
       </c>
       <c r="K49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.37441705529646901</v>
       </c>
       <c r="L49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.36472705458908217</v>
       </c>
       <c r="M49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.39383938393839385</v>
       </c>
       <c r="N49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>1.1574074074074073E-2</v>
       </c>
       <c r="O49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.38794084186575656</v>
       </c>
       <c r="P49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.38461538461538464</v>
       </c>
       <c r="Q49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.40250260688216893</v>
       </c>
       <c r="R49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.31926121372031663</v>
       </c>
       <c r="S49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.40188877229800629</v>
       </c>
       <c r="T49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.40458015267175573</v>
       </c>
       <c r="U49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.39630297565374212</v>
       </c>
       <c r="V49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.29780114722753348</v>
       </c>
       <c r="W49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.40055248618784528</v>
       </c>
       <c r="X49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.39315878378378377</v>
       </c>
       <c r="Y49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.40763052208835343</v>
       </c>
       <c r="Z49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.33222729158025716</v>
       </c>
       <c r="AA49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.45739910313901344</v>
       </c>
       <c r="AB49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.38535564853556487</v>
       </c>
       <c r="AC49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.38616600790513833</v>
       </c>
       <c r="AD49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.35359555025824396</v>
       </c>
       <c r="AE49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.39206868356500407</v>
       </c>
       <c r="AF49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.36488492947290274</v>
       </c>
       <c r="AG49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.41111111111111109</v>
       </c>
       <c r="AH49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.33853410740203194</v>
       </c>
       <c r="AI49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.3953913679590344</v>
       </c>
       <c r="AJ49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.38552243694726501</v>
       </c>
       <c r="AK49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.42083578575632724</v>
       </c>
       <c r="AL49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>6.8538647342995168E-2</v>
       </c>
       <c r="AM49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.41675977653631285</v>
       </c>
       <c r="AN49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.42810368349249661</v>
       </c>
       <c r="AO49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.48717290918419703</v>
       </c>
       <c r="AP49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.23614394536380351</v>
       </c>
       <c r="AQ49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.47878632039084595</v>
       </c>
       <c r="AR49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.49793338195964015</v>
       </c>
       <c r="AS49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.47190508171032014</v>
       </c>
       <c r="AT49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.47575894879927505</v>
       </c>
       <c r="AU49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.42229982539286604</v>
       </c>
       <c r="AV49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.42578710644677659</v>
       </c>
       <c r="AW49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.39431847797758668</v>
       </c>
       <c r="AX49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.43325242718446599</v>
       </c>
       <c r="AY49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.43995186522262336</v>
       </c>
       <c r="AZ49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.45627208480565373</v>
       </c>
       <c r="BA49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.48425275827482445</v>
       </c>
       <c r="BB49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.45609662576687116</v>
       </c>
       <c r="BC49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.50919295529320685</v>
       </c>
       <c r="BD49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.41386210660360195</v>
       </c>
       <c r="BE49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.43415566365531622</v>
       </c>
       <c r="BF49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.43407254598590339</v>
       </c>
       <c r="BG49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.41075156576200417</v>
       </c>
       <c r="BH49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.45382038602647951</v>
       </c>
       <c r="BI49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.48951477116179398</v>
       </c>
       <c r="BJ49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.42623701893708005</v>
       </c>
       <c r="BK49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.47432262129804664</v>
       </c>
       <c r="BL49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.46803620169515875</v>
       </c>
       <c r="BM49" s="53">
-        <f t="shared" si="92"/>
+        <f t="shared" si="108"/>
         <v>0.44280092278463834</v>
       </c>
       <c r="BN49" s="53">
-        <f t="shared" ref="BN49:BO49" si="93">BN39/BN26</f>
+        <f t="shared" ref="BN49:BO49" si="109">BN39/BN26</f>
         <v>0.44625450660969423</v>
       </c>
       <c r="BO49" s="53">
-        <f t="shared" si="93"/>
+        <f t="shared" si="109"/>
         <v>0.45241379310344826</v>
       </c>
       <c r="BP49" s="53">
-        <f t="shared" ref="BP49:BQ49" si="94">BP39/BP26</f>
+        <f t="shared" ref="BP49:BQ49" si="110">BP39/BP26</f>
         <v>0.45505963359154061</v>
       </c>
       <c r="BQ49" s="53">
-        <f t="shared" si="94"/>
+        <f t="shared" si="110"/>
         <v>0.45652173913043476</v>
       </c>
       <c r="CA49" s="53">
-        <f t="shared" ref="CA49:CP49" si="95">CA39/CA26</f>
+        <f t="shared" ref="CA49:CP49" si="111">CA39/CA26</f>
         <v>0.28691900372622081</v>
       </c>
       <c r="CB49" s="53">
-        <f t="shared" si="95"/>
+        <f t="shared" si="111"/>
         <v>0.33345369200216646</v>
       </c>
       <c r="CC49" s="53">
-        <f t="shared" si="95"/>
+        <f t="shared" si="111"/>
         <v>0.28388442061364311</v>
       </c>
       <c r="CD49" s="53">
-        <f t="shared" si="95"/>
+        <f t="shared" si="111"/>
         <v>0.3732918414287647</v>
       </c>
       <c r="CE49" s="53">
-        <f t="shared" si="95"/>
+        <f t="shared" si="111"/>
         <v>0.37487969201154958</v>
       </c>
       <c r="CF49" s="53">
-        <f t="shared" si="95"/>
+        <f t="shared" si="111"/>
         <v>0.38311619531829255</v>
       </c>
       <c r="CG49" s="53">
-        <f t="shared" si="95"/>
+        <f t="shared" si="111"/>
         <v>0.39391745112237508</v>
       </c>
       <c r="CH49" s="53">
-        <f t="shared" si="95"/>
+        <f t="shared" si="111"/>
         <v>0.3766703786191537</v>
       </c>
       <c r="CI49" s="53">
-        <f t="shared" si="95"/>
+        <f t="shared" si="111"/>
         <v>0.31327518604465071</v>
       </c>
       <c r="CJ49" s="53">
-        <f t="shared" si="95"/>
+        <f t="shared" si="111"/>
         <v>0.39190635451505018</v>
       </c>
       <c r="CK49" s="53">
-        <f t="shared" si="95"/>
+        <f t="shared" si="111"/>
         <v>0.48083871349878576</v>
       </c>
       <c r="CL49" s="53">
-        <f t="shared" si="95"/>
+        <f t="shared" si="111"/>
         <v>0.41899222273054049</v>
       </c>
       <c r="CM49" s="53">
-        <f t="shared" si="95"/>
+        <f t="shared" si="111"/>
         <v>0.46001906375767848</v>
       </c>
       <c r="CN49" s="53">
-        <f t="shared" si="95"/>
+        <f t="shared" si="111"/>
         <v>0.44655304222691911</v>
       </c>
       <c r="CO49" s="53">
-        <f t="shared" si="95"/>
+        <f t="shared" si="111"/>
         <v>0.44605147820543467</v>
       </c>
       <c r="CP49" s="53">
-        <f t="shared" si="95"/>
+        <f t="shared" si="111"/>
         <v>0.45705967976710332</v>
       </c>
       <c r="CQ49" s="68">
         <f>CQ39/CQ26</f>
-        <v>0.7355518379931667</v>
+        <v>0.51721504238325333</v>
       </c>
       <c r="CR49" s="68">
-        <f t="shared" ref="CR49:CZ49" si="96">CR39/CR26</f>
-        <v>0.81811416219158173</v>
+        <f t="shared" ref="CR49:CZ49" si="112">CR39/CR26</f>
+        <v>0.53949064077235187</v>
       </c>
       <c r="CS49" s="68">
-        <f t="shared" si="96"/>
-        <v>0.94012153029370205</v>
+        <f t="shared" si="112"/>
+        <v>0.58010187654829959</v>
       </c>
       <c r="CT49" s="68">
-        <f t="shared" si="96"/>
-        <v>1.0811338012731111</v>
+        <f t="shared" si="112"/>
+        <v>0.61423953361255335</v>
       </c>
       <c r="CU49" s="68">
-        <f t="shared" si="96"/>
-        <v>1.2707688485536115</v>
+        <f t="shared" si="112"/>
+        <v>0.66190047764416726</v>
       </c>
       <c r="CV49" s="68">
-        <f t="shared" si="96"/>
-        <v>1.5222830841995194</v>
+        <f t="shared" si="112"/>
+        <v>0.71414518311540354</v>
       </c>
       <c r="CW49" s="68">
-        <f t="shared" si="96"/>
-        <v>1.8767155285913106</v>
+        <f t="shared" si="112"/>
+        <v>0.78461898159469479</v>
       </c>
       <c r="CX49" s="68">
-        <f t="shared" si="96"/>
-        <v>2.3694531641864076</v>
+        <f t="shared" si="112"/>
+        <v>0.87734907400046869</v>
       </c>
       <c r="CY49" s="68">
-        <f t="shared" si="96"/>
-        <v>3.0481068753630516</v>
+        <f t="shared" si="112"/>
+        <v>1.0007472479511941</v>
       </c>
       <c r="CZ49" s="68">
-        <f t="shared" si="96"/>
-        <v>3.9866357632709155</v>
+        <f t="shared" si="112"/>
+        <v>1.1652332700813162</v>
       </c>
     </row>
     <row r="51" spans="2:158">
@@ -21812,60 +21809,60 @@
         <v>10313</v>
       </c>
       <c r="CM51" s="1">
-        <f>BB51</f>
+        <f t="shared" ref="CM51:CM63" si="113">BB51</f>
         <v>7421</v>
       </c>
       <c r="CN51" s="1">
-        <f>BF51</f>
+        <f t="shared" ref="CN51:CN63" si="114">BF51</f>
         <v>7008</v>
       </c>
       <c r="CO51" s="1">
-        <f>BJ51</f>
+        <f t="shared" ref="CO51:CO63" si="115">BJ51</f>
         <v>8588</v>
       </c>
       <c r="CP51" s="1">
-        <f>BN51</f>
+        <f t="shared" ref="CP51:CP63" si="116">BN51</f>
         <v>8442</v>
       </c>
       <c r="CQ51" s="63">
         <f>CQ39+CP51</f>
-        <v>32331.715992000001</v>
+        <v>25240.435992000002</v>
       </c>
       <c r="CR51" s="63">
         <f>CR39+CQ51</f>
-        <v>62483.838791579998</v>
+        <v>45123.709991580006</v>
       </c>
       <c r="CS51" s="63">
         <f>CS39+CR51</f>
-        <v>101291.85153916229</v>
+        <v>69070.189563162305</v>
       </c>
       <c r="CT51" s="63">
-        <f t="shared" ref="CT51:CZ51" si="97">CT39+CS51</f>
-        <v>151068.52513574917</v>
+        <f t="shared" ref="CT51:CZ51" si="117">CT39+CS51</f>
+        <v>97350.501157109175</v>
       </c>
       <c r="CU51" s="63">
-        <f t="shared" si="97"/>
-        <v>215929.37280026326</v>
+        <f t="shared" si="117"/>
+        <v>131134.32116372325</v>
       </c>
       <c r="CV51" s="63">
-        <f t="shared" si="97"/>
-        <v>300517.56493952335</v>
+        <f t="shared" si="117"/>
+        <v>170816.9863602941</v>
       </c>
       <c r="CW51" s="63">
-        <f t="shared" si="97"/>
-        <v>411971.42192907404</v>
+        <f t="shared" si="117"/>
+        <v>217413.71902098792</v>
       </c>
       <c r="CX51" s="63">
-        <f t="shared" si="97"/>
-        <v>560658.45225649199</v>
+        <f t="shared" si="117"/>
+        <v>272468.79685302102</v>
       </c>
       <c r="CY51" s="63">
-        <f t="shared" si="97"/>
-        <v>761820.10974640795</v>
+        <f t="shared" si="117"/>
+        <v>338513.71698147169</v>
       </c>
       <c r="CZ51" s="63">
-        <f t="shared" si="97"/>
-        <v>1037220.0913360303</v>
+        <f t="shared" si="117"/>
+        <v>419008.96163976891</v>
       </c>
     </row>
     <row r="52" spans="2:158">
@@ -21930,19 +21927,19 @@
         <v>478</v>
       </c>
       <c r="CM52" s="1">
-        <f>BB52</f>
+        <f t="shared" si="113"/>
         <v>586</v>
       </c>
       <c r="CN52" s="1">
-        <f>BF52</f>
+        <f t="shared" si="114"/>
         <v>589</v>
       </c>
       <c r="CO52" s="1">
-        <f>BJ52</f>
+        <f t="shared" si="115"/>
         <v>32</v>
       </c>
       <c r="CP52" s="1">
-        <f>BN52</f>
+        <f t="shared" si="116"/>
         <v>492</v>
       </c>
     </row>
@@ -22008,19 +22005,19 @@
         <v>2054</v>
       </c>
       <c r="CM53" s="1">
-        <f>BB53</f>
+        <f t="shared" si="113"/>
         <v>473</v>
       </c>
       <c r="CN53" s="1">
-        <f>BF53</f>
+        <f t="shared" si="114"/>
         <v>1568</v>
       </c>
       <c r="CO53" s="1">
-        <f>BJ53</f>
+        <f t="shared" si="115"/>
         <v>1845</v>
       </c>
       <c r="CP53" s="1">
-        <f>BN53</f>
+        <f t="shared" si="116"/>
         <v>1874</v>
       </c>
       <c r="CR53" s="54" t="s">
@@ -22040,7 +22037,7 @@
         <v>1535</v>
       </c>
       <c r="CZ53" s="57">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="54" spans="2:158" ht="14.25" customHeight="1">
@@ -22105,19 +22102,19 @@
         <v>335</v>
       </c>
       <c r="CM54" s="1">
-        <f>BB54</f>
+        <f t="shared" si="113"/>
         <v>3006</v>
       </c>
       <c r="CN54" s="1">
-        <f>BF54</f>
+        <f t="shared" si="114"/>
         <v>400</v>
       </c>
       <c r="CO54" s="1">
-        <f>BJ54</f>
+        <f t="shared" si="115"/>
         <v>592</v>
       </c>
       <c r="CP54" s="1">
-        <f>BN54</f>
+        <f t="shared" si="116"/>
         <v>330</v>
       </c>
       <c r="CR54" s="55">
@@ -22204,19 +22201,19 @@
         <v>4247</v>
       </c>
       <c r="CM55" s="1">
-        <f>BB55</f>
+        <f t="shared" si="113"/>
         <v>1319</v>
       </c>
       <c r="CN55" s="1">
-        <f>BF55</f>
+        <f t="shared" si="114"/>
         <v>3425</v>
       </c>
       <c r="CO55" s="1">
-        <f>BJ55</f>
+        <f t="shared" si="115"/>
         <v>4060</v>
       </c>
       <c r="CP55" s="1">
-        <f>BN55</f>
+        <f t="shared" si="116"/>
         <v>3773</v>
       </c>
       <c r="CR55" s="58">
@@ -22307,19 +22304,19 @@
         <v>1842</v>
       </c>
       <c r="CM56" s="1">
-        <f>BB56</f>
+        <f t="shared" si="113"/>
         <v>1873</v>
       </c>
       <c r="CN56" s="1">
-        <f>BF56</f>
+        <f t="shared" si="114"/>
         <v>1270</v>
       </c>
       <c r="CO56" s="1">
-        <f>BJ56</f>
+        <f t="shared" si="115"/>
         <v>1233</v>
       </c>
       <c r="CP56" s="1">
-        <f>BN56</f>
+        <f t="shared" si="116"/>
         <v>1821</v>
       </c>
       <c r="CR56" s="62">
@@ -22402,19 +22399,19 @@
         <v>3954</v>
       </c>
       <c r="CM57" s="1">
-        <f>BB57</f>
+        <f t="shared" si="113"/>
         <v>2271</v>
       </c>
       <c r="CN57" s="1">
-        <f>BF57</f>
+        <f t="shared" si="114"/>
         <v>2346</v>
       </c>
       <c r="CO57" s="1">
-        <f>BJ57</f>
+        <f t="shared" si="115"/>
         <v>2611</v>
       </c>
       <c r="CP57" s="1">
-        <f>BN57</f>
+        <f t="shared" si="116"/>
         <v>2992</v>
       </c>
       <c r="CR57" s="55"/>
@@ -22494,19 +22491,19 @@
         <v>2299</v>
       </c>
       <c r="CM58" s="1">
-        <f>BB58</f>
+        <f t="shared" si="113"/>
         <v>1907</v>
       </c>
       <c r="CN58" s="1">
-        <f>BF58</f>
+        <f t="shared" si="114"/>
         <v>2006</v>
       </c>
       <c r="CO58" s="1">
-        <f>BJ58</f>
+        <f t="shared" si="115"/>
         <v>2061</v>
       </c>
       <c r="CP58" s="1">
-        <f>BN58</f>
+        <f t="shared" si="116"/>
         <v>2138</v>
       </c>
       <c r="CY58" s="35" t="s">
@@ -22579,19 +22576,19 @@
         <v>1546</v>
       </c>
       <c r="CM59" s="1">
-        <f>BB59</f>
+        <f t="shared" si="113"/>
         <v>486</v>
       </c>
       <c r="CN59" s="1">
-        <f>BF59</f>
+        <f t="shared" si="114"/>
         <v>1151</v>
       </c>
       <c r="CO59" s="1">
-        <f>BJ59</f>
+        <f t="shared" si="115"/>
         <v>1355</v>
       </c>
       <c r="CP59" s="1">
-        <f>BN59</f>
+        <f t="shared" si="116"/>
         <v>1614</v>
       </c>
     </row>
@@ -22657,27 +22654,27 @@
         <v>9574</v>
       </c>
       <c r="CM60" s="1">
-        <f>BB60</f>
+        <f t="shared" si="113"/>
         <v>7662</v>
       </c>
       <c r="CN60" s="1">
-        <f>BF60</f>
+        <f t="shared" si="114"/>
         <v>7522</v>
       </c>
       <c r="CO60" s="1">
-        <f>BJ60</f>
+        <f t="shared" si="115"/>
         <v>7660</v>
       </c>
       <c r="CP60" s="1">
-        <f>BN60</f>
+        <f t="shared" si="116"/>
         <v>9193</v>
       </c>
       <c r="CY60" s="35" t="s">
         <v>1542</v>
       </c>
-      <c r="CZ60" s="74">
+      <c r="CZ60" s="72">
         <f>NPV(CZ58,CQ39:EO39)</f>
-        <v>1840717.7319087465</v>
+        <v>607468.63854771294</v>
       </c>
     </row>
     <row r="61" spans="2:158" ht="14.25" customHeight="1">
@@ -22742,19 +22739,19 @@
         <v>5591</v>
       </c>
       <c r="CM61" s="1">
-        <f>BB61</f>
+        <f t="shared" si="113"/>
         <v>3671</v>
       </c>
       <c r="CN61" s="1">
-        <f>BF61</f>
+        <f t="shared" si="114"/>
         <v>3859</v>
       </c>
       <c r="CO61" s="1">
-        <f>BJ61</f>
+        <f t="shared" si="115"/>
         <v>4086</v>
       </c>
       <c r="CP61" s="1">
-        <f>BN61</f>
+        <f t="shared" si="116"/>
         <v>5453</v>
       </c>
       <c r="CY61" s="35" t="s">
@@ -22830,27 +22827,27 @@
         <v>11056</v>
       </c>
       <c r="CM62" s="1">
-        <f>BB62</f>
+        <f t="shared" si="113"/>
         <v>6994</v>
       </c>
       <c r="CN62" s="1">
-        <f>BF62</f>
+        <f t="shared" si="114"/>
         <v>7580</v>
       </c>
       <c r="CO62" s="1">
-        <f>BJ62</f>
+        <f t="shared" si="115"/>
         <v>8325</v>
       </c>
       <c r="CP62" s="1">
-        <f>BN62</f>
+        <f t="shared" si="116"/>
         <v>9959</v>
       </c>
       <c r="CY62" s="35" t="s">
         <v>1543</v>
       </c>
-      <c r="CZ62" s="72">
+      <c r="CZ62" s="70">
         <f>CZ60/CZ61</f>
-        <v>2038.4471006741378</v>
+        <v>672.72274479259465</v>
       </c>
     </row>
     <row r="63" spans="2:158" s="2" customFormat="1" ht="14.25" customHeight="1">
@@ -22858,79 +22855,79 @@
         <v>1528</v>
       </c>
       <c r="AY63" s="2">
-        <f t="shared" ref="AY63:BO63" si="98">SUM(AY51:AY62)</f>
+        <f t="shared" ref="AY63:BO63" si="118">SUM(AY51:AY62)</f>
         <v>34800</v>
       </c>
       <c r="AZ63" s="2">
-        <f t="shared" si="98"/>
+        <f t="shared" si="118"/>
         <v>34911</v>
       </c>
       <c r="BA63" s="2">
-        <f t="shared" si="98"/>
+        <f t="shared" si="118"/>
         <v>35410</v>
       </c>
       <c r="BB63" s="2">
-        <f t="shared" si="98"/>
+        <f t="shared" si="118"/>
         <v>37669</v>
       </c>
       <c r="BC63" s="2">
-        <f t="shared" si="98"/>
+        <f t="shared" si="118"/>
         <v>37163</v>
       </c>
       <c r="BD63" s="2">
-        <f t="shared" si="98"/>
+        <f t="shared" si="118"/>
         <v>36231</v>
       </c>
       <c r="BE63" s="2">
-        <f t="shared" si="98"/>
+        <f t="shared" si="118"/>
         <v>37612</v>
       </c>
       <c r="BF63" s="2">
-        <f t="shared" si="98"/>
+        <f t="shared" si="118"/>
         <v>38724</v>
       </c>
       <c r="BG63" s="2">
-        <f t="shared" si="98"/>
+        <f t="shared" si="118"/>
         <v>38936</v>
       </c>
       <c r="BH63" s="2">
-        <f t="shared" si="98"/>
+        <f t="shared" si="118"/>
         <v>39004</v>
       </c>
       <c r="BI63" s="2">
-        <f t="shared" si="98"/>
+        <f t="shared" si="118"/>
         <v>39674</v>
       </c>
       <c r="BJ63" s="2">
-        <f t="shared" si="98"/>
+        <f t="shared" si="118"/>
         <v>42448</v>
       </c>
       <c r="BK63" s="2">
-        <f t="shared" si="98"/>
+        <f t="shared" si="118"/>
         <v>42602</v>
       </c>
       <c r="BL63" s="2">
-        <f t="shared" si="98"/>
+        <f t="shared" si="118"/>
         <v>42333</v>
       </c>
       <c r="BM63" s="2">
-        <f t="shared" si="98"/>
+        <f t="shared" si="118"/>
         <v>47237</v>
       </c>
       <c r="BN63" s="2">
-        <f t="shared" si="98"/>
+        <f t="shared" si="118"/>
         <v>48081</v>
       </c>
       <c r="BO63" s="2">
-        <f t="shared" si="98"/>
+        <f t="shared" si="118"/>
         <v>48470</v>
       </c>
       <c r="BP63" s="2">
-        <f t="shared" ref="BP63:BQ63" si="99">SUM(BP51:BP62)</f>
+        <f t="shared" ref="BP63:BQ63" si="119">SUM(BP51:BP62)</f>
         <v>51431</v>
       </c>
       <c r="BQ63" s="2">
-        <f t="shared" si="99"/>
+        <f t="shared" si="119"/>
         <v>53289</v>
       </c>
       <c r="BR63" s="34"/>
@@ -22939,19 +22936,19 @@
       <c r="BU63" s="34"/>
       <c r="BV63" s="34"/>
       <c r="CM63" s="2">
-        <f>BB63</f>
+        <f t="shared" si="113"/>
         <v>37669</v>
       </c>
       <c r="CN63" s="2">
-        <f>BF63</f>
+        <f t="shared" si="114"/>
         <v>38724</v>
       </c>
       <c r="CO63" s="2">
-        <f>BJ63</f>
+        <f t="shared" si="115"/>
         <v>42448</v>
       </c>
       <c r="CP63" s="2">
-        <f>BN63</f>
+        <f t="shared" si="116"/>
         <v>48081</v>
       </c>
       <c r="CQ63" s="35"/>
@@ -22965,9 +22962,9 @@
       <c r="CY63" s="35" t="s">
         <v>1544</v>
       </c>
-      <c r="CZ63" s="72">
+      <c r="CZ63" s="70">
         <f>Main!C3</f>
-        <v>551.99</v>
+        <v>576.75</v>
       </c>
       <c r="DA63" s="35"/>
       <c r="DB63" s="34"/>
@@ -23030,7 +23027,7 @@
       </c>
       <c r="CZ64" s="57">
         <f>CZ62/CZ63-1</f>
-        <v>2.6929058509649408</v>
+        <v>0.16640267844403067</v>
       </c>
       <c r="DA64" s="35" t="str">
         <f>IF(CZ64&gt;0,"Upside","Downside")</f>
@@ -23099,26 +23096,26 @@
         <v>935</v>
       </c>
       <c r="CM65" s="1">
-        <f>BB65</f>
+        <f t="shared" ref="CM65:CM77" si="120">BB65</f>
         <v>738</v>
       </c>
       <c r="CN65" s="1">
-        <f>BF65</f>
+        <f t="shared" ref="CN65:CN77" si="121">BF65</f>
         <v>926</v>
       </c>
       <c r="CO65" s="1">
-        <f>BJ65</f>
+        <f t="shared" ref="CO65:CO77" si="122">BJ65</f>
         <v>834</v>
       </c>
       <c r="CP65" s="1">
-        <f>BN65</f>
+        <f t="shared" ref="CP65:CP77" si="123">BN65</f>
         <v>929</v>
       </c>
-      <c r="CY65" s="71" t="str" cm="1">
+      <c r="CY65" s="74" t="str" cm="1">
         <f t="array" ref="CY65">_xlfn.IFS(CZ64&gt;=25%,"Strong Buy",CZ64&gt;=10.00001%,"Buy",AND(CZ64&lt;=10%,CZ64&gt;=-4.9999%),"Hold",AND(CZ64&lt;=-5%,CZ64&gt;=-14.999999%),"Sell",CZ64&lt;=-15%,"Strong Sell")</f>
-        <v>Strong Buy</v>
-      </c>
-      <c r="CZ65" s="71"/>
+        <v>Buy</v>
+      </c>
+      <c r="CZ65" s="74"/>
     </row>
     <row r="66" spans="2:158" ht="14.25" customHeight="1">
       <c r="B66" s="1" t="s">
@@ -23182,19 +23179,19 @@
         <v>2422</v>
       </c>
       <c r="CM66" s="1">
-        <f>BB66</f>
+        <f t="shared" si="120"/>
         <v>913</v>
       </c>
       <c r="CN66" s="1">
-        <f>BF66</f>
+        <f t="shared" si="121"/>
         <v>1111</v>
       </c>
       <c r="CO66" s="1">
-        <f>BJ66</f>
+        <f t="shared" si="122"/>
         <v>1399</v>
       </c>
       <c r="CP66" s="1">
-        <f>BN66</f>
+        <f t="shared" si="123"/>
         <v>2316</v>
       </c>
     </row>
@@ -23260,19 +23257,19 @@
         <v>2054</v>
       </c>
       <c r="CM67" s="1">
-        <f>BB67</f>
+        <f t="shared" si="120"/>
         <v>1873</v>
       </c>
       <c r="CN67" s="1">
-        <f>BF67</f>
+        <f t="shared" si="121"/>
         <v>1568</v>
       </c>
       <c r="CO67" s="1">
-        <f>BJ67</f>
+        <f t="shared" si="122"/>
         <v>1845</v>
       </c>
       <c r="CP67" s="1">
-        <f>BN67</f>
+        <f t="shared" si="123"/>
         <v>1874</v>
       </c>
     </row>
@@ -23338,19 +23335,19 @@
         <v>943</v>
       </c>
       <c r="CM68" s="1">
-        <f>BB68</f>
+        <f t="shared" si="120"/>
         <v>840</v>
       </c>
       <c r="CN68" s="1">
-        <f>BF68</f>
+        <f t="shared" si="121"/>
         <v>1094</v>
       </c>
       <c r="CO68" s="1">
-        <f>BJ68</f>
+        <f t="shared" si="122"/>
         <v>723</v>
       </c>
       <c r="CP68" s="1">
-        <f>BN68</f>
+        <f t="shared" si="123"/>
         <v>930</v>
       </c>
     </row>
@@ -23416,19 +23413,19 @@
         <v>11979</v>
       </c>
       <c r="CM69" s="1">
-        <f>BB69</f>
+        <f t="shared" si="120"/>
         <v>6642</v>
       </c>
       <c r="CN69" s="1">
-        <f>BF69</f>
+        <f t="shared" si="121"/>
         <v>7801</v>
       </c>
       <c r="CO69" s="1">
-        <f>BJ69</f>
+        <f t="shared" si="122"/>
         <v>8517</v>
       </c>
       <c r="CP69" s="1">
-        <f>BN69</f>
+        <f t="shared" si="123"/>
         <v>10393</v>
       </c>
     </row>
@@ -23494,19 +23491,19 @@
         <v>0</v>
       </c>
       <c r="CM70" s="1">
-        <f>BB70</f>
+        <f t="shared" si="120"/>
         <v>792</v>
       </c>
       <c r="CN70" s="1">
-        <f>BF70</f>
+        <f t="shared" si="121"/>
         <v>274</v>
       </c>
       <c r="CO70" s="1">
-        <f>BJ70</f>
+        <f t="shared" si="122"/>
         <v>1337</v>
       </c>
       <c r="CP70" s="1">
-        <f>BN70</f>
+        <f t="shared" si="123"/>
         <v>750</v>
       </c>
     </row>
@@ -23572,19 +23569,19 @@
         <v>2360</v>
       </c>
       <c r="CM71" s="1">
-        <f>BB71</f>
+        <f t="shared" si="120"/>
         <v>1364</v>
       </c>
       <c r="CN71" s="1">
-        <f>BF71</f>
+        <f t="shared" si="121"/>
         <v>1397</v>
       </c>
       <c r="CO71" s="1">
-        <f>BJ71</f>
+        <f t="shared" si="122"/>
         <v>1609</v>
       </c>
       <c r="CP71" s="1">
-        <f>BN71</f>
+        <f t="shared" si="123"/>
         <v>2028</v>
       </c>
     </row>
@@ -23650,19 +23647,19 @@
         <v>18983</v>
       </c>
       <c r="CM72" s="1">
-        <f>BB72</f>
+        <f t="shared" si="120"/>
         <v>13109</v>
       </c>
       <c r="CN72" s="1">
-        <f>BF72</f>
+        <f t="shared" si="121"/>
         <v>13749</v>
       </c>
       <c r="CO72" s="1">
-        <f>BJ72</f>
+        <f t="shared" si="122"/>
         <v>14344</v>
       </c>
       <c r="CP72" s="1">
-        <f>BN72</f>
+        <f t="shared" si="123"/>
         <v>17476</v>
       </c>
     </row>
@@ -23728,19 +23725,19 @@
         <v>326</v>
       </c>
       <c r="CM73" s="1">
-        <f>BB73</f>
+        <f t="shared" si="120"/>
         <v>395</v>
       </c>
       <c r="CN73" s="1">
-        <f>BF73</f>
+        <f t="shared" si="121"/>
         <v>393</v>
       </c>
       <c r="CO73" s="1">
-        <f>BJ73</f>
+        <f t="shared" si="122"/>
         <v>369</v>
       </c>
       <c r="CP73" s="1">
-        <f>BN73</f>
+        <f t="shared" si="123"/>
         <v>317</v>
       </c>
     </row>
@@ -23806,19 +23803,19 @@
         <v>5368</v>
       </c>
       <c r="CM74" s="1">
-        <f>BB74</f>
+        <f t="shared" si="120"/>
         <v>3591</v>
       </c>
       <c r="CN74" s="1">
-        <f>BF74</f>
+        <f t="shared" si="121"/>
         <v>4034</v>
       </c>
       <c r="CO74" s="1">
-        <f>BJ74</f>
+        <f t="shared" si="122"/>
         <v>4474</v>
       </c>
       <c r="CP74" s="1">
-        <f>BN74</f>
+        <f t="shared" si="123"/>
         <v>4553</v>
       </c>
     </row>
@@ -23827,67 +23824,67 @@
         <v>1529</v>
       </c>
       <c r="AY75" s="2">
-        <f t="shared" ref="AY75:BN75" si="100">SUM(AY65:AY74)</f>
+        <f t="shared" ref="AY75:BN75" si="124">SUM(AY65:AY74)</f>
         <v>28347</v>
       </c>
       <c r="AZ75" s="2">
-        <f t="shared" si="100"/>
+        <f t="shared" si="124"/>
         <v>28342</v>
       </c>
       <c r="BA75" s="2">
-        <f t="shared" si="100"/>
+        <f t="shared" si="124"/>
         <v>28608</v>
       </c>
       <c r="BB75" s="2">
-        <f t="shared" si="100"/>
+        <f t="shared" si="124"/>
         <v>30257</v>
       </c>
       <c r="BC75" s="2">
-        <f t="shared" si="100"/>
+        <f t="shared" si="124"/>
         <v>30033</v>
       </c>
       <c r="BD75" s="2">
-        <f t="shared" si="100"/>
+        <f t="shared" si="124"/>
         <v>29969</v>
       </c>
       <c r="BE75" s="2">
-        <f t="shared" si="100"/>
+        <f t="shared" si="124"/>
         <v>31169</v>
       </c>
       <c r="BF75" s="2">
-        <f t="shared" si="100"/>
+        <f t="shared" si="124"/>
         <v>32347</v>
       </c>
       <c r="BG75" s="2">
-        <f t="shared" si="100"/>
+        <f t="shared" si="124"/>
         <v>33529</v>
       </c>
       <c r="BH75" s="2">
-        <f t="shared" si="100"/>
+        <f t="shared" si="124"/>
         <v>33425</v>
       </c>
       <c r="BI75" s="2">
-        <f t="shared" si="100"/>
+        <f t="shared" si="124"/>
         <v>33293</v>
       </c>
       <c r="BJ75" s="2">
-        <f t="shared" si="100"/>
+        <f t="shared" si="124"/>
         <v>35451</v>
       </c>
       <c r="BK75" s="2">
-        <f t="shared" si="100"/>
+        <f t="shared" si="124"/>
         <v>35294</v>
       </c>
       <c r="BL75" s="2">
-        <f t="shared" si="100"/>
+        <f t="shared" si="124"/>
         <v>34851</v>
       </c>
       <c r="BM75" s="2">
-        <f t="shared" si="100"/>
+        <f t="shared" si="124"/>
         <v>39739</v>
       </c>
       <c r="BN75" s="2">
-        <f t="shared" si="100"/>
+        <f t="shared" si="124"/>
         <v>41566</v>
       </c>
       <c r="BO75" s="2">
@@ -23908,19 +23905,19 @@
       <c r="BU75" s="34"/>
       <c r="BV75" s="34"/>
       <c r="CM75" s="2">
-        <f>BB75</f>
+        <f t="shared" si="120"/>
         <v>30257</v>
       </c>
       <c r="CN75" s="2">
-        <f>BF75</f>
+        <f t="shared" si="121"/>
         <v>32347</v>
       </c>
       <c r="CO75" s="2">
-        <f>BJ75</f>
+        <f t="shared" si="122"/>
         <v>35451</v>
       </c>
       <c r="CP75" s="2">
-        <f>BN75</f>
+        <f t="shared" si="123"/>
         <v>41566</v>
       </c>
       <c r="CQ75" s="34"/>
@@ -24065,19 +24062,19 @@
         <v>7919</v>
       </c>
       <c r="CM76" s="1">
-        <f>BB76</f>
+        <f t="shared" si="120"/>
         <v>7412</v>
       </c>
       <c r="CN76" s="1">
-        <f>BF76</f>
+        <f t="shared" si="121"/>
         <v>6377</v>
       </c>
       <c r="CO76" s="1">
-        <f>BJ76</f>
+        <f t="shared" si="122"/>
         <v>6997</v>
       </c>
       <c r="CP76" s="1">
-        <f>BN76</f>
+        <f t="shared" si="123"/>
         <v>6515</v>
       </c>
     </row>
@@ -24086,67 +24083,67 @@
         <v>1531</v>
       </c>
       <c r="AY77" s="2">
-        <f t="shared" ref="AY77:BN77" si="101">SUM(AY75:AY76)</f>
+        <f t="shared" ref="AY77:BN77" si="125">SUM(AY75:AY76)</f>
         <v>34800</v>
       </c>
       <c r="AZ77" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="125"/>
         <v>34911</v>
       </c>
       <c r="BA77" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="125"/>
         <v>35410</v>
       </c>
       <c r="BB77" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="125"/>
         <v>37669</v>
       </c>
       <c r="BC77" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="125"/>
         <v>37163</v>
       </c>
       <c r="BD77" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="125"/>
         <v>36231</v>
       </c>
       <c r="BE77" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="125"/>
         <v>37612</v>
       </c>
       <c r="BF77" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="125"/>
         <v>38724</v>
       </c>
       <c r="BG77" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="125"/>
         <v>38936</v>
       </c>
       <c r="BH77" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="125"/>
         <v>39004</v>
       </c>
       <c r="BI77" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="125"/>
         <v>39674</v>
       </c>
       <c r="BJ77" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="125"/>
         <v>42448</v>
       </c>
       <c r="BK77" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="125"/>
         <v>42602</v>
       </c>
       <c r="BL77" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="125"/>
         <v>42333</v>
       </c>
       <c r="BM77" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="125"/>
         <v>47237</v>
       </c>
       <c r="BN77" s="2">
-        <f t="shared" si="101"/>
+        <f t="shared" si="125"/>
         <v>48081</v>
       </c>
       <c r="BO77" s="2">
@@ -24167,19 +24164,19 @@
       <c r="BU77" s="34"/>
       <c r="BV77" s="34"/>
       <c r="CM77" s="2">
-        <f>BB77</f>
+        <f t="shared" si="120"/>
         <v>37669</v>
       </c>
       <c r="CN77" s="2">
-        <f>BF77</f>
+        <f t="shared" si="121"/>
         <v>38724</v>
       </c>
       <c r="CO77" s="2">
-        <f>BJ77</f>
+        <f t="shared" si="122"/>
         <v>42448</v>
       </c>
       <c r="CP77" s="2">
-        <f>BN77</f>
+        <f t="shared" si="123"/>
         <v>48081</v>
       </c>
       <c r="CQ77" s="34"/>
@@ -24252,67 +24249,67 @@
         <v>127</v>
       </c>
       <c r="AY79" s="39">
-        <f t="shared" ref="AY79:BN79" si="102">SUM(AY51:AY57)/SUM(AY65:AY71)</f>
+        <f t="shared" ref="AY79:BN79" si="126">SUM(AY51:AY57)/SUM(AY65:AY71)</f>
         <v>1.4296296296296296</v>
       </c>
       <c r="AZ79" s="39">
-        <f t="shared" si="102"/>
+        <f t="shared" si="126"/>
         <v>1.3347791449057271</v>
       </c>
       <c r="BA79" s="39">
-        <f t="shared" si="102"/>
+        <f t="shared" si="126"/>
         <v>1.330507741544849</v>
       </c>
       <c r="BB79" s="39">
-        <f t="shared" si="102"/>
+        <f t="shared" si="126"/>
         <v>1.2877222306640328</v>
       </c>
       <c r="BC79" s="39">
-        <f t="shared" si="102"/>
+        <f t="shared" si="126"/>
         <v>1.3374413145539905</v>
       </c>
       <c r="BD79" s="39">
-        <f t="shared" si="102"/>
+        <f t="shared" si="126"/>
         <v>1.2586677699627637</v>
       </c>
       <c r="BE79" s="39">
-        <f t="shared" si="102"/>
+        <f t="shared" si="126"/>
         <v>1.2483674680914219</v>
       </c>
       <c r="BF79" s="39">
-        <f t="shared" si="102"/>
+        <f t="shared" si="126"/>
         <v>1.1718297932397148</v>
       </c>
       <c r="BG79" s="39">
-        <f t="shared" si="102"/>
+        <f t="shared" si="126"/>
         <v>1.202842282616658</v>
       </c>
       <c r="BH79" s="39">
-        <f t="shared" si="102"/>
+        <f t="shared" si="126"/>
         <v>1.1294069417873736</v>
       </c>
       <c r="BI79" s="39">
-        <f t="shared" si="102"/>
+        <f t="shared" si="126"/>
         <v>1.1697086576210483</v>
       </c>
       <c r="BJ79" s="39">
-        <f t="shared" si="102"/>
+        <f t="shared" si="126"/>
         <v>1.1658263649778653</v>
       </c>
       <c r="BK79" s="39">
-        <f t="shared" si="102"/>
+        <f t="shared" si="126"/>
         <v>1.0898550724637681</v>
       </c>
       <c r="BL79" s="39">
-        <f t="shared" si="102"/>
+        <f t="shared" si="126"/>
         <v>1.1401821213287162</v>
       </c>
       <c r="BM79" s="39">
-        <f t="shared" si="102"/>
+        <f t="shared" si="126"/>
         <v>1.2894645541806407</v>
       </c>
       <c r="BN79" s="39">
-        <f t="shared" si="102"/>
+        <f t="shared" si="126"/>
         <v>1.0262226847034339</v>
       </c>
       <c r="BO79" s="39">
@@ -24328,19 +24325,19 @@
         <v>1.1222635673899386</v>
       </c>
       <c r="CM79" s="39">
-        <f t="shared" ref="CM79:CP79" si="103">SUM(CM51:CM57)/SUM(CM65:CM71)</f>
+        <f t="shared" ref="CM79:CP79" si="127">SUM(CM51:CM57)/SUM(CM65:CM71)</f>
         <v>1.2877222306640328</v>
       </c>
       <c r="CN79" s="39">
-        <f t="shared" si="103"/>
+        <f t="shared" si="127"/>
         <v>1.1718297932397148</v>
       </c>
       <c r="CO79" s="39">
-        <f t="shared" si="103"/>
+        <f t="shared" si="127"/>
         <v>1.1658263649778653</v>
       </c>
       <c r="CP79" s="39">
-        <f t="shared" si="103"/>
+        <f t="shared" si="127"/>
         <v>1.0262226847034339</v>
       </c>
     </row>
@@ -24349,67 +24346,67 @@
         <v>128</v>
       </c>
       <c r="AY80" s="39">
-        <f t="shared" ref="AY80:BN80" si="104">SUM(AY51:AY54)/SUM(AY65:AY71)</f>
+        <f t="shared" ref="AY80:BN80" si="128">SUM(AY51:AY54)/SUM(AY65:AY71)</f>
         <v>0.95590413943355124</v>
       </c>
       <c r="AZ80" s="39">
-        <f t="shared" si="104"/>
+        <f t="shared" si="128"/>
         <v>0.895724528635921</v>
       </c>
       <c r="BA80" s="39">
-        <f t="shared" si="104"/>
+        <f t="shared" si="128"/>
         <v>0.89282934002248937</v>
       </c>
       <c r="BB80" s="39">
-        <f t="shared" si="104"/>
+        <f t="shared" si="128"/>
         <v>0.87266372891657806</v>
       </c>
       <c r="BC80" s="39">
-        <f t="shared" si="104"/>
+        <f t="shared" si="128"/>
         <v>0.90560026827632456</v>
       </c>
       <c r="BD80" s="39">
-        <f t="shared" si="104"/>
+        <f t="shared" si="128"/>
         <v>0.83723624327678936</v>
       </c>
       <c r="BE80" s="39">
-        <f t="shared" si="104"/>
+        <f t="shared" si="128"/>
         <v>0.87548233897298899</v>
       </c>
       <c r="BF80" s="39">
-        <f t="shared" si="104"/>
+        <f t="shared" si="128"/>
         <v>0.67497000917366456</v>
       </c>
       <c r="BG80" s="39">
-        <f t="shared" si="104"/>
+        <f t="shared" si="128"/>
         <v>0.8112958757600176</v>
       </c>
       <c r="BH80" s="39">
-        <f t="shared" si="104"/>
+        <f t="shared" si="128"/>
         <v>0.74303088275485107</v>
       </c>
       <c r="BI80" s="39">
-        <f t="shared" si="104"/>
+        <f t="shared" si="128"/>
         <v>0.69674219987602448</v>
       </c>
       <c r="BJ80" s="39">
-        <f t="shared" si="104"/>
+        <f t="shared" si="128"/>
         <v>0.67984505656665029</v>
       </c>
       <c r="BK80" s="39">
-        <f t="shared" si="104"/>
+        <f t="shared" si="128"/>
         <v>0.56302868973676423</v>
       </c>
       <c r="BL80" s="39">
-        <f t="shared" si="104"/>
+        <f t="shared" si="128"/>
         <v>0.5854815954854431</v>
       </c>
       <c r="BM80" s="39">
-        <f t="shared" si="104"/>
+        <f t="shared" si="128"/>
         <v>0.76726032149878576</v>
       </c>
       <c r="BN80" s="39">
-        <f t="shared" si="104"/>
+        <f t="shared" si="128"/>
         <v>0.57950052029136312</v>
       </c>
       <c r="BO80" s="39">
@@ -24425,19 +24422,19 @@
         <v>0.63693036292466054</v>
       </c>
       <c r="CM80" s="39">
-        <f t="shared" ref="CM80:CP80" si="105">SUM(CM51:CM54)/SUM(CM65:CM71)</f>
+        <f t="shared" ref="CM80:CP80" si="129">SUM(CM51:CM54)/SUM(CM65:CM71)</f>
         <v>0.87266372891657806</v>
       </c>
       <c r="CN80" s="39">
-        <f t="shared" si="105"/>
+        <f t="shared" si="129"/>
         <v>0.67497000917366456</v>
       </c>
       <c r="CO80" s="39">
-        <f t="shared" si="105"/>
+        <f t="shared" si="129"/>
         <v>0.67984505656665029</v>
       </c>
       <c r="CP80" s="39">
-        <f t="shared" si="105"/>
+        <f t="shared" si="129"/>
         <v>0.57950052029136312</v>
       </c>
     </row>
@@ -24446,67 +24443,67 @@
         <v>129</v>
       </c>
       <c r="AY81" s="39">
-        <f t="shared" ref="AY81:BN81" si="106">AY26/AY63</f>
+        <f t="shared" ref="AY81:BN81" si="130">AY26/AY63</f>
         <v>0.11939655172413793</v>
       </c>
       <c r="AZ81" s="39">
-        <f t="shared" si="106"/>
+        <f t="shared" si="130"/>
         <v>0.12970124029675462</v>
       </c>
       <c r="BA81" s="39">
-        <f t="shared" si="106"/>
+        <f t="shared" si="130"/>
         <v>0.14077944083592206</v>
       </c>
       <c r="BB81" s="39">
-        <f t="shared" si="106"/>
+        <f t="shared" si="130"/>
         <v>0.13846929836204838</v>
       </c>
       <c r="BC81" s="39">
-        <f t="shared" si="106"/>
+        <f t="shared" si="130"/>
         <v>0.13903613809434115</v>
       </c>
       <c r="BD81" s="39">
-        <f t="shared" si="106"/>
+        <f t="shared" si="130"/>
         <v>0.15172090199000857</v>
       </c>
       <c r="BE81" s="39">
-        <f t="shared" si="106"/>
+        <f t="shared" si="130"/>
         <v>0.15303626502180157</v>
       </c>
       <c r="BF81" s="39">
-        <f t="shared" si="106"/>
+        <f t="shared" si="130"/>
         <v>0.15021691973969631</v>
       </c>
       <c r="BG81" s="39">
-        <f t="shared" si="106"/>
+        <f t="shared" si="130"/>
         <v>0.14762687487158413</v>
       </c>
       <c r="BH81" s="39">
-        <f t="shared" si="106"/>
+        <f t="shared" si="130"/>
         <v>0.16072710491231668</v>
       </c>
       <c r="BI81" s="39">
-        <f t="shared" si="106"/>
+        <f t="shared" si="130"/>
         <v>0.16466703634622171</v>
       </c>
       <c r="BJ81" s="39">
-        <f t="shared" si="106"/>
+        <f t="shared" si="130"/>
         <v>0.15425932906143988</v>
       </c>
       <c r="BK81" s="39">
-        <f t="shared" si="106"/>
+        <f t="shared" si="130"/>
         <v>0.14900708886906719</v>
       </c>
       <c r="BL81" s="39">
-        <f t="shared" si="106"/>
+        <f t="shared" si="130"/>
         <v>0.16443436562492619</v>
       </c>
       <c r="BM81" s="39">
-        <f t="shared" si="106"/>
+        <f t="shared" si="130"/>
         <v>0.15600059275567882</v>
       </c>
       <c r="BN81" s="39">
-        <f t="shared" si="106"/>
+        <f t="shared" si="130"/>
         <v>0.15575799172230195</v>
       </c>
       <c r="BO81" s="39">
@@ -24522,19 +24519,19 @@
         <v>0.16142168177297378</v>
       </c>
       <c r="CM81" s="39">
-        <f t="shared" ref="CM81:CP81" si="107">CM26/CM63</f>
+        <f t="shared" ref="CM81:CP81" si="131">CM26/CM63</f>
         <v>0.5013140778889803</v>
       </c>
       <c r="CN81" s="39">
-        <f t="shared" si="107"/>
+        <f t="shared" si="131"/>
         <v>0.57424336328891645</v>
       </c>
       <c r="CO81" s="39">
-        <f t="shared" si="107"/>
+        <f t="shared" si="131"/>
         <v>0.59126460610629472</v>
       </c>
       <c r="CP81" s="39">
-        <f t="shared" si="107"/>
+        <f t="shared" si="131"/>
         <v>0.58582392213140322</v>
       </c>
     </row>
@@ -24543,67 +24540,67 @@
         <v>130</v>
       </c>
       <c r="AY82" s="53">
-        <f t="shared" ref="AY82:BN82" si="108">AY39/AY63</f>
+        <f t="shared" ref="AY82:BN82" si="132">AY39/AY63</f>
         <v>5.2528735632183909E-2</v>
       </c>
       <c r="AZ82" s="53">
-        <f t="shared" si="108"/>
+        <f t="shared" si="132"/>
         <v>5.9179055312079287E-2</v>
       </c>
       <c r="BA82" s="53">
-        <f t="shared" si="108"/>
+        <f t="shared" si="132"/>
         <v>6.8172832533182723E-2</v>
       </c>
       <c r="BB82" s="53">
-        <f t="shared" si="108"/>
+        <f t="shared" si="132"/>
         <v>6.3155379755236399E-2</v>
       </c>
       <c r="BC82" s="53">
-        <f t="shared" si="108"/>
+        <f t="shared" si="132"/>
         <v>7.0796222048811988E-2</v>
       </c>
       <c r="BD82" s="53">
-        <f t="shared" si="108"/>
+        <f t="shared" si="132"/>
         <v>6.2791532113383564E-2</v>
       </c>
       <c r="BE82" s="53">
-        <f t="shared" si="108"/>
+        <f t="shared" si="132"/>
         <v>6.6441561203871111E-2</v>
       </c>
       <c r="BF82" s="53">
-        <f t="shared" si="108"/>
+        <f t="shared" si="132"/>
         <v>6.520504080157008E-2</v>
       </c>
       <c r="BG82" s="53">
-        <f t="shared" si="108"/>
+        <f t="shared" si="132"/>
         <v>6.0637970002054654E-2</v>
       </c>
       <c r="BH82" s="53">
-        <f t="shared" si="108"/>
+        <f t="shared" si="132"/>
         <v>7.2941236796226022E-2</v>
       </c>
       <c r="BI82" s="53">
-        <f t="shared" si="108"/>
+        <f t="shared" si="132"/>
         <v>8.0606946614911523E-2</v>
       </c>
       <c r="BJ82" s="53">
-        <f t="shared" si="108"/>
+        <f t="shared" si="132"/>
         <v>6.5751036562382209E-2</v>
       </c>
       <c r="BK82" s="53">
-        <f t="shared" si="108"/>
+        <f t="shared" si="132"/>
         <v>7.0677432984366934E-2</v>
       </c>
       <c r="BL82" s="53">
-        <f t="shared" si="108"/>
+        <f t="shared" si="132"/>
         <v>7.6961235915243426E-2</v>
       </c>
       <c r="BM82" s="53">
-        <f t="shared" si="108"/>
+        <f t="shared" si="132"/>
         <v>6.9077206427165153E-2</v>
       </c>
       <c r="BN82" s="53">
-        <f t="shared" si="108"/>
+        <f t="shared" si="132"/>
         <v>6.9507705746552698E-2</v>
       </c>
       <c r="BO82" s="53">
@@ -24619,19 +24616,19 @@
         <v>7.3692506896357604E-2</v>
       </c>
       <c r="CM82" s="53">
-        <f t="shared" ref="CM82:CP82" si="109">CM39/CM63</f>
+        <f t="shared" ref="CM82:CP82" si="133">CM39/CM63</f>
         <v>0.23061403275903264</v>
       </c>
       <c r="CN82" s="53">
-        <f t="shared" si="109"/>
+        <f t="shared" si="133"/>
         <v>0.25643012085528355</v>
       </c>
       <c r="CO82" s="53">
-        <f t="shared" si="109"/>
+        <f t="shared" si="133"/>
         <v>0.26373445156426689</v>
       </c>
       <c r="CP82" s="53">
-        <f t="shared" si="109"/>
+        <f t="shared" si="133"/>
         <v>0.26775649424928766</v>
       </c>
     </row>
@@ -24640,67 +24637,67 @@
         <v>131</v>
       </c>
       <c r="AY83" s="53">
-        <f t="shared" ref="AY83:BN83" si="110">AY39/AY76</f>
+        <f t="shared" ref="AY83:BN83" si="134">AY39/AY76</f>
         <v>0.28327909499457615</v>
       </c>
       <c r="AZ83" s="53">
-        <f t="shared" si="110"/>
+        <f t="shared" si="134"/>
         <v>0.314507535393515</v>
       </c>
       <c r="BA83" s="53">
-        <f t="shared" si="110"/>
+        <f t="shared" si="134"/>
         <v>0.35489561893560717</v>
       </c>
       <c r="BB83" s="53">
-        <f t="shared" si="110"/>
+        <f t="shared" si="134"/>
         <v>0.32096600107933082</v>
       </c>
       <c r="BC83" s="53">
-        <f t="shared" si="110"/>
+        <f t="shared" si="134"/>
         <v>0.36900420757363256</v>
       </c>
       <c r="BD83" s="53">
-        <f t="shared" si="110"/>
+        <f t="shared" si="134"/>
         <v>0.36330245927818589</v>
       </c>
       <c r="BE83" s="53">
-        <f t="shared" si="110"/>
+        <f t="shared" si="134"/>
         <v>0.38786279683377306</v>
       </c>
       <c r="BF83" s="53">
-        <f t="shared" si="110"/>
+        <f t="shared" si="134"/>
         <v>0.39595421044378232</v>
       </c>
       <c r="BG83" s="53">
-        <f t="shared" si="110"/>
+        <f t="shared" si="134"/>
         <v>0.43665618642500464</v>
       </c>
       <c r="BH83" s="53">
-        <f t="shared" si="110"/>
+        <f t="shared" si="134"/>
         <v>0.50994801935830791</v>
       </c>
       <c r="BI83" s="53">
-        <f t="shared" si="110"/>
+        <f t="shared" si="134"/>
         <v>0.50117536436295251</v>
       </c>
       <c r="BJ83" s="53">
-        <f t="shared" si="110"/>
+        <f t="shared" si="134"/>
         <v>0.3988852365299414</v>
       </c>
       <c r="BK83" s="53">
-        <f t="shared" si="110"/>
+        <f t="shared" si="134"/>
         <v>0.41201423097974821</v>
       </c>
       <c r="BL83" s="53">
-        <f t="shared" si="110"/>
+        <f t="shared" si="134"/>
         <v>0.43544506816359263</v>
       </c>
       <c r="BM83" s="53">
-        <f t="shared" si="110"/>
+        <f t="shared" si="134"/>
         <v>0.43518271539077086</v>
       </c>
       <c r="BN83" s="53">
-        <f t="shared" si="110"/>
+        <f t="shared" si="134"/>
         <v>0.51297006907137377</v>
       </c>
       <c r="BO83" s="53">
@@ -24716,19 +24713,19 @@
         <v>0.49589594645788609</v>
       </c>
       <c r="CM83" s="53">
-        <f t="shared" ref="CM83:CP83" si="111">CM39/CM76</f>
+        <f t="shared" ref="CM83:CP83" si="135">CM39/CM76</f>
         <v>1.1720183486238531</v>
       </c>
       <c r="CN83" s="53">
-        <f t="shared" si="111"/>
+        <f t="shared" si="135"/>
         <v>1.5571585384977262</v>
       </c>
       <c r="CO83" s="53">
-        <f t="shared" si="111"/>
+        <f t="shared" si="135"/>
         <v>1.5999714163212806</v>
       </c>
       <c r="CP83" s="53">
-        <f t="shared" si="111"/>
+        <f t="shared" si="135"/>
         <v>1.9760552570990022</v>
       </c>
     </row>
@@ -24737,271 +24734,271 @@
         <v>132</v>
       </c>
       <c r="C85" s="1">
-        <f t="shared" ref="C85:AH85" si="112">C39</f>
+        <f t="shared" ref="C85:AH85" si="136">C39</f>
         <v>367</v>
       </c>
       <c r="D85" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="136"/>
         <v>349</v>
       </c>
       <c r="E85" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="136"/>
         <v>439</v>
       </c>
       <c r="F85" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="136"/>
         <v>308</v>
       </c>
       <c r="G85" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="136"/>
         <v>455</v>
       </c>
       <c r="H85" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="136"/>
         <v>458</v>
       </c>
       <c r="I85" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="136"/>
         <v>519</v>
       </c>
       <c r="J85" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="136"/>
         <v>415</v>
       </c>
       <c r="K85" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="136"/>
         <v>562</v>
       </c>
       <c r="L85" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="136"/>
         <v>608</v>
       </c>
       <c r="M85" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="136"/>
         <v>716</v>
       </c>
       <c r="N85" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="136"/>
         <v>20</v>
       </c>
       <c r="O85" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="136"/>
         <v>682</v>
       </c>
       <c r="P85" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="136"/>
         <v>700</v>
       </c>
       <c r="Q85" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="136"/>
         <v>772</v>
       </c>
       <c r="R85" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="136"/>
         <v>605</v>
       </c>
       <c r="S85" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="136"/>
         <v>766</v>
       </c>
       <c r="T85" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="136"/>
         <v>848</v>
       </c>
       <c r="U85" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="136"/>
         <v>879</v>
       </c>
       <c r="V85" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="136"/>
         <v>623</v>
       </c>
       <c r="W85" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="136"/>
         <v>870</v>
       </c>
       <c r="X85" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="136"/>
         <v>931</v>
       </c>
       <c r="Y85" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="136"/>
         <v>1015</v>
       </c>
       <c r="Z85" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="136"/>
         <v>801</v>
       </c>
       <c r="AA85" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="136"/>
         <v>1020</v>
       </c>
       <c r="AB85" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="136"/>
         <v>921</v>
       </c>
       <c r="AC85" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="136"/>
         <v>977</v>
       </c>
       <c r="AD85" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="136"/>
         <v>890</v>
       </c>
       <c r="AE85" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="136"/>
         <v>959</v>
       </c>
       <c r="AF85" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="136"/>
         <v>983</v>
       </c>
       <c r="AG85" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="136"/>
         <v>1184</v>
       </c>
       <c r="AH85" s="1">
-        <f t="shared" si="112"/>
+        <f t="shared" si="136"/>
         <v>933</v>
       </c>
       <c r="AI85" s="1">
-        <f t="shared" ref="AI85:BO85" si="113">AI39</f>
+        <f t="shared" ref="AI85:BO85" si="137">AI39</f>
         <v>1081</v>
       </c>
       <c r="AJ85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>1177</v>
       </c>
       <c r="AK85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>1430</v>
       </c>
       <c r="AL85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>227</v>
       </c>
       <c r="AM85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>1492</v>
       </c>
       <c r="AN85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>1569</v>
       </c>
       <c r="AO85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>1899</v>
       </c>
       <c r="AP85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>899</v>
       </c>
       <c r="AQ85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>1862</v>
       </c>
       <c r="AR85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>2048</v>
       </c>
       <c r="AS85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>2108</v>
       </c>
       <c r="AT85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>2100</v>
       </c>
       <c r="AU85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>1693</v>
       </c>
       <c r="AV85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>1420</v>
       </c>
       <c r="AW85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>1513</v>
       </c>
       <c r="AX85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>1785</v>
       </c>
       <c r="AY85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>1828</v>
       </c>
       <c r="AZ85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>2066</v>
       </c>
       <c r="BA85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>2414</v>
       </c>
       <c r="BB85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>2379</v>
       </c>
       <c r="BC85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>2631</v>
       </c>
       <c r="BD85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>2275</v>
       </c>
       <c r="BE85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>2499</v>
       </c>
       <c r="BF85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>2525</v>
       </c>
       <c r="BG85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>2361</v>
       </c>
       <c r="BH85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>2845</v>
       </c>
       <c r="BI85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>3198</v>
       </c>
       <c r="BJ85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>2791</v>
       </c>
       <c r="BK85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>3011</v>
       </c>
       <c r="BL85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>3258</v>
       </c>
       <c r="BM85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>3263</v>
       </c>
       <c r="BN85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>3342</v>
       </c>
       <c r="BO85" s="1">
-        <f t="shared" si="113"/>
+        <f t="shared" si="137"/>
         <v>3280</v>
       </c>
       <c r="BP85" s="1">
-        <f t="shared" ref="BP85:BQ85" si="114">BP39</f>
+        <f t="shared" ref="BP85:BQ85" si="138">BP39</f>
         <v>3701</v>
       </c>
       <c r="BQ85" s="1">
-        <f t="shared" si="114"/>
+        <f t="shared" si="138"/>
         <v>3927</v>
       </c>
       <c r="CA85" s="1">
@@ -25685,259 +25682,259 @@
         <v>135</v>
       </c>
       <c r="C88" s="2">
-        <f t="shared" ref="C88:BN88" si="115">C86+C87</f>
+        <f t="shared" ref="C88:BN88" si="139">C86+C87</f>
         <v>388</v>
       </c>
       <c r="D88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>327</v>
       </c>
       <c r="E88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>283</v>
       </c>
       <c r="F88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>240</v>
       </c>
       <c r="G88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>75</v>
       </c>
       <c r="H88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>298</v>
       </c>
       <c r="I88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>549</v>
       </c>
       <c r="J88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>624</v>
       </c>
       <c r="K88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>330</v>
       </c>
       <c r="L88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>491</v>
       </c>
       <c r="M88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>963</v>
       </c>
       <c r="N88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>723</v>
       </c>
       <c r="O88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>376</v>
       </c>
       <c r="P88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>585</v>
       </c>
       <c r="Q88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>957</v>
       </c>
       <c r="R88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>812</v>
       </c>
       <c r="S88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>830</v>
       </c>
       <c r="T88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>681</v>
       </c>
       <c r="U88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>1272</v>
       </c>
       <c r="V88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>1053</v>
       </c>
       <c r="W88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>543</v>
       </c>
       <c r="X88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>715</v>
       </c>
       <c r="Y88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>1327</v>
       </c>
       <c r="Z88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>647</v>
       </c>
       <c r="AA88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>880</v>
       </c>
       <c r="AB88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>796</v>
       </c>
       <c r="AC88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>1203</v>
       </c>
       <c r="AD88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>1045</v>
       </c>
       <c r="AE88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>1021</v>
       </c>
       <c r="AF88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>997</v>
       </c>
       <c r="AG88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>1369</v>
       </c>
       <c r="AH88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>1035</v>
       </c>
       <c r="AI88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>663</v>
       </c>
       <c r="AJ88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>1275</v>
       </c>
       <c r="AK88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>1689</v>
       </c>
       <c r="AL88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>1737</v>
       </c>
       <c r="AM88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>953</v>
       </c>
       <c r="AN88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>1399</v>
       </c>
       <c r="AO88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>2284</v>
       </c>
       <c r="AP88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>1257</v>
       </c>
       <c r="AQ88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>1229</v>
       </c>
       <c r="AR88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>1445</v>
       </c>
       <c r="AS88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>2223</v>
       </c>
       <c r="AT88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>2864</v>
       </c>
       <c r="AU88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>1728</v>
       </c>
       <c r="AV88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>1388</v>
       </c>
       <c r="AW88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>1575</v>
       </c>
       <c r="AX88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>2194</v>
       </c>
       <c r="AY88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>1398</v>
       </c>
       <c r="AZ88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>2187</v>
       </c>
       <c r="BA88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>2404</v>
       </c>
       <c r="BB88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>3067</v>
       </c>
       <c r="BC88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>1636</v>
       </c>
       <c r="BD88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>2402</v>
       </c>
       <c r="BE88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>3745</v>
       </c>
       <c r="BF88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>2970</v>
       </c>
       <c r="BG88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>1809</v>
       </c>
       <c r="BH88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>2618</v>
       </c>
       <c r="BI88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>3129</v>
       </c>
       <c r="BJ88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>4053</v>
       </c>
       <c r="BK88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>1515</v>
       </c>
       <c r="BL88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>3023</v>
       </c>
       <c r="BM88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>5029</v>
       </c>
       <c r="BN88" s="2">
-        <f t="shared" si="115"/>
+        <f t="shared" si="139"/>
         <v>4739</v>
       </c>
       <c r="BO88" s="2">
@@ -26091,255 +26088,255 @@
         <v>136</v>
       </c>
       <c r="C89" s="1">
-        <f t="shared" ref="C89:AH89" si="116">C40</f>
+        <f t="shared" ref="C89:AH89" si="140">C40</f>
         <v>1300</v>
       </c>
       <c r="D89" s="1">
-        <f t="shared" si="116"/>
+        <f t="shared" si="140"/>
         <v>1300</v>
       </c>
       <c r="E89" s="1">
-        <f t="shared" si="116"/>
+        <f t="shared" si="140"/>
         <v>1300</v>
       </c>
       <c r="F89" s="1">
-        <f t="shared" si="116"/>
+        <f t="shared" si="140"/>
         <v>1300</v>
       </c>
       <c r="G89" s="1">
-        <f t="shared" si="116"/>
+        <f t="shared" si="140"/>
         <v>1300</v>
       </c>
       <c r="H89" s="1">
-        <f t="shared" si="116"/>
+        <f t="shared" si="140"/>
         <v>1310</v>
       </c>
       <c r="I89" s="1">
-        <f t="shared" si="116"/>
+        <f t="shared" si="140"/>
         <v>1310</v>
       </c>
       <c r="J89" s="1">
-        <f t="shared" si="116"/>
+        <f t="shared" si="140"/>
         <v>1310</v>
       </c>
       <c r="K89" s="1">
-        <f t="shared" si="116"/>
+        <f t="shared" si="140"/>
         <v>1300</v>
       </c>
       <c r="L89" s="1">
-        <f t="shared" si="116"/>
+        <f t="shared" si="140"/>
         <v>1270</v>
       </c>
       <c r="M89" s="1">
-        <f t="shared" si="116"/>
+        <f t="shared" si="140"/>
         <v>1270</v>
       </c>
       <c r="N89" s="1">
-        <f t="shared" si="116"/>
+        <f t="shared" si="140"/>
         <v>1279</v>
       </c>
       <c r="O89" s="1">
-        <f t="shared" si="116"/>
+        <f t="shared" si="140"/>
         <v>1270</v>
       </c>
       <c r="P89" s="1">
-        <f t="shared" si="116"/>
+        <f t="shared" si="140"/>
         <v>1260</v>
       </c>
       <c r="Q89" s="1">
-        <f t="shared" si="116"/>
+        <f t="shared" si="140"/>
         <v>1250</v>
       </c>
       <c r="R89" s="1">
-        <f t="shared" si="116"/>
+        <f t="shared" si="140"/>
         <v>1253</v>
       </c>
       <c r="S89" s="1">
-        <f t="shared" si="116"/>
+        <f t="shared" si="140"/>
         <v>1226</v>
       </c>
       <c r="T89" s="1">
-        <f t="shared" si="116"/>
+        <f t="shared" si="140"/>
         <v>1214</v>
       </c>
       <c r="U89" s="1">
-        <f t="shared" si="116"/>
+        <f t="shared" si="140"/>
         <v>1205</v>
       </c>
       <c r="V89" s="1">
-        <f t="shared" si="116"/>
+        <f t="shared" si="140"/>
         <v>1211</v>
       </c>
       <c r="W89" s="1">
-        <f t="shared" si="116"/>
+        <f t="shared" si="140"/>
         <v>1185</v>
       </c>
       <c r="X89" s="1">
-        <f t="shared" si="116"/>
+        <f t="shared" si="140"/>
         <v>1165</v>
       </c>
       <c r="Y89" s="1">
-        <f t="shared" si="116"/>
+        <f t="shared" si="140"/>
         <v>1157</v>
       </c>
       <c r="Z89" s="1">
-        <f t="shared" si="116"/>
+        <f t="shared" si="140"/>
         <v>1165</v>
       </c>
       <c r="AA89" s="1">
-        <f t="shared" si="116"/>
+        <f t="shared" si="140"/>
         <v>1148</v>
       </c>
       <c r="AB89" s="1">
-        <f t="shared" si="116"/>
+        <f t="shared" si="140"/>
         <v>1138</v>
       </c>
       <c r="AC89" s="1">
-        <f t="shared" si="116"/>
+        <f t="shared" si="140"/>
         <v>1130</v>
       </c>
       <c r="AD89" s="1">
-        <f t="shared" si="116"/>
+        <f t="shared" si="140"/>
         <v>1134</v>
       </c>
       <c r="AE89" s="1">
-        <f t="shared" si="116"/>
+        <f t="shared" si="140"/>
         <v>1109</v>
       </c>
       <c r="AF89" s="1">
-        <f t="shared" si="116"/>
+        <f t="shared" si="140"/>
         <v>1098</v>
       </c>
       <c r="AG89" s="1">
-        <f t="shared" si="116"/>
+        <f t="shared" si="140"/>
         <v>1096</v>
       </c>
       <c r="AH89" s="1">
-        <f t="shared" si="116"/>
+        <f t="shared" si="140"/>
         <v>1098</v>
       </c>
       <c r="AI89" s="1">
-        <f t="shared" ref="AI89:BM89" si="117">AI40</f>
+        <f t="shared" ref="AI89:BM89" si="141">AI40</f>
         <v>1078</v>
       </c>
       <c r="AJ89" s="1">
-        <f t="shared" si="117"/>
+        <f t="shared" si="141"/>
         <v>1070</v>
       </c>
       <c r="AK89" s="1">
-        <f t="shared" si="117"/>
+        <f t="shared" si="141"/>
         <v>1063</v>
       </c>
       <c r="AL89" s="1">
-        <f t="shared" si="117"/>
+        <f t="shared" si="141"/>
         <v>1067</v>
       </c>
       <c r="AM89" s="1">
-        <f t="shared" si="117"/>
+        <f t="shared" si="141"/>
         <v>1051</v>
       </c>
       <c r="AN89" s="1">
-        <f t="shared" si="117"/>
+        <f t="shared" si="141"/>
         <v>1043</v>
       </c>
       <c r="AO89" s="1">
-        <f t="shared" si="117"/>
+        <f t="shared" si="141"/>
         <v>1037</v>
       </c>
       <c r="AP89" s="1">
-        <f t="shared" si="117"/>
+        <f t="shared" si="141"/>
         <v>1041</v>
       </c>
       <c r="AQ89" s="1">
-        <f t="shared" si="117"/>
+        <f t="shared" si="141"/>
         <v>1026</v>
       </c>
       <c r="AR89" s="1">
-        <f t="shared" si="117"/>
+        <f t="shared" si="141"/>
         <v>1020</v>
       </c>
       <c r="AS89" s="1">
-        <f t="shared" si="117"/>
+        <f t="shared" si="141"/>
         <v>1013</v>
       </c>
       <c r="AT89" s="1">
-        <f t="shared" si="117"/>
+        <f t="shared" si="141"/>
         <v>1017</v>
       </c>
       <c r="AU89" s="1">
-        <f t="shared" si="117"/>
+        <f t="shared" si="141"/>
         <v>1005</v>
       </c>
       <c r="AV89" s="1">
-        <f t="shared" si="117"/>
+        <f t="shared" si="141"/>
         <v>1004</v>
       </c>
       <c r="AW89" s="1">
-        <f t="shared" si="117"/>
+        <f t="shared" si="141"/>
         <v>1001</v>
       </c>
       <c r="AX89" s="1">
-        <f t="shared" si="117"/>
+        <f t="shared" si="141"/>
         <v>1002</v>
       </c>
       <c r="AY89" s="1">
-        <f t="shared" si="117"/>
+        <f t="shared" si="141"/>
         <v>994</v>
       </c>
       <c r="AZ89" s="1">
-        <f t="shared" si="117"/>
+        <f t="shared" si="141"/>
         <v>990</v>
       </c>
       <c r="BA89" s="1">
-        <f t="shared" si="117"/>
+        <f t="shared" si="141"/>
         <v>986</v>
       </c>
       <c r="BB89" s="1">
-        <f t="shared" si="117"/>
+        <f t="shared" si="141"/>
         <v>988</v>
       </c>
       <c r="BC89" s="1">
-        <f t="shared" si="117"/>
+        <f t="shared" si="141"/>
         <v>977</v>
       </c>
       <c r="BD89" s="1">
-        <f t="shared" si="117"/>
+        <f t="shared" si="141"/>
         <v>971</v>
       </c>
       <c r="BE89" s="1">
-        <f t="shared" si="117"/>
+        <f t="shared" si="141"/>
         <v>965</v>
       </c>
       <c r="BF89" s="1">
-        <f t="shared" si="117"/>
+        <f t="shared" si="141"/>
         <v>968</v>
       </c>
       <c r="BG89" s="1">
-        <f t="shared" si="117"/>
+        <f t="shared" si="141"/>
         <v>953</v>
       </c>
       <c r="BH89" s="1">
-        <f t="shared" si="117"/>
+        <f t="shared" si="141"/>
         <v>946</v>
       </c>
       <c r="BI89" s="1">
-        <f t="shared" si="117"/>
+        <f t="shared" si="141"/>
         <v>941</v>
       </c>
       <c r="BJ89" s="1">
-        <f t="shared" si="117"/>
+        <f t="shared" si="141"/>
         <v>944</v>
       </c>
       <c r="BK89" s="1">
-        <f t="shared" si="117"/>
+        <f t="shared" si="141"/>
         <v>933</v>
       </c>
       <c r="BL89" s="1">
-        <f t="shared" si="117"/>
+        <f t="shared" si="141"/>
         <v>929</v>
       </c>
       <c r="BM89" s="1">
-        <f t="shared" si="117"/>
+        <f t="shared" si="141"/>
         <v>923</v>
       </c>
       <c r="BN89" s="1">
@@ -26358,63 +26355,63 @@
         <v>903</v>
       </c>
       <c r="CA89" s="1">
-        <f t="shared" ref="CA89:CO89" si="118">CA40</f>
+        <f t="shared" ref="CA89:CO89" si="142">CA40</f>
         <v>1300</v>
       </c>
       <c r="CB89" s="1">
-        <f t="shared" si="118"/>
+        <f t="shared" si="142"/>
         <v>1307.5</v>
       </c>
       <c r="CC89" s="1">
-        <f t="shared" si="118"/>
+        <f t="shared" si="142"/>
         <v>1279.75</v>
       </c>
       <c r="CD89" s="1">
-        <f t="shared" si="118"/>
+        <f t="shared" si="142"/>
         <v>1258.25</v>
       </c>
       <c r="CE89" s="1">
-        <f t="shared" si="118"/>
+        <f t="shared" si="142"/>
         <v>1214</v>
       </c>
       <c r="CF89" s="1">
-        <f t="shared" si="118"/>
+        <f t="shared" si="142"/>
         <v>1168</v>
       </c>
       <c r="CG89" s="1">
-        <f t="shared" si="118"/>
+        <f t="shared" si="142"/>
         <v>1137.5</v>
       </c>
       <c r="CH89" s="1">
-        <f t="shared" si="118"/>
+        <f t="shared" si="142"/>
         <v>1100.25</v>
       </c>
       <c r="CI89" s="1">
-        <f t="shared" si="118"/>
+        <f t="shared" si="142"/>
         <v>1069.5</v>
       </c>
       <c r="CJ89" s="1">
-        <f t="shared" si="118"/>
+        <f t="shared" si="142"/>
         <v>1043</v>
       </c>
       <c r="CK89" s="1">
-        <f t="shared" si="118"/>
+        <f t="shared" si="142"/>
         <v>1019</v>
       </c>
       <c r="CL89" s="1">
-        <f t="shared" si="118"/>
+        <f t="shared" si="142"/>
         <v>1003</v>
       </c>
       <c r="CM89" s="1">
-        <f t="shared" si="118"/>
+        <f t="shared" si="142"/>
         <v>989.5</v>
       </c>
       <c r="CN89" s="1">
-        <f t="shared" si="118"/>
+        <f t="shared" si="142"/>
         <v>970.25</v>
       </c>
       <c r="CO89" s="1">
-        <f t="shared" si="118"/>
+        <f t="shared" si="142"/>
         <v>946</v>
       </c>
       <c r="CP89" s="1">
@@ -26427,259 +26424,259 @@
         <v>137</v>
       </c>
       <c r="C90" s="39">
-        <f t="shared" ref="C90:BN90" si="119">C88/C89</f>
+        <f t="shared" ref="C90:BN90" si="143">C88/C89</f>
         <v>0.29846153846153844</v>
       </c>
       <c r="D90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>0.25153846153846154</v>
       </c>
       <c r="E90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>0.21769230769230768</v>
       </c>
       <c r="F90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>0.18461538461538463</v>
       </c>
       <c r="G90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>5.7692307692307696E-2</v>
       </c>
       <c r="H90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>0.22748091603053436</v>
       </c>
       <c r="I90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>0.41908396946564885</v>
       </c>
       <c r="J90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>0.4763358778625954</v>
       </c>
       <c r="K90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>0.25384615384615383</v>
       </c>
       <c r="L90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>0.38661417322834646</v>
       </c>
       <c r="M90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>0.75826771653543312</v>
       </c>
       <c r="N90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>0.56528537920250199</v>
       </c>
       <c r="O90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>0.29606299212598425</v>
       </c>
       <c r="P90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>0.4642857142857143</v>
       </c>
       <c r="Q90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>0.76559999999999995</v>
       </c>
       <c r="R90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>0.64804469273743015</v>
       </c>
       <c r="S90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>0.67699836867862973</v>
       </c>
       <c r="T90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>0.56095551894563422</v>
       </c>
       <c r="U90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>1.0556016597510374</v>
       </c>
       <c r="V90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>0.86952931461601979</v>
       </c>
       <c r="W90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>0.45822784810126582</v>
       </c>
       <c r="X90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>0.61373390557939911</v>
       </c>
       <c r="Y90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>1.1469317199654279</v>
       </c>
       <c r="Z90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>0.55536480686695278</v>
       </c>
       <c r="AA90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>0.76655052264808365</v>
       </c>
       <c r="AB90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>0.69947275922671348</v>
       </c>
       <c r="AC90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>1.0646017699115045</v>
       </c>
       <c r="AD90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>0.92151675485008822</v>
       </c>
       <c r="AE90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>0.92064923354373307</v>
       </c>
       <c r="AF90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>0.90801457194899815</v>
       </c>
       <c r="AG90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>1.2490875912408759</v>
       </c>
       <c r="AH90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>0.94262295081967218</v>
       </c>
       <c r="AI90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>0.61502782931354361</v>
       </c>
       <c r="AJ90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>1.191588785046729</v>
       </c>
       <c r="AK90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>1.5888993414863593</v>
       </c>
       <c r="AL90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>1.6279287722586693</v>
       </c>
       <c r="AM90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>0.90675547098001907</v>
       </c>
       <c r="AN90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>1.3413231064237776</v>
       </c>
       <c r="AO90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>2.2025072324011572</v>
       </c>
       <c r="AP90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>1.2074927953890491</v>
       </c>
       <c r="AQ90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>1.1978557504873295</v>
       </c>
       <c r="AR90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>1.4166666666666667</v>
       </c>
       <c r="AS90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>2.1944718657453111</v>
       </c>
       <c r="AT90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>2.8161258603736479</v>
       </c>
       <c r="AU90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>1.7194029850746269</v>
       </c>
       <c r="AV90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>1.3824701195219125</v>
       </c>
       <c r="AW90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>1.5734265734265733</v>
       </c>
       <c r="AX90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>2.1896207584830338</v>
       </c>
       <c r="AY90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>1.4064386317907445</v>
       </c>
       <c r="AZ90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>2.209090909090909</v>
       </c>
       <c r="BA90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>2.4381338742393508</v>
       </c>
       <c r="BB90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>3.1042510121457489</v>
       </c>
       <c r="BC90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>1.6745138178096213</v>
       </c>
       <c r="BD90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>2.4737384140061791</v>
       </c>
       <c r="BE90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>3.8808290155440415</v>
       </c>
       <c r="BF90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>3.0681818181818183</v>
       </c>
       <c r="BG90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>1.8982161594963274</v>
       </c>
       <c r="BH90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>2.7674418604651163</v>
       </c>
       <c r="BI90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>3.3251859723698192</v>
       </c>
       <c r="BJ90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>4.2934322033898304</v>
       </c>
       <c r="BK90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>1.6237942122186495</v>
       </c>
       <c r="BL90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>3.2540365984930033</v>
       </c>
       <c r="BM90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>5.4485373781148425</v>
       </c>
       <c r="BN90" s="39">
-        <f t="shared" si="119"/>
+        <f t="shared" si="143"/>
         <v>5.1679389312977095</v>
       </c>
       <c r="BO90" s="39">
@@ -26695,67 +26692,67 @@
         <v>8.709856035437431</v>
       </c>
       <c r="CA90" s="39">
-        <f t="shared" ref="CA90:CP90" si="120">CA88/CA89</f>
+        <f t="shared" ref="CA90:CP90" si="144">CA88/CA89</f>
         <v>0.9523076923076923</v>
       </c>
       <c r="CB90" s="39">
-        <f t="shared" si="120"/>
+        <f t="shared" si="144"/>
         <v>1.1824091778202677</v>
       </c>
       <c r="CC90" s="39">
-        <f t="shared" si="120"/>
+        <f t="shared" si="144"/>
         <v>1.9589763625708145</v>
       </c>
       <c r="CD90" s="39">
-        <f t="shared" si="120"/>
+        <f t="shared" si="144"/>
         <v>2.1696801112656465</v>
       </c>
       <c r="CE90" s="39">
-        <f t="shared" si="120"/>
+        <f t="shared" si="144"/>
         <v>3.1598023064250413</v>
       </c>
       <c r="CF90" s="39">
-        <f t="shared" si="120"/>
+        <f t="shared" si="144"/>
         <v>2.7671232876712328</v>
       </c>
       <c r="CG90" s="39">
-        <f t="shared" si="120"/>
+        <f t="shared" si="144"/>
         <v>3.4496703296703295</v>
       </c>
       <c r="CH90" s="39">
-        <f t="shared" si="120"/>
+        <f t="shared" si="144"/>
         <v>4.0190865712338102</v>
       </c>
       <c r="CI90" s="39">
-        <f t="shared" si="120"/>
+        <f t="shared" si="144"/>
         <v>5.0154277699859744</v>
       </c>
       <c r="CJ90" s="39">
-        <f t="shared" si="120"/>
+        <f t="shared" si="144"/>
         <v>5.6500479386385427</v>
       </c>
       <c r="CK90" s="39">
-        <f t="shared" si="120"/>
+        <f t="shared" si="144"/>
         <v>7.6162904808635918</v>
       </c>
       <c r="CL90" s="39">
-        <f t="shared" si="120"/>
+        <f t="shared" si="144"/>
         <v>6.8644067796610173</v>
       </c>
       <c r="CM90" s="39">
-        <f t="shared" si="120"/>
+        <f t="shared" si="144"/>
         <v>9.1520970186963115</v>
       </c>
       <c r="CN90" s="39">
-        <f t="shared" si="120"/>
+        <f t="shared" si="144"/>
         <v>11.082710641587219</v>
       </c>
       <c r="CO90" s="39">
-        <f t="shared" si="120"/>
+        <f t="shared" si="144"/>
         <v>12.271670190274842</v>
       </c>
       <c r="CP90" s="39">
-        <f t="shared" si="120"/>
+        <f t="shared" si="144"/>
         <v>15.424258760107817</v>
       </c>
     </row>
